--- a/admiralty-shipyards-territory/dist/admiralty-shipyards-registry.xlsx
+++ b/admiralty-shipyards-territory/dist/admiralty-shipyards-registry.xlsx
@@ -8346,7 +8346,7 @@
         <v>1</v>
       </c>
       <c r="F142">
-        <v>31.5</v>
+        <v>33</v>
       </c>
       <c r="G142" s="3">
         <v>4937</v>
@@ -8355,7 +8355,7 @@
         <v>4937</v>
       </c>
       <c r="I142" s="3">
-        <v>147040</v>
+        <v>154445</v>
       </c>
       <c r="W142" t="inlineStr">
         <is>
@@ -14876,7 +14876,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Караульный дом</t>
+          <t xml:space="preserve">Караульный дом (северная проходная Нового Адмиралтейства)</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -14890,19 +14890,19 @@
         </is>
       </c>
       <c r="E256">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F256">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="G256">
         <v>157</v>
       </c>
       <c r="H256">
-        <v>157</v>
-      </c>
-      <c r="I256">
-        <v>785</v>
+        <v>314</v>
+      </c>
+      <c r="I256" s="3">
+        <v>1491</v>
       </c>
       <c r="W256" t="inlineStr">
         <is>

--- a/admiralty-shipyards-territory/dist/admiralty-shipyards-registry.xlsx
+++ b/admiralty-shipyards-territory/dist/admiralty-shipyards-registry.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Справка" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Реестр'!$A$1:$AA$330</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Реестр'!$A$1:$AA$331</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Склад</t>
+          <t xml:space="preserve">Корпус вдоль Сальнобуянского канала (лит. ЭС)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Склад</t>
+          <t xml:space="preserve">Административно-бытовой корпус</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3728,16 +3728,16 @@
         </is>
       </c>
       <c r="E62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G62" s="3">
         <v>1062</v>
       </c>
       <c r="H62" s="3">
-        <v>1062</v>
+        <v>2124</v>
       </c>
       <c r="I62" s="3">
         <v>9556</v>
@@ -3747,11 +3747,6 @@
           <t xml:space="preserve">Нет данных</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">да</t>
-        </is>
-      </c>
       <c r="Y62" t="inlineStr">
         <is>
           <t xml:space="preserve">OpenStreetMap</t>
@@ -8160,12 +8155,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Эллинг-цех</t>
+          <t xml:space="preserve">Токарная и слесарная мастерские Нового Адмиралтейства</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Эллинг</t>
+          <t xml:space="preserve">Производственный корпус</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -8177,16 +8172,16 @@
         <v>1</v>
       </c>
       <c r="F139">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="G139" s="3">
-        <v>6586</v>
+        <v>6587</v>
       </c>
       <c r="H139" s="3">
-        <v>6586</v>
+        <v>6587</v>
       </c>
       <c r="I139" s="3">
-        <v>191008</v>
+        <v>102099</v>
       </c>
       <c r="W139" t="inlineStr">
         <is>
@@ -8213,12 +8208,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Эллинг-цех</t>
+          <t xml:space="preserve">Корпус Нового Адмиралтейства (лит. ЖД)</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Эллинг</t>
+          <t xml:space="preserve">Производственный корпус</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -8230,7 +8225,7 @@
         <v>1</v>
       </c>
       <c r="F140">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G140" s="3">
         <v>6044</v>
@@ -8239,16 +8234,11 @@
         <v>6044</v>
       </c>
       <c r="I140" s="3">
-        <v>163199</v>
+        <v>111822</v>
       </c>
       <c r="W140" t="inlineStr">
         <is>
           <t xml:space="preserve">Нет данных</t>
-        </is>
-      </c>
-      <c r="X140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">да</t>
         </is>
       </c>
       <c r="Y140" t="inlineStr">
@@ -8271,7 +8261,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Цех Нового Адмиралтейства</t>
+          <t xml:space="preserve">Три металлических сарая</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8288,7 +8278,7 @@
         <v>1</v>
       </c>
       <c r="F141">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="G141" s="3">
         <v>5705</v>
@@ -8297,7 +8287,7 @@
         <v>5705</v>
       </c>
       <c r="I141" s="3">
-        <v>125512</v>
+        <v>125887</v>
       </c>
       <c r="W141" t="inlineStr">
         <is>
@@ -8435,12 +8425,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крытый эллинг</t>
+          <t xml:space="preserve">Малый каменный эллинг (эллинг № 1)</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Эллинг</t>
+          <t xml:space="preserve">Эллинг (исторический)</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -8452,7 +8442,7 @@
         <v>1</v>
       </c>
       <c r="F144">
-        <v>25.7</v>
+        <v>26</v>
       </c>
       <c r="G144" s="3">
         <v>2926</v>
@@ -8461,7 +8451,7 @@
         <v>2926</v>
       </c>
       <c r="I144" s="3">
-        <v>66874</v>
+        <v>69630</v>
       </c>
       <c r="W144" t="inlineStr">
         <is>
@@ -8483,17 +8473,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z191</t>
+          <t xml:space="preserve">Z153</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Эллинг</t>
+          <t xml:space="preserve">Мастерская между эллингами (1830-е)</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Эллинг</t>
+          <t xml:space="preserve">Историческое здание</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -8502,19 +8492,19 @@
         </is>
       </c>
       <c r="E145">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F145">
-        <v>25.5</v>
+        <v>19</v>
       </c>
       <c r="G145" s="3">
-        <v>2771</v>
+        <v>2466</v>
       </c>
       <c r="H145" s="3">
-        <v>2771</v>
+        <v>12330</v>
       </c>
       <c r="I145" s="3">
-        <v>70668</v>
+        <v>41922</v>
       </c>
       <c r="W145" t="inlineStr">
         <is>
@@ -8528,30 +8518,30 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenStreetMap</t>
+          <t xml:space="preserve">карта предприятия</t>
         </is>
       </c>
       <c r="Z145">
-        <v>59.929817</v>
+        <v>59.93045</v>
       </c>
       <c r="AA145">
-        <v>30.283854</v>
+        <v>30.28129</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z153</t>
+          <t xml:space="preserve">Z177</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Малый каменный эллинг (эллинг № 1)</t>
+          <t xml:space="preserve">Крытый эллинг</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Эллинг (исторический)</t>
+          <t xml:space="preserve">Эллинг</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -8563,16 +8553,16 @@
         <v>1</v>
       </c>
       <c r="F146">
-        <v>26</v>
+        <v>22.8</v>
       </c>
       <c r="G146" s="3">
-        <v>2466</v>
+        <v>2244</v>
       </c>
       <c r="H146" s="3">
-        <v>2466</v>
+        <v>2244</v>
       </c>
       <c r="I146" s="3">
-        <v>58690</v>
+        <v>45806</v>
       </c>
       <c r="W146" t="inlineStr">
         <is>
@@ -8585,26 +8575,26 @@
         </is>
       </c>
       <c r="Z146">
-        <v>59.93045</v>
+        <v>59.930838</v>
       </c>
       <c r="AA146">
-        <v>30.28129</v>
+        <v>30.282461</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z177</t>
+          <t xml:space="preserve">Z131</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крытый эллинг</t>
+          <t xml:space="preserve">Цех</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Эллинг</t>
+          <t xml:space="preserve">Производственный корпус</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -8616,48 +8606,53 @@
         <v>1</v>
       </c>
       <c r="F147">
-        <v>22.8</v>
+        <v>21.3</v>
       </c>
       <c r="G147" s="3">
-        <v>2244</v>
+        <v>2177</v>
       </c>
       <c r="H147" s="3">
-        <v>2244</v>
+        <v>2177</v>
       </c>
       <c r="I147" s="3">
-        <v>45806</v>
+        <v>38403</v>
       </c>
       <c r="W147" t="inlineStr">
         <is>
           <t xml:space="preserve">Нет данных</t>
         </is>
       </c>
+      <c r="X147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
       <c r="Y147" t="inlineStr">
         <is>
           <t xml:space="preserve">карта предприятия</t>
         </is>
       </c>
       <c r="Z147">
-        <v>59.930838</v>
+        <v>59.928348</v>
       </c>
       <c r="AA147">
-        <v>30.282461</v>
+        <v>30.278646</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z131</t>
+          <t xml:space="preserve">Z173</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Цех</t>
+          <t xml:space="preserve">Эллинг</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Производственный корпус</t>
+          <t xml:space="preserve">Эллинг</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -8669,16 +8664,16 @@
         <v>1</v>
       </c>
       <c r="F148">
-        <v>21.3</v>
+        <v>32.9</v>
       </c>
       <c r="G148" s="3">
-        <v>2177</v>
+        <v>2108</v>
       </c>
       <c r="H148" s="3">
-        <v>2177</v>
+        <v>2108</v>
       </c>
       <c r="I148" s="3">
-        <v>38403</v>
+        <v>69337</v>
       </c>
       <c r="W148" t="inlineStr">
         <is>
@@ -8692,32 +8687,32 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z148">
-        <v>59.928348</v>
+        <v>59.928755</v>
       </c>
       <c r="AA148">
-        <v>30.278646</v>
+        <v>30.281284</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z173</t>
+          <t xml:space="preserve">Z191</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
+          <t xml:space="preserve">Шлюпочная мастерская (административный корпус)</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
           <t xml:space="preserve">Эллинг</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Эллинг</t>
-        </is>
-      </c>
       <c r="D149" t="inlineStr">
         <is>
           <t xml:space="preserve">Ново-Адмиралтейский остров</t>
@@ -8727,16 +8722,16 @@
         <v>1</v>
       </c>
       <c r="F149">
-        <v>32.9</v>
+        <v>25.5</v>
       </c>
       <c r="G149" s="3">
-        <v>2108</v>
+        <v>2097</v>
       </c>
       <c r="H149" s="3">
-        <v>2108</v>
+        <v>2097</v>
       </c>
       <c r="I149" s="3">
-        <v>69337</v>
+        <v>53464</v>
       </c>
       <c r="W149" t="inlineStr">
         <is>
@@ -8754,10 +8749,10 @@
         </is>
       </c>
       <c r="Z149">
-        <v>59.928755</v>
+        <v>59.92966</v>
       </c>
       <c r="AA149">
-        <v>30.281284</v>
+        <v>30.28401</v>
       </c>
     </row>
     <row r="150">
@@ -9343,17 +9338,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y7f5591</t>
+          <t xml:space="preserve">N1</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Склад</t>
+          <t xml:space="preserve">Караульный дом (северная проходная Нового Адмиралтейства)</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Склад</t>
+          <t xml:space="preserve">Историческое здание</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -9362,56 +9357,46 @@
         </is>
       </c>
       <c r="E160">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F160">
         <v>11.5</v>
       </c>
       <c r="G160">
-        <v>609</v>
-      </c>
-      <c r="H160">
-        <v>609</v>
+        <v>675</v>
+      </c>
+      <c r="H160" s="3">
+        <v>1350</v>
       </c>
       <c r="I160" s="3">
-        <v>6237</v>
+        <v>6411</v>
       </c>
       <c r="W160" t="inlineStr">
         <is>
           <t xml:space="preserve">Нет данных</t>
         </is>
       </c>
-      <c r="X160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">да</t>
-        </is>
-      </c>
-      <c r="Y160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OpenStreetMap</t>
-        </is>
-      </c>
       <c r="Z160">
-        <v>59.928677</v>
+        <v>59.930305</v>
       </c>
       <c r="AA160">
-        <v>30.275286</v>
+        <v>30.283372</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z164</t>
+          <t xml:space="preserve">Y7f5591</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вспомогательное здание</t>
+          <t xml:space="preserve">Склад</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вспомогательное здание</t>
+          <t xml:space="preserve">Склад</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -9420,19 +9405,19 @@
         </is>
       </c>
       <c r="E161">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F161">
-        <v>6.5</v>
+        <v>11.5</v>
       </c>
       <c r="G161">
-        <v>523</v>
-      </c>
-      <c r="H161" s="3">
-        <v>1045</v>
+        <v>609</v>
+      </c>
+      <c r="H161">
+        <v>609</v>
       </c>
       <c r="I161" s="3">
-        <v>3397</v>
+        <v>6237</v>
       </c>
       <c r="W161" t="inlineStr">
         <is>
@@ -9446,20 +9431,20 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z161">
-        <v>59.928301</v>
+        <v>59.928677</v>
       </c>
       <c r="AA161">
-        <v>30.279961</v>
+        <v>30.275286</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z138</t>
+          <t xml:space="preserve">Z164</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -9484,13 +9469,13 @@
         <v>6.5</v>
       </c>
       <c r="G162">
-        <v>455</v>
-      </c>
-      <c r="H162">
-        <v>911</v>
+        <v>523</v>
+      </c>
+      <c r="H162" s="3">
+        <v>1045</v>
       </c>
       <c r="I162" s="3">
-        <v>2960</v>
+        <v>3397</v>
       </c>
       <c r="W162" t="inlineStr">
         <is>
@@ -9508,16 +9493,16 @@
         </is>
       </c>
       <c r="Z162">
-        <v>59.927751</v>
+        <v>59.928301</v>
       </c>
       <c r="AA162">
-        <v>30.278334</v>
+        <v>30.279961</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z143</t>
+          <t xml:space="preserve">Z138</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -9542,13 +9527,13 @@
         <v>6.5</v>
       </c>
       <c r="G163">
-        <v>320</v>
+        <v>455</v>
       </c>
       <c r="H163">
-        <v>639</v>
+        <v>911</v>
       </c>
       <c r="I163" s="3">
-        <v>2078</v>
+        <v>2960</v>
       </c>
       <c r="W163" t="inlineStr">
         <is>
@@ -9562,30 +9547,30 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenStreetMap</t>
+          <t xml:space="preserve">карта предприятия</t>
         </is>
       </c>
       <c r="Z163">
-        <v>59.92917</v>
+        <v>59.927751</v>
       </c>
       <c r="AA163">
-        <v>30.27945</v>
+        <v>30.278334</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y40444c</t>
+          <t xml:space="preserve">Z143</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вспомогательное здание</t>
+          <t xml:space="preserve">Нарядный дом</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вспомогательное здание</t>
+          <t xml:space="preserve">Историческое здание</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -9597,43 +9582,38 @@
         <v>2</v>
       </c>
       <c r="F164">
-        <v>6.5</v>
+        <v>11.5</v>
       </c>
       <c r="G164">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="H164">
-        <v>612</v>
+        <v>639</v>
       </c>
       <c r="I164" s="3">
-        <v>1988</v>
+        <v>3037</v>
       </c>
       <c r="W164" t="inlineStr">
         <is>
           <t xml:space="preserve">Нет данных</t>
         </is>
       </c>
-      <c r="X164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">да</t>
-        </is>
-      </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Microsoft ML Buildings</t>
+          <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z164">
-        <v>59.931374</v>
+        <v>59.92917</v>
       </c>
       <c r="AA164">
-        <v>30.28092</v>
+        <v>30.27945</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z132</t>
+          <t xml:space="preserve">Y40444c</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -9658,13 +9638,13 @@
         <v>6.5</v>
       </c>
       <c r="G165">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="H165">
-        <v>590</v>
+        <v>612</v>
       </c>
       <c r="I165" s="3">
-        <v>1917</v>
+        <v>1988</v>
       </c>
       <c r="W165" t="inlineStr">
         <is>
@@ -9678,20 +9658,20 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenStreetMap</t>
+          <t xml:space="preserve">Microsoft ML Buildings</t>
         </is>
       </c>
       <c r="Z165">
-        <v>59.927484</v>
+        <v>59.931374</v>
       </c>
       <c r="AA165">
-        <v>30.277846</v>
+        <v>30.28092</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z194</t>
+          <t xml:space="preserve">Z132</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -9716,13 +9696,13 @@
         <v>6.5</v>
       </c>
       <c r="G166">
-        <v>244</v>
+        <v>295</v>
       </c>
       <c r="H166">
-        <v>487</v>
+        <v>590</v>
       </c>
       <c r="I166" s="3">
-        <v>1583</v>
+        <v>1917</v>
       </c>
       <c r="W166" t="inlineStr">
         <is>
@@ -9740,16 +9720,16 @@
         </is>
       </c>
       <c r="Z166">
-        <v>59.929165</v>
+        <v>59.927484</v>
       </c>
       <c r="AA166">
-        <v>30.28346</v>
+        <v>30.277846</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yd51e5a</t>
+          <t xml:space="preserve">Z194</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -9774,13 +9754,13 @@
         <v>6.5</v>
       </c>
       <c r="G167">
-        <v>217</v>
+        <v>244</v>
       </c>
       <c r="H167">
-        <v>435</v>
+        <v>487</v>
       </c>
       <c r="I167" s="3">
-        <v>1413</v>
+        <v>1583</v>
       </c>
       <c r="W167" t="inlineStr">
         <is>
@@ -9794,20 +9774,20 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Microsoft ML Buildings</t>
+          <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z167">
-        <v>59.931101</v>
+        <v>59.929165</v>
       </c>
       <c r="AA167">
-        <v>30.281054</v>
+        <v>30.28346</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z54</t>
+          <t xml:space="preserve">Yd51e5a</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -9832,13 +9812,13 @@
         <v>6.5</v>
       </c>
       <c r="G168">
-        <v>176</v>
+        <v>217</v>
       </c>
       <c r="H168">
-        <v>352</v>
+        <v>435</v>
       </c>
       <c r="I168" s="3">
-        <v>1145</v>
+        <v>1413</v>
       </c>
       <c r="W168" t="inlineStr">
         <is>
@@ -9852,20 +9832,20 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenStreetMap</t>
+          <t xml:space="preserve">Microsoft ML Buildings</t>
         </is>
       </c>
       <c r="Z168">
-        <v>59.928998</v>
+        <v>59.931101</v>
       </c>
       <c r="AA168">
-        <v>30.275845</v>
+        <v>30.281054</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yee9839</t>
+          <t xml:space="preserve">Z54</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -9890,13 +9870,13 @@
         <v>6.5</v>
       </c>
       <c r="G169">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="H169">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="I169" s="3">
-        <v>1122</v>
+        <v>1145</v>
       </c>
       <c r="W169" t="inlineStr">
         <is>
@@ -9914,16 +9894,16 @@
         </is>
       </c>
       <c r="Z169">
-        <v>59.931291</v>
+        <v>59.928998</v>
       </c>
       <c r="AA169">
-        <v>30.281862</v>
+        <v>30.275845</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y63e2a7</t>
+          <t xml:space="preserve">Yee9839</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -9948,13 +9928,13 @@
         <v>6.5</v>
       </c>
       <c r="G170">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H170">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I170" s="3">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="W170" t="inlineStr">
         <is>
@@ -9972,16 +9952,16 @@
         </is>
       </c>
       <c r="Z170">
-        <v>59.931268</v>
+        <v>59.931291</v>
       </c>
       <c r="AA170">
-        <v>30.280566</v>
+        <v>30.281862</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z176</t>
+          <t xml:space="preserve">Y63e2a7</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10006,13 +9986,13 @@
         <v>6.5</v>
       </c>
       <c r="G171">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="H171">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="I171" s="3">
-        <v>1092</v>
+        <v>1118</v>
       </c>
       <c r="W171" t="inlineStr">
         <is>
@@ -10026,20 +10006,20 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z171">
-        <v>59.928997</v>
+        <v>59.931268</v>
       </c>
       <c r="AA171">
-        <v>30.280813</v>
+        <v>30.280566</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z168</t>
+          <t xml:space="preserve">Z176</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10058,19 +10038,19 @@
         </is>
       </c>
       <c r="E172">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F172">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="G172">
-        <v>133</v>
+        <v>168</v>
       </c>
       <c r="H172">
-        <v>133</v>
-      </c>
-      <c r="I172">
-        <v>599</v>
+        <v>336</v>
+      </c>
+      <c r="I172" s="3">
+        <v>1092</v>
       </c>
       <c r="W172" t="inlineStr">
         <is>
@@ -10088,16 +10068,16 @@
         </is>
       </c>
       <c r="Z172">
-        <v>59.931321</v>
+        <v>59.928997</v>
       </c>
       <c r="AA172">
-        <v>30.281697</v>
+        <v>30.280813</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z73</t>
+          <t xml:space="preserve">Z168</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10122,13 +10102,13 @@
         <v>4.5</v>
       </c>
       <c r="G173">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="H173">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="I173">
-        <v>568</v>
+        <v>599</v>
       </c>
       <c r="W173" t="inlineStr">
         <is>
@@ -10146,16 +10126,16 @@
         </is>
       </c>
       <c r="Z173">
-        <v>59.927798</v>
+        <v>59.931321</v>
       </c>
       <c r="AA173">
-        <v>30.275726</v>
+        <v>30.281697</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ye7a1c8</t>
+          <t xml:space="preserve">Z73</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -10180,13 +10160,13 @@
         <v>4.5</v>
       </c>
       <c r="G174">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="H174">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="I174">
-        <v>533</v>
+        <v>568</v>
       </c>
       <c r="W174" t="inlineStr">
         <is>
@@ -10200,20 +10180,20 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Microsoft ML Buildings</t>
+          <t xml:space="preserve">карта предприятия</t>
         </is>
       </c>
       <c r="Z174">
-        <v>59.927463</v>
+        <v>59.927798</v>
       </c>
       <c r="AA174">
-        <v>30.274482</v>
+        <v>30.275726</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y821c91</t>
+          <t xml:space="preserve">Ye7a1c8</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -10238,13 +10218,13 @@
         <v>4.5</v>
       </c>
       <c r="G175">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="H175">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="I175">
-        <v>492</v>
+        <v>533</v>
       </c>
       <c r="W175" t="inlineStr">
         <is>
@@ -10262,16 +10242,16 @@
         </is>
       </c>
       <c r="Z175">
-        <v>59.931129</v>
+        <v>59.927463</v>
       </c>
       <c r="AA175">
-        <v>30.279272</v>
+        <v>30.274482</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y9d3494</t>
+          <t xml:space="preserve">Y821c91</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -10296,13 +10276,13 @@
         <v>4.5</v>
       </c>
       <c r="G176">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H176">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="I176">
-        <v>474</v>
+        <v>492</v>
       </c>
       <c r="W176" t="inlineStr">
         <is>
@@ -10320,16 +10300,16 @@
         </is>
       </c>
       <c r="Z176">
-        <v>59.931263</v>
+        <v>59.931129</v>
       </c>
       <c r="AA176">
-        <v>30.28082</v>
+        <v>30.279272</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z38</t>
+          <t xml:space="preserve">Y9d3494</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -10354,13 +10334,13 @@
         <v>4.5</v>
       </c>
       <c r="G177">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H177">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I177">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="W177" t="inlineStr">
         <is>
@@ -10374,20 +10354,20 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">Microsoft ML Buildings</t>
         </is>
       </c>
       <c r="Z177">
-        <v>59.927565</v>
+        <v>59.931263</v>
       </c>
       <c r="AA177">
-        <v>30.274461</v>
+        <v>30.28082</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y32ed76</t>
+          <t xml:space="preserve">Z38</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -10412,13 +10392,13 @@
         <v>4.5</v>
       </c>
       <c r="G178">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="H178">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="I178">
-        <v>439</v>
+        <v>462</v>
       </c>
       <c r="W178" t="inlineStr">
         <is>
@@ -10432,20 +10412,20 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Microsoft ML Buildings</t>
+          <t xml:space="preserve">карта предприятия</t>
         </is>
       </c>
       <c r="Z178">
-        <v>59.927248</v>
+        <v>59.927565</v>
       </c>
       <c r="AA178">
-        <v>30.274163</v>
+        <v>30.274461</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y1eac04</t>
+          <t xml:space="preserve">Y32ed76</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -10470,13 +10450,13 @@
         <v>4.5</v>
       </c>
       <c r="G179">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="H179">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="I179">
-        <v>385</v>
+        <v>439</v>
       </c>
       <c r="W179" t="inlineStr">
         <is>
@@ -10490,20 +10470,20 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenStreetMap</t>
+          <t xml:space="preserve">Microsoft ML Buildings</t>
         </is>
       </c>
       <c r="Z179">
-        <v>59.929342</v>
+        <v>59.927248</v>
       </c>
       <c r="AA179">
-        <v>30.27777</v>
+        <v>30.274163</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z35</t>
+          <t xml:space="preserve">Y1eac04</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -10528,13 +10508,13 @@
         <v>4.5</v>
       </c>
       <c r="G180">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="H180">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I180">
-        <v>365</v>
+        <v>385</v>
       </c>
       <c r="W180" t="inlineStr">
         <is>
@@ -10548,20 +10528,20 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Microsoft ML Buildings</t>
+          <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z180">
-        <v>59.927337</v>
+        <v>59.929342</v>
       </c>
       <c r="AA180">
-        <v>30.274198</v>
+        <v>30.27777</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y013ff0</t>
+          <t xml:space="preserve">Z35</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -10586,13 +10566,13 @@
         <v>4.5</v>
       </c>
       <c r="G181">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H181">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I181">
-        <v>339</v>
+        <v>365</v>
       </c>
       <c r="W181" t="inlineStr">
         <is>
@@ -10610,16 +10590,16 @@
         </is>
       </c>
       <c r="Z181">
-        <v>59.930367</v>
+        <v>59.927337</v>
       </c>
       <c r="AA181">
-        <v>30.277882</v>
+        <v>30.274198</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y5ff43a</t>
+          <t xml:space="preserve">Y013ff0</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -10644,13 +10624,13 @@
         <v>4.5</v>
       </c>
       <c r="G182">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H182">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I182">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="W182" t="inlineStr">
         <is>
@@ -10664,20 +10644,20 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenStreetMap</t>
+          <t xml:space="preserve">Microsoft ML Buildings</t>
         </is>
       </c>
       <c r="Z182">
-        <v>59.927253</v>
+        <v>59.930367</v>
       </c>
       <c r="AA182">
-        <v>30.277517</v>
+        <v>30.277882</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y2e3bc5</t>
+          <t xml:space="preserve">Y5ff43a</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -10702,13 +10682,13 @@
         <v>4.5</v>
       </c>
       <c r="G183">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H183">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I183">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="W183" t="inlineStr">
         <is>
@@ -10722,20 +10702,20 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Microsoft ML Buildings</t>
+          <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z183">
-        <v>59.930654</v>
+        <v>59.927253</v>
       </c>
       <c r="AA183">
-        <v>30.279134</v>
+        <v>30.277517</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z180</t>
+          <t xml:space="preserve">Y2e3bc5</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -10760,13 +10740,13 @@
         <v>4.5</v>
       </c>
       <c r="G184">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H184">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I184">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="W184" t="inlineStr">
         <is>
@@ -10780,20 +10760,20 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">Microsoft ML Buildings</t>
         </is>
       </c>
       <c r="Z184">
-        <v>59.9303</v>
+        <v>59.930654</v>
       </c>
       <c r="AA184">
-        <v>30.281996</v>
+        <v>30.279134</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z179</t>
+          <t xml:space="preserve">Z180</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -10818,13 +10798,13 @@
         <v>4.5</v>
       </c>
       <c r="G185">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="H185">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="I185">
-        <v>264</v>
+        <v>304</v>
       </c>
       <c r="W185" t="inlineStr">
         <is>
@@ -10842,16 +10822,16 @@
         </is>
       </c>
       <c r="Z185">
-        <v>59.929976</v>
+        <v>59.9303</v>
       </c>
       <c r="AA185">
-        <v>30.281601</v>
+        <v>30.281996</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z145</t>
+          <t xml:space="preserve">Z179</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -10882,7 +10862,7 @@
         <v>59</v>
       </c>
       <c r="I186">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="W186" t="inlineStr">
         <is>
@@ -10900,16 +10880,16 @@
         </is>
       </c>
       <c r="Z186">
-        <v>59.931283</v>
+        <v>59.929976</v>
       </c>
       <c r="AA186">
-        <v>30.280404</v>
+        <v>30.281601</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y45217a</t>
+          <t xml:space="preserve">Z145</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -10934,13 +10914,13 @@
         <v>4.5</v>
       </c>
       <c r="G187">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H187">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I187">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="W187" t="inlineStr">
         <is>
@@ -10954,20 +10934,20 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Microsoft ML Buildings</t>
+          <t xml:space="preserve">карта предприятия</t>
         </is>
       </c>
       <c r="Z187">
-        <v>59.93094</v>
+        <v>59.931283</v>
       </c>
       <c r="AA187">
-        <v>30.279824</v>
+        <v>30.280404</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y1eed6a</t>
+          <t xml:space="preserve">Y45217a</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -10992,13 +10972,13 @@
         <v>4.5</v>
       </c>
       <c r="G188">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H188">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I188">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="W188" t="inlineStr">
         <is>
@@ -11016,16 +10996,16 @@
         </is>
       </c>
       <c r="Z188">
-        <v>59.927372</v>
+        <v>59.93094</v>
       </c>
       <c r="AA188">
-        <v>30.274017</v>
+        <v>30.279824</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y00020a</t>
+          <t xml:space="preserve">Y1eed6a</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11050,13 +11030,13 @@
         <v>4.5</v>
       </c>
       <c r="G189">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H189">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I189">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="W189" t="inlineStr">
         <is>
@@ -11074,16 +11054,16 @@
         </is>
       </c>
       <c r="Z189">
-        <v>59.9299</v>
+        <v>59.927372</v>
       </c>
       <c r="AA189">
-        <v>30.277187</v>
+        <v>30.274017</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z39</t>
+          <t xml:space="preserve">Y00020a</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -11108,13 +11088,13 @@
         <v>4.5</v>
       </c>
       <c r="G190">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H190">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I190">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="W190" t="inlineStr">
         <is>
@@ -11128,20 +11108,20 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">Microsoft ML Buildings</t>
         </is>
       </c>
       <c r="Z190">
-        <v>59.92776</v>
+        <v>59.9299</v>
       </c>
       <c r="AA190">
-        <v>30.27456</v>
+        <v>30.277187</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yf6b127</t>
+          <t xml:space="preserve">Z39</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -11166,13 +11146,13 @@
         <v>4.5</v>
       </c>
       <c r="G191">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H191">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I191">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="W191" t="inlineStr">
         <is>
@@ -11186,20 +11166,20 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Microsoft ML Buildings</t>
+          <t xml:space="preserve">карта предприятия</t>
         </is>
       </c>
       <c r="Z191">
-        <v>59.927513</v>
+        <v>59.92776</v>
       </c>
       <c r="AA191">
-        <v>30.274199</v>
+        <v>30.27456</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z186</t>
+          <t xml:space="preserve">Yf6b127</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -11224,13 +11204,13 @@
         <v>4.5</v>
       </c>
       <c r="G192">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H192">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I192">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="W192" t="inlineStr">
         <is>
@@ -11244,20 +11224,20 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">Microsoft ML Buildings</t>
         </is>
       </c>
       <c r="Z192">
-        <v>59.929199</v>
+        <v>59.927513</v>
       </c>
       <c r="AA192">
-        <v>30.282395</v>
+        <v>30.274199</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y70d9c2</t>
+          <t xml:space="preserve">Z186</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -11282,13 +11262,13 @@
         <v>4.5</v>
       </c>
       <c r="G193">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H193">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I193">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="W193" t="inlineStr">
         <is>
@@ -11302,20 +11282,20 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Microsoft ML Buildings</t>
+          <t xml:space="preserve">карта предприятия</t>
         </is>
       </c>
       <c r="Z193">
-        <v>59.926545</v>
+        <v>59.929199</v>
       </c>
       <c r="AA193">
-        <v>30.273651</v>
+        <v>30.282395</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y2b5f78</t>
+          <t xml:space="preserve">Y70d9c2</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -11340,13 +11320,13 @@
         <v>4.5</v>
       </c>
       <c r="G194">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="H194">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="I194">
-        <v>153</v>
+        <v>188</v>
       </c>
       <c r="W194" t="inlineStr">
         <is>
@@ -11364,16 +11344,16 @@
         </is>
       </c>
       <c r="Z194">
-        <v>59.926463</v>
+        <v>59.926545</v>
       </c>
       <c r="AA194">
-        <v>30.27353</v>
+        <v>30.273651</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y3254f1</t>
+          <t xml:space="preserve">Y2b5f78</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -11398,13 +11378,13 @@
         <v>4.5</v>
       </c>
       <c r="G195">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H195">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I195">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="W195" t="inlineStr">
         <is>
@@ -11422,16 +11402,16 @@
         </is>
       </c>
       <c r="Z195">
-        <v>59.929433</v>
+        <v>59.926463</v>
       </c>
       <c r="AA195">
-        <v>30.283111</v>
+        <v>30.27353</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y6aa9c4</t>
+          <t xml:space="preserve">Y3254f1</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -11456,13 +11436,13 @@
         <v>4.5</v>
       </c>
       <c r="G196">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H196">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I196">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="W196" t="inlineStr">
         <is>
@@ -11480,16 +11460,16 @@
         </is>
       </c>
       <c r="Z196">
-        <v>59.930793</v>
+        <v>59.929433</v>
       </c>
       <c r="AA196">
-        <v>30.279774</v>
+        <v>30.283111</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y31a1ee</t>
+          <t xml:space="preserve">Y6aa9c4</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -11514,13 +11494,13 @@
         <v>4.5</v>
       </c>
       <c r="G197">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H197">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I197">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="W197" t="inlineStr">
         <is>
@@ -11538,16 +11518,16 @@
         </is>
       </c>
       <c r="Z197">
-        <v>59.930609</v>
+        <v>59.930793</v>
       </c>
       <c r="AA197">
-        <v>30.278754</v>
+        <v>30.279774</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z114</t>
+          <t xml:space="preserve">Y31a1ee</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -11572,13 +11552,13 @@
         <v>4.5</v>
       </c>
       <c r="G198">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H198">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I198">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="W198" t="inlineStr">
         <is>
@@ -11596,16 +11576,16 @@
         </is>
       </c>
       <c r="Z198">
-        <v>59.930346</v>
+        <v>59.930609</v>
       </c>
       <c r="AA198">
-        <v>30.278646</v>
+        <v>30.278754</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y35768c</t>
+          <t xml:space="preserve">Z114</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -11654,16 +11634,16 @@
         </is>
       </c>
       <c r="Z199">
-        <v>59.929346</v>
+        <v>59.930346</v>
       </c>
       <c r="AA199">
-        <v>30.283104</v>
+        <v>30.278646</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y17f85d</t>
+          <t xml:space="preserve">Y35768c</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -11688,13 +11668,13 @@
         <v>4.5</v>
       </c>
       <c r="G200">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H200">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I200">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="W200" t="inlineStr">
         <is>
@@ -11712,16 +11692,16 @@
         </is>
       </c>
       <c r="Z200">
-        <v>59.929555</v>
+        <v>59.929346</v>
       </c>
       <c r="AA200">
-        <v>30.277708</v>
+        <v>30.283104</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yb278e2</t>
+          <t xml:space="preserve">Y17f85d</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -11746,13 +11726,13 @@
         <v>4.5</v>
       </c>
       <c r="G201">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H201">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I201">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="W201" t="inlineStr">
         <is>
@@ -11770,16 +11750,16 @@
         </is>
       </c>
       <c r="Z201">
-        <v>59.928919</v>
+        <v>59.929555</v>
       </c>
       <c r="AA201">
-        <v>30.275464</v>
+        <v>30.277708</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y8f6c14</t>
+          <t xml:space="preserve">Yb278e2</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -11804,13 +11784,13 @@
         <v>4.5</v>
       </c>
       <c r="G202">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H202">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I202">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="W202" t="inlineStr">
         <is>
@@ -11828,16 +11808,16 @@
         </is>
       </c>
       <c r="Z202">
-        <v>59.926942</v>
+        <v>59.928919</v>
       </c>
       <c r="AA202">
-        <v>30.274894</v>
+        <v>30.275464</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ya4af4b</t>
+          <t xml:space="preserve">Y8f6c14</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -11862,13 +11842,13 @@
         <v>4.5</v>
       </c>
       <c r="G203">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H203">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I203">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="W203" t="inlineStr">
         <is>
@@ -11886,16 +11866,16 @@
         </is>
       </c>
       <c r="Z203">
-        <v>59.926928</v>
+        <v>59.926942</v>
       </c>
       <c r="AA203">
-        <v>30.273747</v>
+        <v>30.274894</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y7c2cff</t>
+          <t xml:space="preserve">Ya4af4b</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -11926,7 +11906,7 @@
         <v>16</v>
       </c>
       <c r="I204">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="W204" t="inlineStr">
         <is>
@@ -11944,16 +11924,16 @@
         </is>
       </c>
       <c r="Z204">
-        <v>59.929309</v>
+        <v>59.926928</v>
       </c>
       <c r="AA204">
-        <v>30.28263</v>
+        <v>30.273747</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y5502d7</t>
+          <t xml:space="preserve">Y7c2cff</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -11978,13 +11958,13 @@
         <v>4.5</v>
       </c>
       <c r="G205">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H205">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I205">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="W205" t="inlineStr">
         <is>
@@ -12002,16 +11982,16 @@
         </is>
       </c>
       <c r="Z205">
-        <v>59.930009</v>
+        <v>59.929309</v>
       </c>
       <c r="AA205">
-        <v>30.281978</v>
+        <v>30.28263</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y5fba1f</t>
+          <t xml:space="preserve">Y5502d7</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12036,13 +12016,13 @@
         <v>4.5</v>
       </c>
       <c r="G206">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H206">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I206">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="W206" t="inlineStr">
         <is>
@@ -12060,16 +12040,16 @@
         </is>
       </c>
       <c r="Z206">
-        <v>59.926643</v>
+        <v>59.930009</v>
       </c>
       <c r="AA206">
-        <v>30.275014</v>
+        <v>30.281978</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y1c5f7d</t>
+          <t xml:space="preserve">Y5fba1f</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -12094,13 +12074,13 @@
         <v>4.5</v>
       </c>
       <c r="G207">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H207">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I207">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="W207" t="inlineStr">
         <is>
@@ -12118,16 +12098,16 @@
         </is>
       </c>
       <c r="Z207">
-        <v>59.928895</v>
+        <v>59.926643</v>
       </c>
       <c r="AA207">
-        <v>30.279488</v>
+        <v>30.275014</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y1c2cdb</t>
+          <t xml:space="preserve">Y1c5f7d</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -12176,74 +12156,79 @@
         </is>
       </c>
       <c r="Z208">
-        <v>59.928832</v>
+        <v>59.928895</v>
       </c>
       <c r="AA208">
-        <v>30.280536</v>
+        <v>30.279488</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z58</t>
+          <t xml:space="preserve">Y1c2cdb</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сборочно-сварочный цех</t>
+          <t xml:space="preserve">Вспомогательное здание</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Производственный корпус</t>
+          <t xml:space="preserve">Вспомогательное здание</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Основная площадка</t>
+          <t xml:space="preserve">Ново-Адмиралтейский остров</t>
         </is>
       </c>
       <c r="E209">
         <v>1</v>
       </c>
       <c r="F209">
-        <v>26</v>
-      </c>
-      <c r="G209" s="3">
-        <v>11603</v>
-      </c>
-      <c r="H209" s="3">
-        <v>11603</v>
-      </c>
-      <c r="I209" s="3">
-        <v>301688</v>
+        <v>4.5</v>
+      </c>
+      <c r="G209">
+        <v>10</v>
+      </c>
+      <c r="H209">
+        <v>10</v>
+      </c>
+      <c r="I209">
+        <v>46</v>
       </c>
       <c r="W209" t="inlineStr">
         <is>
           <t xml:space="preserve">Нет данных</t>
         </is>
       </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">Microsoft ML Buildings</t>
         </is>
       </c>
       <c r="Z209">
-        <v>59.919854</v>
+        <v>59.928832</v>
       </c>
       <c r="AA209">
-        <v>30.271808</v>
+        <v>30.280536</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z129</t>
+          <t xml:space="preserve">Z58</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Корпусосборочный цех (предстапельная сборка)</t>
+          <t xml:space="preserve">Сборочно-сварочный цех</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -12263,13 +12248,13 @@
         <v>26</v>
       </c>
       <c r="G210" s="3">
-        <v>9566</v>
+        <v>11603</v>
       </c>
       <c r="H210" s="3">
-        <v>9566</v>
+        <v>11603</v>
       </c>
       <c r="I210" s="3">
-        <v>248720</v>
+        <v>301688</v>
       </c>
       <c r="W210" t="inlineStr">
         <is>
@@ -12282,21 +12267,21 @@
         </is>
       </c>
       <c r="Z210">
-        <v>59.916875</v>
+        <v>59.919854</v>
       </c>
       <c r="AA210">
-        <v>30.271936</v>
+        <v>30.271808</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z23</t>
+          <t xml:space="preserve">Z129</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Цех достройки у ковша</t>
+          <t xml:space="preserve">Главная судостроительная мастерская с кузницей</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -12313,16 +12298,16 @@
         <v>1</v>
       </c>
       <c r="F211">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G211" s="3">
-        <v>6501</v>
+        <v>9566</v>
       </c>
       <c r="H211" s="3">
-        <v>6501</v>
+        <v>9566</v>
       </c>
       <c r="I211" s="3">
-        <v>104010</v>
+        <v>248720</v>
       </c>
       <c r="W211" t="inlineStr">
         <is>
@@ -12335,21 +12320,21 @@
         </is>
       </c>
       <c r="Z211">
-        <v>59.918807</v>
+        <v>59.916875</v>
       </c>
       <c r="AA211">
-        <v>30.27121</v>
+        <v>30.271936</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z14</t>
+          <t xml:space="preserve">Z23</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Корпусообрабатывающий цех</t>
+          <t xml:space="preserve">Цех вдоль ковша (лит. Д)</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -12363,19 +12348,19 @@
         </is>
       </c>
       <c r="E212">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F212">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G212" s="3">
-        <v>6098</v>
+        <v>6501</v>
       </c>
       <c r="H212" s="3">
-        <v>6098</v>
+        <v>13001</v>
       </c>
       <c r="I212" s="3">
-        <v>121968</v>
+        <v>84508</v>
       </c>
       <c r="W212" t="inlineStr">
         <is>
@@ -12388,21 +12373,21 @@
         </is>
       </c>
       <c r="Z212">
-        <v>59.916616</v>
+        <v>59.918807</v>
       </c>
       <c r="AA212">
-        <v>30.26734</v>
+        <v>30.27121</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z55</t>
+          <t xml:space="preserve">Z14</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Механосборочный цех</t>
+          <t xml:space="preserve">Корпусообрабатывающий цех</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -12419,16 +12404,16 @@
         <v>1</v>
       </c>
       <c r="F213">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G213" s="3">
-        <v>4122</v>
+        <v>6098</v>
       </c>
       <c r="H213" s="3">
-        <v>4122</v>
+        <v>6098</v>
       </c>
       <c r="I213" s="3">
-        <v>65951</v>
+        <v>121968</v>
       </c>
       <c r="W213" t="inlineStr">
         <is>
@@ -12441,21 +12426,21 @@
         </is>
       </c>
       <c r="Z213">
-        <v>59.916324</v>
+        <v>59.916616</v>
       </c>
       <c r="AA213">
-        <v>30.268739</v>
+        <v>30.26734</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z154</t>
+          <t xml:space="preserve">Z55</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Трубомедницкий цех</t>
+          <t xml:space="preserve">Механосборочный цех</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -12472,16 +12457,16 @@
         <v>1</v>
       </c>
       <c r="F214">
-        <v>19.6</v>
+        <v>16</v>
       </c>
       <c r="G214" s="3">
-        <v>4037</v>
+        <v>4122</v>
       </c>
       <c r="H214" s="3">
-        <v>4037</v>
+        <v>4122</v>
       </c>
       <c r="I214" s="3">
-        <v>67722</v>
+        <v>65951</v>
       </c>
       <c r="W214" t="inlineStr">
         <is>
@@ -12494,21 +12479,21 @@
         </is>
       </c>
       <c r="Z214">
-        <v>59.916595</v>
+        <v>59.916324</v>
       </c>
       <c r="AA214">
-        <v>30.273731</v>
+        <v>30.268739</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z52</t>
+          <t xml:space="preserve">Z154</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Цех металлоконструкций</t>
+          <t xml:space="preserve">Разбивочный плаз</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -12522,56 +12507,51 @@
         </is>
       </c>
       <c r="E215">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F215">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G215" s="3">
-        <v>3395</v>
+        <v>4037</v>
       </c>
       <c r="H215" s="3">
-        <v>3395</v>
+        <v>12111</v>
       </c>
       <c r="I215" s="3">
-        <v>67890</v>
+        <v>68628</v>
       </c>
       <c r="W215" t="inlineStr">
         <is>
           <t xml:space="preserve">Нет данных</t>
         </is>
       </c>
-      <c r="X215" t="inlineStr">
-        <is>
-          <t xml:space="preserve">да</t>
-        </is>
-      </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenStreetMap</t>
+          <t xml:space="preserve">карта предприятия</t>
         </is>
       </c>
       <c r="Z215">
-        <v>59.920687</v>
+        <v>59.916595</v>
       </c>
       <c r="AA215">
-        <v>30.271827</v>
+        <v>30.273731</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z182</t>
+          <t xml:space="preserve">Z52</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Заводоуправление</t>
+          <t xml:space="preserve">Цех металлоконструкций</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Административно-бытовой корпус</t>
+          <t xml:space="preserve">Производственный корпус</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -12580,51 +12560,56 @@
         </is>
       </c>
       <c r="E216">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F216">
-        <v>17.6</v>
+        <v>20</v>
       </c>
       <c r="G216" s="3">
-        <v>3375</v>
+        <v>3395</v>
       </c>
       <c r="H216" s="3">
-        <v>16876</v>
+        <v>3395</v>
       </c>
       <c r="I216" s="3">
-        <v>59404</v>
+        <v>67890</v>
       </c>
       <c r="W216" t="inlineStr">
         <is>
           <t xml:space="preserve">Нет данных</t>
         </is>
       </c>
+      <c r="X216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
       <c r="Y216" t="inlineStr">
         <is>
           <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z216">
-        <v>59.918162</v>
+        <v>59.920687</v>
       </c>
       <c r="AA216">
-        <v>30.276503</v>
+        <v>30.271827</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z181</t>
+          <t xml:space="preserve">Z182</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Цех</t>
+          <t xml:space="preserve">Заводоуправление</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Производственный корпус</t>
+          <t xml:space="preserve">Административно-бытовой корпус</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -12633,56 +12618,51 @@
         </is>
       </c>
       <c r="E217">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F217">
-        <v>23.8</v>
+        <v>17.6</v>
       </c>
       <c r="G217" s="3">
-        <v>2204</v>
+        <v>3375</v>
       </c>
       <c r="H217" s="3">
-        <v>2204</v>
+        <v>16876</v>
       </c>
       <c r="I217" s="3">
-        <v>52458</v>
+        <v>59404</v>
       </c>
       <c r="W217" t="inlineStr">
         <is>
           <t xml:space="preserve">Нет данных</t>
         </is>
       </c>
-      <c r="X217" t="inlineStr">
-        <is>
-          <t xml:space="preserve">да</t>
-        </is>
-      </c>
       <c r="Y217" t="inlineStr">
         <is>
           <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z217">
-        <v>59.916923</v>
+        <v>59.918162</v>
       </c>
       <c r="AA217">
-        <v>30.274636</v>
+        <v>30.276503</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z155</t>
+          <t xml:space="preserve">Z181</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Инженерный корпус</t>
+          <t xml:space="preserve">Главная электрическая станция</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Административно-бытовой корпус</t>
+          <t xml:space="preserve">Производственный корпус</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -12691,56 +12671,51 @@
         </is>
       </c>
       <c r="E218">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F218">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G218" s="3">
-        <v>2122</v>
+        <v>2204</v>
       </c>
       <c r="H218" s="3">
-        <v>8487</v>
+        <v>4408</v>
       </c>
       <c r="I218" s="3">
-        <v>31824</v>
+        <v>30858</v>
       </c>
       <c r="W218" t="inlineStr">
         <is>
           <t xml:space="preserve">Нет данных</t>
         </is>
       </c>
-      <c r="X218" t="inlineStr">
-        <is>
-          <t xml:space="preserve">да</t>
-        </is>
-      </c>
       <c r="Y218" t="inlineStr">
         <is>
           <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z218">
-        <v>59.91856</v>
+        <v>59.916923</v>
       </c>
       <c r="AA218">
-        <v>30.27438</v>
+        <v>30.274636</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z108</t>
+          <t xml:space="preserve">Z155</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Цех</t>
+          <t xml:space="preserve">Инженерный корпус</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Производственный корпус</t>
+          <t xml:space="preserve">Административно-бытовой корпус</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -12749,19 +12724,19 @@
         </is>
       </c>
       <c r="E219">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F219">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G219" s="3">
-        <v>1864</v>
+        <v>2122</v>
       </c>
       <c r="H219" s="3">
-        <v>1864</v>
+        <v>8487</v>
       </c>
       <c r="I219" s="3">
-        <v>26099</v>
+        <v>31824</v>
       </c>
       <c r="W219" t="inlineStr">
         <is>
@@ -12775,30 +12750,30 @@
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z219">
-        <v>59.916421</v>
+        <v>59.91856</v>
       </c>
       <c r="AA219">
-        <v>30.270523</v>
+        <v>30.27438</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z162</t>
+          <t xml:space="preserve">Z108</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Административный корпус</t>
+          <t xml:space="preserve">Цех</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Административно-бытовой корпус</t>
+          <t xml:space="preserve">Производственный корпус</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -12807,19 +12782,19 @@
         </is>
       </c>
       <c r="E220">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F220">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G220" s="3">
-        <v>1851</v>
+        <v>1864</v>
       </c>
       <c r="H220" s="3">
-        <v>7404</v>
+        <v>1864</v>
       </c>
       <c r="I220" s="3">
-        <v>27764</v>
+        <v>26099</v>
       </c>
       <c r="W220" t="inlineStr">
         <is>
@@ -12833,30 +12808,30 @@
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenStreetMap</t>
+          <t xml:space="preserve">карта предприятия</t>
         </is>
       </c>
       <c r="Z220">
-        <v>59.919241</v>
+        <v>59.916421</v>
       </c>
       <c r="AA220">
-        <v>30.274757</v>
+        <v>30.270523</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z11</t>
+          <t xml:space="preserve">Z162</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Цех</t>
+          <t xml:space="preserve">Административный корпус</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Производственный корпус</t>
+          <t xml:space="preserve">Административно-бытовой корпус</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -12865,19 +12840,19 @@
         </is>
       </c>
       <c r="E221">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F221">
-        <v>29.8</v>
+        <v>15</v>
       </c>
       <c r="G221" s="3">
-        <v>1703</v>
+        <v>1851</v>
       </c>
       <c r="H221" s="3">
-        <v>1703</v>
+        <v>7404</v>
       </c>
       <c r="I221" s="3">
-        <v>45394</v>
+        <v>27764</v>
       </c>
       <c r="W221" t="inlineStr">
         <is>
@@ -12895,21 +12870,21 @@
         </is>
       </c>
       <c r="Z221">
-        <v>59.91687</v>
+        <v>59.919241</v>
       </c>
       <c r="AA221">
-        <v>30.266039</v>
+        <v>30.274757</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y47f4ff</t>
+          <t xml:space="preserve">Z11</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Адмиралтейская</t>
+          <t xml:space="preserve">Цех</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -12926,16 +12901,16 @@
         <v>1</v>
       </c>
       <c r="F222">
-        <v>21.2</v>
+        <v>29.8</v>
       </c>
       <c r="G222" s="3">
-        <v>1451</v>
+        <v>1703</v>
       </c>
       <c r="H222" s="3">
-        <v>1451</v>
+        <v>1703</v>
       </c>
       <c r="I222" s="3">
-        <v>30771</v>
+        <v>45394</v>
       </c>
       <c r="W222" t="inlineStr">
         <is>
@@ -12953,26 +12928,26 @@
         </is>
       </c>
       <c r="Z222">
-        <v>59.920131</v>
+        <v>59.91687</v>
       </c>
       <c r="AA222">
-        <v>30.275259</v>
+        <v>30.266039</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z197</t>
+          <t xml:space="preserve">Y47f4ff</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Административно-бытовой корпус</t>
+          <t xml:space="preserve">Адмиралтейская</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Административно-бытовой корпус</t>
+          <t xml:space="preserve">Производственный корпус</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -12981,19 +12956,19 @@
         </is>
       </c>
       <c r="E223">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F223">
-        <v>15</v>
+        <v>21.2</v>
       </c>
       <c r="G223" s="3">
-        <v>1335</v>
+        <v>1451</v>
       </c>
       <c r="H223" s="3">
-        <v>5341</v>
+        <v>1451</v>
       </c>
       <c r="I223" s="3">
-        <v>20029</v>
+        <v>30771</v>
       </c>
       <c r="W223" t="inlineStr">
         <is>
@@ -13011,26 +12986,26 @@
         </is>
       </c>
       <c r="Z223">
-        <v>59.916375</v>
+        <v>59.920131</v>
       </c>
       <c r="AA223">
-        <v>30.276311</v>
+        <v>30.275259</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z115</t>
+          <t xml:space="preserve">Z197</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Цех</t>
+          <t xml:space="preserve">Административный корпус у Фонтанки</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Производственный корпус</t>
+          <t xml:space="preserve">Административно-бытовой корпус</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -13039,19 +13014,19 @@
         </is>
       </c>
       <c r="E224">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F224">
-        <v>20.3</v>
+        <v>18.5</v>
       </c>
       <c r="G224" s="3">
-        <v>1203</v>
+        <v>1335</v>
       </c>
       <c r="H224" s="3">
-        <v>1203</v>
+        <v>3864</v>
       </c>
       <c r="I224" s="3">
-        <v>24427</v>
+        <v>17069</v>
       </c>
       <c r="W224" t="inlineStr">
         <is>
@@ -13069,26 +13044,26 @@
         </is>
       </c>
       <c r="Z224">
-        <v>59.916881</v>
+        <v>59.916375</v>
       </c>
       <c r="AA224">
-        <v>30.270821</v>
+        <v>30.276311</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z165</t>
+          <t xml:space="preserve">Z115</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Административно-бытовой корпус</t>
+          <t xml:space="preserve">Цех</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Административно-бытовой корпус</t>
+          <t xml:space="preserve">Производственный корпус</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -13097,19 +13072,19 @@
         </is>
       </c>
       <c r="E225">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F225">
-        <v>12</v>
+        <v>20.3</v>
       </c>
       <c r="G225" s="3">
-        <v>1199</v>
+        <v>1203</v>
       </c>
       <c r="H225" s="3">
-        <v>3597</v>
+        <v>1203</v>
       </c>
       <c r="I225" s="3">
-        <v>14387</v>
+        <v>24427</v>
       </c>
       <c r="W225" t="inlineStr">
         <is>
@@ -13127,26 +13102,26 @@
         </is>
       </c>
       <c r="Z225">
-        <v>59.917093</v>
+        <v>59.916881</v>
       </c>
       <c r="AA225">
-        <v>30.273341</v>
+        <v>30.270821</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z110</t>
+          <t xml:space="preserve">Z165</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Административно-бытовой корпус</t>
+          <t xml:space="preserve">Производственный корпус (лит. Ж)</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Административно-бытовой корпус</t>
+          <t xml:space="preserve">Историческое здание</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -13155,56 +13130,51 @@
         </is>
       </c>
       <c r="E226">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F226">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="G226" s="3">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="H226" s="3">
-        <v>3595</v>
+        <v>2398</v>
       </c>
       <c r="I226" s="3">
-        <v>14380</v>
+        <v>12888</v>
       </c>
       <c r="W226" t="inlineStr">
         <is>
           <t xml:space="preserve">Нет данных</t>
         </is>
       </c>
-      <c r="X226" t="inlineStr">
-        <is>
-          <t xml:space="preserve">да</t>
-        </is>
-      </c>
       <c r="Y226" t="inlineStr">
         <is>
           <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z226">
-        <v>59.920653</v>
+        <v>59.917093</v>
       </c>
       <c r="AA226">
-        <v>30.273124</v>
+        <v>30.273341</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z7</t>
+          <t xml:space="preserve">Z110</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Склад</t>
+          <t xml:space="preserve">Административно-бытовой корпус</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Склад</t>
+          <t xml:space="preserve">Административно-бытовой корпус</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -13213,19 +13183,19 @@
         </is>
       </c>
       <c r="E227">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F227">
-        <v>12.6</v>
-      </c>
-      <c r="G227">
-        <v>948</v>
-      </c>
-      <c r="H227">
-        <v>948</v>
+        <v>12</v>
+      </c>
+      <c r="G227" s="3">
+        <v>1198</v>
+      </c>
+      <c r="H227" s="3">
+        <v>3595</v>
       </c>
       <c r="I227" s="3">
-        <v>10222</v>
+        <v>14380</v>
       </c>
       <c r="W227" t="inlineStr">
         <is>
@@ -13243,26 +13213,26 @@
         </is>
       </c>
       <c r="Z227">
-        <v>59.916973</v>
+        <v>59.920653</v>
       </c>
       <c r="AA227">
-        <v>30.265413</v>
+        <v>30.273124</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z67</t>
+          <t xml:space="preserve">Z7</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Административно-бытовой корпус</t>
+          <t xml:space="preserve">Склад</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Административно-бытовой корпус</t>
+          <t xml:space="preserve">Склад</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -13271,19 +13241,19 @@
         </is>
       </c>
       <c r="E228">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F228">
-        <v>12</v>
+        <v>12.6</v>
       </c>
       <c r="G228">
-        <v>882</v>
-      </c>
-      <c r="H228" s="3">
-        <v>2646</v>
+        <v>948</v>
+      </c>
+      <c r="H228">
+        <v>948</v>
       </c>
       <c r="I228" s="3">
-        <v>10585</v>
+        <v>10222</v>
       </c>
       <c r="W228" t="inlineStr">
         <is>
@@ -13297,30 +13267,30 @@
       </c>
       <c r="Y228" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z228">
-        <v>59.920346</v>
+        <v>59.916973</v>
       </c>
       <c r="AA228">
-        <v>30.271233</v>
+        <v>30.265413</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z199</t>
+          <t xml:space="preserve">Z67</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Центральная проходная АО «Адмиралтейские верфи»</t>
+          <t xml:space="preserve">Административно-бытовой корпус</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Проходная, КПП</t>
+          <t xml:space="preserve">Административно-бытовой корпус</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -13329,19 +13299,19 @@
         </is>
       </c>
       <c r="E229">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F229">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G229">
-        <v>864</v>
+        <v>882</v>
       </c>
       <c r="H229" s="3">
-        <v>1729</v>
+        <v>2646</v>
       </c>
       <c r="I229" s="3">
-        <v>6915</v>
+        <v>10585</v>
       </c>
       <c r="W229" t="inlineStr">
         <is>
@@ -13355,30 +13325,30 @@
       </c>
       <c r="Y229" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenStreetMap</t>
+          <t xml:space="preserve">карта предприятия</t>
         </is>
       </c>
       <c r="Z229">
-        <v>59.917265</v>
+        <v>59.920346</v>
       </c>
       <c r="AA229">
-        <v>30.277625</v>
+        <v>30.271233</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z141</t>
+          <t xml:space="preserve">Z199</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Административно-бытовой корпус</t>
+          <t xml:space="preserve">Центральная проходная АО «Адмиралтейские верфи»</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Административно-бытовой корпус</t>
+          <t xml:space="preserve">Проходная, КПП</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -13387,19 +13357,19 @@
         </is>
       </c>
       <c r="E230">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F230">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G230">
-        <v>810</v>
+        <v>864</v>
       </c>
       <c r="H230" s="3">
-        <v>2429</v>
+        <v>1729</v>
       </c>
       <c r="I230" s="3">
-        <v>9718</v>
+        <v>6915</v>
       </c>
       <c r="W230" t="inlineStr">
         <is>
@@ -13417,26 +13387,26 @@
         </is>
       </c>
       <c r="Z230">
-        <v>59.920024</v>
+        <v>59.917265</v>
       </c>
       <c r="AA230">
-        <v>30.273876</v>
+        <v>30.277625</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z43</t>
+          <t xml:space="preserve">Z141</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Склад</t>
+          <t xml:space="preserve">Административно-бытовой корпус</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Склад</t>
+          <t xml:space="preserve">Административно-бытовой корпус</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -13445,19 +13415,19 @@
         </is>
       </c>
       <c r="E231">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F231">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="G231">
-        <v>752</v>
-      </c>
-      <c r="H231">
-        <v>752</v>
+        <v>810</v>
+      </c>
+      <c r="H231" s="3">
+        <v>2429</v>
       </c>
       <c r="I231" s="3">
-        <v>7954</v>
+        <v>9718</v>
       </c>
       <c r="W231" t="inlineStr">
         <is>
@@ -13471,30 +13441,30 @@
       </c>
       <c r="Y231" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z231">
-        <v>59.919915</v>
+        <v>59.920024</v>
       </c>
       <c r="AA231">
-        <v>30.270178</v>
+        <v>30.273876</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z117</t>
+          <t xml:space="preserve">Z43</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Административно-бытовой корпус</t>
+          <t xml:space="preserve">Склад</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Административно-бытовой корпус</t>
+          <t xml:space="preserve">Склад</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -13503,19 +13473,19 @@
         </is>
       </c>
       <c r="E232">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F232">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="G232">
-        <v>533</v>
-      </c>
-      <c r="H232" s="3">
-        <v>1599</v>
+        <v>752</v>
+      </c>
+      <c r="H232">
+        <v>752</v>
       </c>
       <c r="I232" s="3">
-        <v>6398</v>
+        <v>7954</v>
       </c>
       <c r="W232" t="inlineStr">
         <is>
@@ -13529,30 +13499,30 @@
       </c>
       <c r="Y232" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenStreetMap</t>
+          <t xml:space="preserve">карта предприятия</t>
         </is>
       </c>
       <c r="Z232">
-        <v>59.917356</v>
+        <v>59.919915</v>
       </c>
       <c r="AA232">
-        <v>30.271116</v>
+        <v>30.270178</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z174</t>
+          <t xml:space="preserve">Z117</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Склад</t>
+          <t xml:space="preserve">Канцелярия, чертёжная и бухгалтерия</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Склад</t>
+          <t xml:space="preserve">Административно-бытовой корпус</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -13561,19 +13531,19 @@
         </is>
       </c>
       <c r="E233">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F233">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="G233">
-        <v>526</v>
-      </c>
-      <c r="H233">
-        <v>526</v>
+        <v>533</v>
+      </c>
+      <c r="H233" s="3">
+        <v>1599</v>
       </c>
       <c r="I233" s="3">
-        <v>5395</v>
+        <v>6398</v>
       </c>
       <c r="W233" t="inlineStr">
         <is>
@@ -13591,26 +13561,26 @@
         </is>
       </c>
       <c r="Z233">
-        <v>59.917052</v>
+        <v>59.917356</v>
       </c>
       <c r="AA233">
-        <v>30.273775</v>
+        <v>30.271116</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z198</t>
+          <t xml:space="preserve">Z174</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Административно-бытовой корпус</t>
+          <t xml:space="preserve">Склад</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Административно-бытовой корпус</t>
+          <t xml:space="preserve">Склад</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -13619,19 +13589,19 @@
         </is>
       </c>
       <c r="E234">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F234">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="G234">
-        <v>506</v>
-      </c>
-      <c r="H234" s="3">
-        <v>1518</v>
+        <v>526</v>
+      </c>
+      <c r="H234">
+        <v>526</v>
       </c>
       <c r="I234" s="3">
-        <v>6071</v>
+        <v>5395</v>
       </c>
       <c r="W234" t="inlineStr">
         <is>
@@ -13649,26 +13619,26 @@
         </is>
       </c>
       <c r="Z234">
-        <v>59.916608</v>
+        <v>59.917052</v>
       </c>
       <c r="AA234">
-        <v>30.276732</v>
+        <v>30.273775</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z42</t>
+          <t xml:space="preserve">Z198</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вспомогательное здание</t>
+          <t xml:space="preserve">Административно-бытовой корпус</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вспомогательное здание</t>
+          <t xml:space="preserve">Административно-бытовой корпус</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -13677,19 +13647,19 @@
         </is>
       </c>
       <c r="E235">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F235">
-        <v>6.5</v>
+        <v>12</v>
       </c>
       <c r="G235">
-        <v>491</v>
-      </c>
-      <c r="H235">
-        <v>981</v>
+        <v>506</v>
+      </c>
+      <c r="H235" s="3">
+        <v>1518</v>
       </c>
       <c r="I235" s="3">
-        <v>3189</v>
+        <v>6071</v>
       </c>
       <c r="W235" t="inlineStr">
         <is>
@@ -13703,20 +13673,20 @@
       </c>
       <c r="Y235" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z235">
-        <v>59.918025</v>
+        <v>59.916608</v>
       </c>
       <c r="AA235">
-        <v>30.269341</v>
+        <v>30.276732</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z142</t>
+          <t xml:space="preserve">Z42</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -13741,13 +13711,13 @@
         <v>6.5</v>
       </c>
       <c r="G236">
-        <v>441</v>
+        <v>491</v>
       </c>
       <c r="H236">
-        <v>882</v>
+        <v>981</v>
       </c>
       <c r="I236" s="3">
-        <v>2866</v>
+        <v>3189</v>
       </c>
       <c r="W236" t="inlineStr">
         <is>
@@ -13761,20 +13731,20 @@
       </c>
       <c r="Y236" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenStreetMap</t>
+          <t xml:space="preserve">карта предприятия</t>
         </is>
       </c>
       <c r="Z236">
-        <v>59.920594</v>
+        <v>59.918025</v>
       </c>
       <c r="AA236">
-        <v>30.274176</v>
+        <v>30.269341</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z66</t>
+          <t xml:space="preserve">Z142</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -13799,13 +13769,13 @@
         <v>6.5</v>
       </c>
       <c r="G237">
-        <v>378</v>
+        <v>441</v>
       </c>
       <c r="H237">
-        <v>757</v>
+        <v>882</v>
       </c>
       <c r="I237" s="3">
-        <v>2460</v>
+        <v>2866</v>
       </c>
       <c r="W237" t="inlineStr">
         <is>
@@ -13823,16 +13793,16 @@
         </is>
       </c>
       <c r="Z237">
-        <v>59.919154</v>
+        <v>59.920594</v>
       </c>
       <c r="AA237">
-        <v>30.270439</v>
+        <v>30.274176</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z10</t>
+          <t xml:space="preserve">Z66</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -13857,13 +13827,13 @@
         <v>6.5</v>
       </c>
       <c r="G238">
-        <v>363</v>
+        <v>378</v>
       </c>
       <c r="H238">
-        <v>726</v>
+        <v>757</v>
       </c>
       <c r="I238" s="3">
-        <v>2360</v>
+        <v>2460</v>
       </c>
       <c r="W238" t="inlineStr">
         <is>
@@ -13877,20 +13847,20 @@
       </c>
       <c r="Y238" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z238">
-        <v>59.91841</v>
+        <v>59.919154</v>
       </c>
       <c r="AA238">
-        <v>30.266818</v>
+        <v>30.270439</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z29</t>
+          <t xml:space="preserve">Z10</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -13915,13 +13885,13 @@
         <v>6.5</v>
       </c>
       <c r="G239">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="H239">
-        <v>717</v>
+        <v>726</v>
       </c>
       <c r="I239" s="3">
-        <v>2331</v>
+        <v>2360</v>
       </c>
       <c r="W239" t="inlineStr">
         <is>
@@ -13935,20 +13905,20 @@
       </c>
       <c r="Y239" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenStreetMap</t>
+          <t xml:space="preserve">карта предприятия</t>
         </is>
       </c>
       <c r="Z239">
-        <v>59.91623</v>
+        <v>59.91841</v>
       </c>
       <c r="AA239">
-        <v>30.267671</v>
+        <v>30.266818</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z134</t>
+          <t xml:space="preserve">Z29</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -13973,13 +13943,13 @@
         <v>6.5</v>
       </c>
       <c r="G240">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="H240">
-        <v>704</v>
+        <v>717</v>
       </c>
       <c r="I240" s="3">
-        <v>2289</v>
+        <v>2331</v>
       </c>
       <c r="W240" t="inlineStr">
         <is>
@@ -13997,16 +13967,16 @@
         </is>
       </c>
       <c r="Z240">
-        <v>59.919242</v>
+        <v>59.91623</v>
       </c>
       <c r="AA240">
-        <v>30.273115</v>
+        <v>30.267671</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z83</t>
+          <t xml:space="preserve">Z134</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -14031,13 +14001,13 @@
         <v>6.5</v>
       </c>
       <c r="G241">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="H241">
-        <v>693</v>
+        <v>704</v>
       </c>
       <c r="I241" s="3">
-        <v>2252</v>
+        <v>2289</v>
       </c>
       <c r="W241" t="inlineStr">
         <is>
@@ -14055,16 +14025,16 @@
         </is>
       </c>
       <c r="Z241">
-        <v>59.919041</v>
+        <v>59.919242</v>
       </c>
       <c r="AA241">
-        <v>30.271084</v>
+        <v>30.273115</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z79</t>
+          <t xml:space="preserve">Z83</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -14089,13 +14059,13 @@
         <v>6.5</v>
       </c>
       <c r="G242">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="H242">
-        <v>674</v>
+        <v>693</v>
       </c>
       <c r="I242" s="3">
-        <v>2191</v>
+        <v>2252</v>
       </c>
       <c r="W242" t="inlineStr">
         <is>
@@ -14109,20 +14079,20 @@
       </c>
       <c r="Y242" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z242">
-        <v>59.916646</v>
+        <v>59.919041</v>
       </c>
       <c r="AA242">
-        <v>30.269619</v>
+        <v>30.271084</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z18</t>
+          <t xml:space="preserve">Z79</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -14147,13 +14117,13 @@
         <v>6.5</v>
       </c>
       <c r="G243">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="H243">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="I243" s="3">
-        <v>2174</v>
+        <v>2191</v>
       </c>
       <c r="W243" t="inlineStr">
         <is>
@@ -14167,20 +14137,20 @@
       </c>
       <c r="Y243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Microsoft ML Buildings</t>
+          <t xml:space="preserve">карта предприятия</t>
         </is>
       </c>
       <c r="Z243">
-        <v>59.918178</v>
+        <v>59.916646</v>
       </c>
       <c r="AA243">
-        <v>30.268236</v>
+        <v>30.269619</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z122</t>
+          <t xml:space="preserve">Z18</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -14205,13 +14175,13 @@
         <v>6.5</v>
       </c>
       <c r="G244">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="H244">
-        <v>646</v>
+        <v>669</v>
       </c>
       <c r="I244" s="3">
-        <v>2099</v>
+        <v>2174</v>
       </c>
       <c r="W244" t="inlineStr">
         <is>
@@ -14225,20 +14195,20 @@
       </c>
       <c r="Y244" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenStreetMap</t>
+          <t xml:space="preserve">Microsoft ML Buildings</t>
         </is>
       </c>
       <c r="Z244">
-        <v>59.917663</v>
+        <v>59.918178</v>
       </c>
       <c r="AA244">
-        <v>30.271202</v>
+        <v>30.268236</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z20</t>
+          <t xml:space="preserve">Z122</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -14263,13 +14233,13 @@
         <v>6.5</v>
       </c>
       <c r="G245">
-        <v>290</v>
+        <v>323</v>
       </c>
       <c r="H245">
-        <v>581</v>
+        <v>646</v>
       </c>
       <c r="I245" s="3">
-        <v>1888</v>
+        <v>2099</v>
       </c>
       <c r="W245" t="inlineStr">
         <is>
@@ -14283,20 +14253,20 @@
       </c>
       <c r="Y245" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z245">
-        <v>59.919108</v>
+        <v>59.917663</v>
       </c>
       <c r="AA245">
-        <v>30.268853</v>
+        <v>30.271202</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z25</t>
+          <t xml:space="preserve">Z20</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -14321,13 +14291,13 @@
         <v>6.5</v>
       </c>
       <c r="G246">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="H246">
-        <v>540</v>
+        <v>581</v>
       </c>
       <c r="I246" s="3">
-        <v>1755</v>
+        <v>1888</v>
       </c>
       <c r="W246" t="inlineStr">
         <is>
@@ -14341,20 +14311,20 @@
       </c>
       <c r="Y246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Microsoft ML Buildings</t>
+          <t xml:space="preserve">карта предприятия</t>
         </is>
       </c>
       <c r="Z246">
-        <v>59.918074</v>
+        <v>59.919108</v>
       </c>
       <c r="AA246">
-        <v>30.268785</v>
+        <v>30.268853</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z98</t>
+          <t xml:space="preserve">Z25</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -14379,13 +14349,13 @@
         <v>6.5</v>
       </c>
       <c r="G247">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="H247">
-        <v>525</v>
+        <v>540</v>
       </c>
       <c r="I247" s="3">
-        <v>1706</v>
+        <v>1755</v>
       </c>
       <c r="W247" t="inlineStr">
         <is>
@@ -14403,16 +14373,16 @@
         </is>
       </c>
       <c r="Z247">
-        <v>59.917964</v>
+        <v>59.918074</v>
       </c>
       <c r="AA247">
-        <v>30.270548</v>
+        <v>30.268785</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y7ecd57</t>
+          <t xml:space="preserve">Z98</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -14437,13 +14407,13 @@
         <v>6.5</v>
       </c>
       <c r="G248">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="H248">
-        <v>490</v>
+        <v>525</v>
       </c>
       <c r="I248" s="3">
-        <v>1593</v>
+        <v>1706</v>
       </c>
       <c r="W248" t="inlineStr">
         <is>
@@ -14461,16 +14431,16 @@
         </is>
       </c>
       <c r="Z248">
-        <v>59.918443</v>
+        <v>59.917964</v>
       </c>
       <c r="AA248">
-        <v>30.267458</v>
+        <v>30.270548</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z157</t>
+          <t xml:space="preserve">Y7ecd57</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -14495,13 +14465,13 @@
         <v>6.5</v>
       </c>
       <c r="G249">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="H249">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="I249" s="3">
-        <v>1570</v>
+        <v>1593</v>
       </c>
       <c r="W249" t="inlineStr">
         <is>
@@ -14515,20 +14485,20 @@
       </c>
       <c r="Y249" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenStreetMap</t>
+          <t xml:space="preserve">Microsoft ML Buildings</t>
         </is>
       </c>
       <c r="Z249">
-        <v>59.920499</v>
+        <v>59.918443</v>
       </c>
       <c r="AA249">
-        <v>30.274833</v>
+        <v>30.267458</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z195</t>
+          <t xml:space="preserve">Z157</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -14553,13 +14523,13 @@
         <v>6.5</v>
       </c>
       <c r="G250">
-        <v>204</v>
+        <v>242</v>
       </c>
       <c r="H250">
-        <v>408</v>
+        <v>483</v>
       </c>
       <c r="I250" s="3">
-        <v>1327</v>
+        <v>1570</v>
       </c>
       <c r="W250" t="inlineStr">
         <is>
@@ -14577,16 +14547,16 @@
         </is>
       </c>
       <c r="Z250">
-        <v>59.916787</v>
+        <v>59.920499</v>
       </c>
       <c r="AA250">
-        <v>30.276143</v>
+        <v>30.274833</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z19</t>
+          <t xml:space="preserve">Z195</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -14611,13 +14581,13 @@
         <v>6.5</v>
       </c>
       <c r="G251">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H251">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="I251" s="3">
-        <v>1320</v>
+        <v>1327</v>
       </c>
       <c r="W251" t="inlineStr">
         <is>
@@ -14631,20 +14601,20 @@
       </c>
       <c r="Y251" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z251">
-        <v>59.917016</v>
+        <v>59.916787</v>
       </c>
       <c r="AA251">
-        <v>30.267698</v>
+        <v>30.276143</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yb16555</t>
+          <t xml:space="preserve">Z19</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -14663,41 +14633,46 @@
         </is>
       </c>
       <c r="E252">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F252">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="G252">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="H252">
-        <v>194</v>
-      </c>
-      <c r="I252">
-        <v>776</v>
+        <v>406</v>
+      </c>
+      <c r="I252" s="3">
+        <v>1320</v>
       </c>
       <c r="W252" t="inlineStr">
         <is>
           <t xml:space="preserve">Нет данных</t>
         </is>
       </c>
+      <c r="X252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
       <c r="Y252" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenStreetMap</t>
+          <t xml:space="preserve">карта предприятия</t>
         </is>
       </c>
       <c r="Z252">
-        <v>59.918785</v>
+        <v>59.917016</v>
       </c>
       <c r="AA252">
-        <v>30.27544</v>
+        <v>30.267698</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z49</t>
+          <t xml:space="preserve">Yb16555</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -14719,43 +14694,38 @@
         <v>1</v>
       </c>
       <c r="F253">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="G253">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="H253">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="I253">
-        <v>857</v>
+        <v>776</v>
       </c>
       <c r="W253" t="inlineStr">
         <is>
           <t xml:space="preserve">Нет данных</t>
         </is>
       </c>
-      <c r="X253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">да</t>
-        </is>
-      </c>
       <c r="Y253" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z253">
-        <v>59.920428</v>
+        <v>59.918785</v>
       </c>
       <c r="AA253">
-        <v>30.27058</v>
+        <v>30.27544</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z16</t>
+          <t xml:space="preserve">Z49</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -14774,19 +14744,19 @@
         </is>
       </c>
       <c r="E254">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F254">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="G254">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="H254">
-        <v>361</v>
-      </c>
-      <c r="I254" s="3">
-        <v>1173</v>
+        <v>190</v>
+      </c>
+      <c r="I254">
+        <v>857</v>
       </c>
       <c r="W254" t="inlineStr">
         <is>
@@ -14804,16 +14774,16 @@
         </is>
       </c>
       <c r="Z254">
-        <v>59.917091</v>
+        <v>59.920428</v>
       </c>
       <c r="AA254">
-        <v>30.267237</v>
+        <v>30.27058</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y4f6129</t>
+          <t xml:space="preserve">Z16</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -14838,13 +14808,13 @@
         <v>6.5</v>
       </c>
       <c r="G255">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="H255">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="I255" s="3">
-        <v>1129</v>
+        <v>1173</v>
       </c>
       <c r="W255" t="inlineStr">
         <is>
@@ -14858,30 +14828,30 @@
       </c>
       <c r="Y255" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenStreetMap</t>
+          <t xml:space="preserve">карта предприятия</t>
         </is>
       </c>
       <c r="Z255">
-        <v>59.921035</v>
+        <v>59.917091</v>
       </c>
       <c r="AA255">
-        <v>30.271017</v>
+        <v>30.267237</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z161</t>
+          <t xml:space="preserve">Y4f6129</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Караульный дом (северная проходная Нового Адмиралтейства)</t>
+          <t xml:space="preserve">Вспомогательное здание</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Историческое здание</t>
+          <t xml:space="preserve">Вспомогательное здание</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -14893,48 +14863,53 @@
         <v>2</v>
       </c>
       <c r="F256">
-        <v>11.5</v>
+        <v>6.5</v>
       </c>
       <c r="G256">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="H256">
-        <v>314</v>
+        <v>347</v>
       </c>
       <c r="I256" s="3">
-        <v>1491</v>
+        <v>1129</v>
       </c>
       <c r="W256" t="inlineStr">
         <is>
           <t xml:space="preserve">Нет данных</t>
         </is>
       </c>
+      <c r="X256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
       <c r="Y256" t="inlineStr">
         <is>
           <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z256">
-        <v>59.931366</v>
+        <v>59.921035</v>
       </c>
       <c r="AA256">
-        <v>30.282141</v>
+        <v>30.271017</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y43a4c5</t>
+          <t xml:space="preserve">Z161</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вспомогательное здание</t>
+          <t xml:space="preserve">Служебное здание у часовни</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вспомогательное здание</t>
+          <t xml:space="preserve">Историческое здание</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -14946,43 +14921,38 @@
         <v>1</v>
       </c>
       <c r="F257">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="G257">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="H257">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="I257">
-        <v>636</v>
+        <v>785</v>
       </c>
       <c r="W257" t="inlineStr">
         <is>
           <t xml:space="preserve">Нет данных</t>
         </is>
       </c>
-      <c r="X257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">да</t>
-        </is>
-      </c>
       <c r="Y257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Microsoft ML Buildings</t>
+          <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z257">
-        <v>59.91832</v>
+        <v>59.931366</v>
       </c>
       <c r="AA257">
-        <v>30.268162</v>
+        <v>30.282141</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ya0f72e</t>
+          <t xml:space="preserve">Y43a4c5</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -15007,13 +14977,13 @@
         <v>4.5</v>
       </c>
       <c r="G258">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="H258">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="I258">
-        <v>507</v>
+        <v>636</v>
       </c>
       <c r="W258" t="inlineStr">
         <is>
@@ -15031,16 +15001,16 @@
         </is>
       </c>
       <c r="Z258">
-        <v>59.918837</v>
+        <v>59.91832</v>
       </c>
       <c r="AA258">
-        <v>30.269144</v>
+        <v>30.268162</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yf9aefe</t>
+          <t xml:space="preserve">Ya0f72e</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -15089,16 +15059,16 @@
         </is>
       </c>
       <c r="Z259">
-        <v>59.919075</v>
+        <v>59.918837</v>
       </c>
       <c r="AA259">
-        <v>30.272368</v>
+        <v>30.269144</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y3f0129</t>
+          <t xml:space="preserve">Yf9aefe</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -15123,13 +15093,13 @@
         <v>4.5</v>
       </c>
       <c r="G260">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="H260">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="I260">
-        <v>467</v>
+        <v>507</v>
       </c>
       <c r="W260" t="inlineStr">
         <is>
@@ -15147,16 +15117,16 @@
         </is>
       </c>
       <c r="Z260">
-        <v>59.917315</v>
+        <v>59.919075</v>
       </c>
       <c r="AA260">
-        <v>30.265637</v>
+        <v>30.272368</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z6</t>
+          <t xml:space="preserve">Y3f0129</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -15187,7 +15157,7 @@
         <v>104</v>
       </c>
       <c r="I261">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="W261" t="inlineStr">
         <is>
@@ -15201,20 +15171,20 @@
       </c>
       <c r="Y261" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenStreetMap</t>
+          <t xml:space="preserve">Microsoft ML Buildings</t>
         </is>
       </c>
       <c r="Z261">
-        <v>59.916734</v>
+        <v>59.917315</v>
       </c>
       <c r="AA261">
-        <v>30.265018</v>
+        <v>30.265637</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z15</t>
+          <t xml:space="preserve">Z6</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -15239,13 +15209,13 @@
         <v>4.5</v>
       </c>
       <c r="G262">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H262">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I262">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="W262" t="inlineStr">
         <is>
@@ -15259,20 +15229,20 @@
       </c>
       <c r="Y262" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z262">
-        <v>59.918251</v>
+        <v>59.916734</v>
       </c>
       <c r="AA262">
-        <v>30.267724</v>
+        <v>30.265018</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z12</t>
+          <t xml:space="preserve">Z15</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -15297,13 +15267,13 @@
         <v>4.5</v>
       </c>
       <c r="G263">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H263">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I263">
-        <v>446</v>
+        <v>462</v>
       </c>
       <c r="W263" t="inlineStr">
         <is>
@@ -15321,16 +15291,16 @@
         </is>
       </c>
       <c r="Z263">
-        <v>59.918314</v>
+        <v>59.918251</v>
       </c>
       <c r="AA263">
-        <v>30.267323</v>
+        <v>30.267724</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y24c47e</t>
+          <t xml:space="preserve">Z12</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -15355,13 +15325,13 @@
         <v>4.5</v>
       </c>
       <c r="G264">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H264">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I264">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="W264" t="inlineStr">
         <is>
@@ -15375,20 +15345,20 @@
       </c>
       <c r="Y264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Microsoft ML Buildings</t>
+          <t xml:space="preserve">карта предприятия</t>
         </is>
       </c>
       <c r="Z264">
-        <v>59.918802</v>
+        <v>59.918314</v>
       </c>
       <c r="AA264">
-        <v>30.272684</v>
+        <v>30.267323</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z78</t>
+          <t xml:space="preserve">Y24c47e</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -15413,13 +15383,13 @@
         <v>4.5</v>
       </c>
       <c r="G265">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="H265">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="I265">
-        <v>360</v>
+        <v>438</v>
       </c>
       <c r="W265" t="inlineStr">
         <is>
@@ -15433,20 +15403,20 @@
       </c>
       <c r="Y265" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">Microsoft ML Buildings</t>
         </is>
       </c>
       <c r="Z265">
-        <v>59.916289</v>
+        <v>59.918802</v>
       </c>
       <c r="AA265">
-        <v>30.269171</v>
+        <v>30.272684</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y39fdef</t>
+          <t xml:space="preserve">Z78</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -15471,13 +15441,13 @@
         <v>4.5</v>
       </c>
       <c r="G266">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H266">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="I266">
-        <v>335</v>
+        <v>360</v>
       </c>
       <c r="W266" t="inlineStr">
         <is>
@@ -15491,20 +15461,20 @@
       </c>
       <c r="Y266" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenStreetMap</t>
+          <t xml:space="preserve">карта предприятия</t>
         </is>
       </c>
       <c r="Z266">
-        <v>59.916869</v>
+        <v>59.916289</v>
       </c>
       <c r="AA266">
-        <v>30.276026</v>
+        <v>30.269171</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y97543d</t>
+          <t xml:space="preserve">Y39fdef</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -15529,13 +15499,13 @@
         <v>4.5</v>
       </c>
       <c r="G267">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="H267">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="I267">
-        <v>301</v>
+        <v>335</v>
       </c>
       <c r="W267" t="inlineStr">
         <is>
@@ -15549,20 +15519,20 @@
       </c>
       <c r="Y267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Microsoft ML Buildings</t>
+          <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z267">
-        <v>59.91616</v>
+        <v>59.916869</v>
       </c>
       <c r="AA267">
-        <v>30.266067</v>
+        <v>30.276026</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yb90624</t>
+          <t xml:space="preserve">Y97543d</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -15587,13 +15557,13 @@
         <v>4.5</v>
       </c>
       <c r="G268">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H268">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="I268">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="W268" t="inlineStr">
         <is>
@@ -15611,16 +15581,16 @@
         </is>
       </c>
       <c r="Z268">
-        <v>59.918887</v>
+        <v>59.91616</v>
       </c>
       <c r="AA268">
-        <v>30.272798</v>
+        <v>30.266067</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y6ae3a7</t>
+          <t xml:space="preserve">Yb90624</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -15645,13 +15615,13 @@
         <v>4.5</v>
       </c>
       <c r="G269">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H269">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I269">
-        <v>262</v>
+        <v>285</v>
       </c>
       <c r="W269" t="inlineStr">
         <is>
@@ -15669,16 +15639,16 @@
         </is>
       </c>
       <c r="Z269">
-        <v>59.917264</v>
+        <v>59.918887</v>
       </c>
       <c r="AA269">
-        <v>30.273049</v>
+        <v>30.272798</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ycc04ca</t>
+          <t xml:space="preserve">Y6ae3a7</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -15703,13 +15673,13 @@
         <v>4.5</v>
       </c>
       <c r="G270">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H270">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I270">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="W270" t="inlineStr">
         <is>
@@ -15723,20 +15693,20 @@
       </c>
       <c r="Y270" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenStreetMap</t>
+          <t xml:space="preserve">Microsoft ML Buildings</t>
         </is>
       </c>
       <c r="Z270">
-        <v>59.91654</v>
+        <v>59.917264</v>
       </c>
       <c r="AA270">
-        <v>30.276045</v>
+        <v>30.273049</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y64b17f</t>
+          <t xml:space="preserve">Ycc04ca</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -15761,13 +15731,13 @@
         <v>4.5</v>
       </c>
       <c r="G271">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H271">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I271">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="W271" t="inlineStr">
         <is>
@@ -15781,20 +15751,20 @@
       </c>
       <c r="Y271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Microsoft ML Buildings</t>
+          <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z271">
-        <v>59.920224</v>
+        <v>59.91654</v>
       </c>
       <c r="AA271">
-        <v>30.270423</v>
+        <v>30.276045</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y8ec98b</t>
+          <t xml:space="preserve">Y64b17f</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -15819,13 +15789,13 @@
         <v>4.5</v>
       </c>
       <c r="G272">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H272">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I272">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="W272" t="inlineStr">
         <is>
@@ -15843,16 +15813,16 @@
         </is>
       </c>
       <c r="Z272">
-        <v>59.916248</v>
+        <v>59.920224</v>
       </c>
       <c r="AA272">
-        <v>30.266045</v>
+        <v>30.270423</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z86</t>
+          <t xml:space="preserve">Y8ec98b</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -15883,7 +15853,7 @@
         <v>53</v>
       </c>
       <c r="I273">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="W273" t="inlineStr">
         <is>
@@ -15901,21 +15871,21 @@
         </is>
       </c>
       <c r="Z273">
-        <v>59.917903</v>
+        <v>59.916248</v>
       </c>
       <c r="AA273">
-        <v>30.270279</v>
+        <v>30.266045</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y536a17</t>
+          <t xml:space="preserve">Z86</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Часовня храма «Спас-на-Водах»</t>
+          <t xml:space="preserve">Вспомогательное здание</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -15932,43 +15902,48 @@
         <v>1</v>
       </c>
       <c r="F274">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="G274">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H274">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I274">
-        <v>199</v>
+        <v>240</v>
       </c>
       <c r="W274" t="inlineStr">
         <is>
           <t xml:space="preserve">Нет данных</t>
         </is>
       </c>
+      <c r="X274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
       <c r="Y274" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenStreetMap</t>
+          <t xml:space="preserve">Microsoft ML Buildings</t>
         </is>
       </c>
       <c r="Z274">
-        <v>59.931521</v>
+        <v>59.917903</v>
       </c>
       <c r="AA274">
-        <v>30.281789</v>
+        <v>30.270279</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y91523f</t>
+          <t xml:space="preserve">Y536a17</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вспомогательное здание</t>
+          <t xml:space="preserve">Часовня храма «Спас-на-Водах»</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -15985,43 +15960,38 @@
         <v>1</v>
       </c>
       <c r="F275">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="G275">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H275">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I275">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="W275" t="inlineStr">
         <is>
           <t xml:space="preserve">Нет данных</t>
         </is>
       </c>
-      <c r="X275" t="inlineStr">
-        <is>
-          <t xml:space="preserve">да</t>
-        </is>
-      </c>
       <c r="Y275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Microsoft ML Buildings</t>
+          <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z275">
-        <v>59.916955</v>
+        <v>59.931521</v>
       </c>
       <c r="AA275">
-        <v>30.268761</v>
+        <v>30.281789</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y459669</t>
+          <t xml:space="preserve">Y91523f</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -16046,13 +16016,13 @@
         <v>4.5</v>
       </c>
       <c r="G276">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H276">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I276">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="W276" t="inlineStr">
         <is>
@@ -16070,16 +16040,16 @@
         </is>
       </c>
       <c r="Z276">
-        <v>59.918267</v>
+        <v>59.916955</v>
       </c>
       <c r="AA276">
-        <v>30.268037</v>
+        <v>30.268761</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y7fa697</t>
+          <t xml:space="preserve">Y459669</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -16104,13 +16074,13 @@
         <v>4.5</v>
       </c>
       <c r="G277">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H277">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I277">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="W277" t="inlineStr">
         <is>
@@ -16124,20 +16094,20 @@
       </c>
       <c r="Y277" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenStreetMap</t>
+          <t xml:space="preserve">Microsoft ML Buildings</t>
         </is>
       </c>
       <c r="Z277">
-        <v>59.916091</v>
+        <v>59.918267</v>
       </c>
       <c r="AA277">
-        <v>30.270079</v>
+        <v>30.268037</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y604d03</t>
+          <t xml:space="preserve">Y7fa697</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -16162,13 +16132,13 @@
         <v>4.5</v>
       </c>
       <c r="G278">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H278">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I278">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="W278" t="inlineStr">
         <is>
@@ -16182,20 +16152,20 @@
       </c>
       <c r="Y278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Microsoft ML Buildings</t>
+          <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z278">
-        <v>59.919335</v>
+        <v>59.916091</v>
       </c>
       <c r="AA278">
-        <v>30.268958</v>
+        <v>30.270079</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ye48a35</t>
+          <t xml:space="preserve">Y604d03</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -16226,7 +16196,7 @@
         <v>36</v>
       </c>
       <c r="I279">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="W279" t="inlineStr">
         <is>
@@ -16244,16 +16214,16 @@
         </is>
       </c>
       <c r="Z279">
-        <v>59.916893</v>
+        <v>59.919335</v>
       </c>
       <c r="AA279">
-        <v>30.276229</v>
+        <v>30.268958</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y1a50d5</t>
+          <t xml:space="preserve">Ye48a35</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -16278,13 +16248,13 @@
         <v>4.5</v>
       </c>
       <c r="G280">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H280">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I280">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="W280" t="inlineStr">
         <is>
@@ -16302,16 +16272,16 @@
         </is>
       </c>
       <c r="Z280">
-        <v>59.917883</v>
+        <v>59.916893</v>
       </c>
       <c r="AA280">
-        <v>30.266264</v>
+        <v>30.276229</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y33cd36</t>
+          <t xml:space="preserve">Y1a50d5</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -16342,7 +16312,7 @@
         <v>31</v>
       </c>
       <c r="I281">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="W281" t="inlineStr">
         <is>
@@ -16360,16 +16330,16 @@
         </is>
       </c>
       <c r="Z281">
-        <v>59.916815</v>
+        <v>59.917883</v>
       </c>
       <c r="AA281">
-        <v>30.265001</v>
+        <v>30.266264</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yac22bc</t>
+          <t xml:space="preserve">Y33cd36</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -16394,13 +16364,13 @@
         <v>4.5</v>
       </c>
       <c r="G282">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H282">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I282">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="W282" t="inlineStr">
         <is>
@@ -16418,16 +16388,16 @@
         </is>
       </c>
       <c r="Z282">
-        <v>59.916682</v>
+        <v>59.916815</v>
       </c>
       <c r="AA282">
-        <v>30.269965</v>
+        <v>30.265001</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yba1032</t>
+          <t xml:space="preserve">Yac22bc</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -16452,13 +16422,13 @@
         <v>4.5</v>
       </c>
       <c r="G283">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H283">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I283">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="W283" t="inlineStr">
         <is>
@@ -16476,16 +16446,16 @@
         </is>
       </c>
       <c r="Z283">
-        <v>59.917812</v>
+        <v>59.916682</v>
       </c>
       <c r="AA283">
-        <v>30.266622</v>
+        <v>30.269965</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y8ef773</t>
+          <t xml:space="preserve">Yba1032</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -16516,7 +16486,7 @@
         <v>27</v>
       </c>
       <c r="I284">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="W284" t="inlineStr">
         <is>
@@ -16534,16 +16504,16 @@
         </is>
       </c>
       <c r="Z284">
-        <v>59.917792</v>
+        <v>59.917812</v>
       </c>
       <c r="AA284">
-        <v>30.271182</v>
+        <v>30.266622</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y9d36fa</t>
+          <t xml:space="preserve">Y8ef773</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -16574,7 +16544,7 @@
         <v>27</v>
       </c>
       <c r="I285">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="W285" t="inlineStr">
         <is>
@@ -16592,16 +16562,16 @@
         </is>
       </c>
       <c r="Z285">
-        <v>59.924858</v>
+        <v>59.917792</v>
       </c>
       <c r="AA285">
-        <v>30.276895</v>
+        <v>30.271182</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y5f32ee</t>
+          <t xml:space="preserve">Y9d36fa</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -16626,13 +16596,13 @@
         <v>4.5</v>
       </c>
       <c r="G286">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H286">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I286">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="W286" t="inlineStr">
         <is>
@@ -16650,16 +16620,16 @@
         </is>
       </c>
       <c r="Z286">
-        <v>59.918398</v>
+        <v>59.924858</v>
       </c>
       <c r="AA286">
-        <v>30.267786</v>
+        <v>30.276895</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y0af2fb</t>
+          <t xml:space="preserve">Y5f32ee</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -16684,13 +16654,13 @@
         <v>4.5</v>
       </c>
       <c r="G287">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H287">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I287">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="W287" t="inlineStr">
         <is>
@@ -16708,16 +16678,16 @@
         </is>
       </c>
       <c r="Z287">
-        <v>59.918313</v>
+        <v>59.918398</v>
       </c>
       <c r="AA287">
-        <v>30.266511</v>
+        <v>30.267786</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y289bd5</t>
+          <t xml:space="preserve">Y0af2fb</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -16742,13 +16712,13 @@
         <v>4.5</v>
       </c>
       <c r="G288">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H288">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I288">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="W288" t="inlineStr">
         <is>
@@ -16766,16 +16736,16 @@
         </is>
       </c>
       <c r="Z288">
-        <v>59.918011</v>
+        <v>59.918313</v>
       </c>
       <c r="AA288">
-        <v>30.275561</v>
+        <v>30.266511</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y2cf1c4</t>
+          <t xml:space="preserve">Y289bd5</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -16800,13 +16770,13 @@
         <v>4.5</v>
       </c>
       <c r="G289">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H289">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I289">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="W289" t="inlineStr">
         <is>
@@ -16824,16 +16794,16 @@
         </is>
       </c>
       <c r="Z289">
-        <v>59.920802</v>
+        <v>59.918011</v>
       </c>
       <c r="AA289">
-        <v>30.270869</v>
+        <v>30.275561</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ye86f38</t>
+          <t xml:space="preserve">Y2cf1c4</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -16858,13 +16828,13 @@
         <v>4.5</v>
       </c>
       <c r="G290">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H290">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I290">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="W290" t="inlineStr">
         <is>
@@ -16882,16 +16852,16 @@
         </is>
       </c>
       <c r="Z290">
-        <v>59.917665</v>
+        <v>59.920802</v>
       </c>
       <c r="AA290">
-        <v>30.267606</v>
+        <v>30.270869</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y842542</t>
+          <t xml:space="preserve">Ye86f38</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -16940,16 +16910,16 @@
         </is>
       </c>
       <c r="Z291">
-        <v>59.916201</v>
+        <v>59.917665</v>
       </c>
       <c r="AA291">
-        <v>30.268012</v>
+        <v>30.267606</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ya14596</t>
+          <t xml:space="preserve">Y842542</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -16980,7 +16950,7 @@
         <v>19</v>
       </c>
       <c r="I292">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="W292" t="inlineStr">
         <is>
@@ -16998,16 +16968,16 @@
         </is>
       </c>
       <c r="Z292">
-        <v>59.917193</v>
+        <v>59.916201</v>
       </c>
       <c r="AA292">
-        <v>30.272902</v>
+        <v>30.268012</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yd8176d</t>
+          <t xml:space="preserve">Ya14596</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -17032,13 +17002,13 @@
         <v>4.5</v>
       </c>
       <c r="G293">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H293">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I293">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="W293" t="inlineStr">
         <is>
@@ -17056,16 +17026,16 @@
         </is>
       </c>
       <c r="Z293">
-        <v>59.920319</v>
+        <v>59.917193</v>
       </c>
       <c r="AA293">
-        <v>30.270815</v>
+        <v>30.272902</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y8819d9</t>
+          <t xml:space="preserve">Yd8176d</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -17096,7 +17066,7 @@
         <v>16</v>
       </c>
       <c r="I294">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="W294" t="inlineStr">
         <is>
@@ -17114,16 +17084,16 @@
         </is>
       </c>
       <c r="Z294">
-        <v>59.918745</v>
+        <v>59.920319</v>
       </c>
       <c r="AA294">
-        <v>30.273317</v>
+        <v>30.270815</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yc9cd64</t>
+          <t xml:space="preserve">Y8819d9</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -17154,7 +17124,7 @@
         <v>16</v>
       </c>
       <c r="I295">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="W295" t="inlineStr">
         <is>
@@ -17172,16 +17142,16 @@
         </is>
       </c>
       <c r="Z295">
-        <v>59.919104</v>
+        <v>59.918745</v>
       </c>
       <c r="AA295">
-        <v>30.272734</v>
+        <v>30.273317</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y9f3807</t>
+          <t xml:space="preserve">Yc9cd64</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -17206,13 +17176,13 @@
         <v>4.5</v>
       </c>
       <c r="G296">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H296">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I296">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="W296" t="inlineStr">
         <is>
@@ -17230,16 +17200,16 @@
         </is>
       </c>
       <c r="Z296">
-        <v>59.91927</v>
+        <v>59.919104</v>
       </c>
       <c r="AA296">
-        <v>30.268932</v>
+        <v>30.272734</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z139</t>
+          <t xml:space="preserve">Y9f3807</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -17270,7 +17240,7 @@
         <v>15</v>
       </c>
       <c r="I297">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="W297" t="inlineStr">
         <is>
@@ -17288,16 +17258,16 @@
         </is>
       </c>
       <c r="Z297">
-        <v>59.918826</v>
+        <v>59.91927</v>
       </c>
       <c r="AA297">
-        <v>30.273003</v>
+        <v>30.268932</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yc94432</t>
+          <t xml:space="preserve">Z139</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -17328,7 +17298,7 @@
         <v>15</v>
       </c>
       <c r="I298">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="W298" t="inlineStr">
         <is>
@@ -17346,16 +17316,16 @@
         </is>
       </c>
       <c r="Z298">
-        <v>59.917389</v>
+        <v>59.918826</v>
       </c>
       <c r="AA298">
-        <v>30.27673</v>
+        <v>30.273003</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y11bd95</t>
+          <t xml:space="preserve">Yc94432</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -17380,13 +17350,13 @@
         <v>4.5</v>
       </c>
       <c r="G299">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H299">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I299">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="W299" t="inlineStr">
         <is>
@@ -17404,16 +17374,16 @@
         </is>
       </c>
       <c r="Z299">
-        <v>59.920819</v>
+        <v>59.917389</v>
       </c>
       <c r="AA299">
-        <v>30.270751</v>
+        <v>30.27673</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y8d968a</t>
+          <t xml:space="preserve">Y11bd95</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -17444,7 +17414,7 @@
         <v>13</v>
       </c>
       <c r="I300">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="W300" t="inlineStr">
         <is>
@@ -17462,16 +17432,16 @@
         </is>
       </c>
       <c r="Z300">
-        <v>59.919203</v>
+        <v>59.920819</v>
       </c>
       <c r="AA300">
-        <v>30.272331</v>
+        <v>30.270751</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y8cb1f5</t>
+          <t xml:space="preserve">Y8d968a</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -17502,7 +17472,7 @@
         <v>13</v>
       </c>
       <c r="I301">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="W301" t="inlineStr">
         <is>
@@ -17520,16 +17490,16 @@
         </is>
       </c>
       <c r="Z301">
-        <v>59.917333</v>
+        <v>59.919203</v>
       </c>
       <c r="AA301">
-        <v>30.276728</v>
+        <v>30.272331</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ya7ebb7</t>
+          <t xml:space="preserve">Y8cb1f5</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -17554,13 +17524,13 @@
         <v>4.5</v>
       </c>
       <c r="G302">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H302">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I302">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="W302" t="inlineStr">
         <is>
@@ -17578,16 +17548,16 @@
         </is>
       </c>
       <c r="Z302">
-        <v>59.917716</v>
+        <v>59.917333</v>
       </c>
       <c r="AA302">
-        <v>30.267397</v>
+        <v>30.276728</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ydee944</t>
+          <t xml:space="preserve">Ya7ebb7</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -17612,13 +17582,13 @@
         <v>4.5</v>
       </c>
       <c r="G303">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H303">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I303">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="W303" t="inlineStr">
         <is>
@@ -17636,16 +17606,16 @@
         </is>
       </c>
       <c r="Z303">
-        <v>59.916563</v>
+        <v>59.917716</v>
       </c>
       <c r="AA303">
-        <v>30.265103</v>
+        <v>30.267397</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y56dd04</t>
+          <t xml:space="preserve">Ydee944</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -17676,7 +17646,7 @@
         <v>11</v>
       </c>
       <c r="I304">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="W304" t="inlineStr">
         <is>
@@ -17694,16 +17664,16 @@
         </is>
       </c>
       <c r="Z304">
-        <v>59.916593</v>
+        <v>59.916563</v>
       </c>
       <c r="AA304">
-        <v>30.26494</v>
+        <v>30.265103</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y350b1e</t>
+          <t xml:space="preserve">Y56dd04</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -17734,7 +17704,7 @@
         <v>11</v>
       </c>
       <c r="I305">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="W305" t="inlineStr">
         <is>
@@ -17752,16 +17722,16 @@
         </is>
       </c>
       <c r="Z305">
-        <v>59.916464</v>
+        <v>59.916593</v>
       </c>
       <c r="AA305">
-        <v>30.269654</v>
+        <v>30.26494</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y064ef1</t>
+          <t xml:space="preserve">Y350b1e</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -17792,7 +17762,7 @@
         <v>11</v>
       </c>
       <c r="I306">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="W306" t="inlineStr">
         <is>
@@ -17810,16 +17780,16 @@
         </is>
       </c>
       <c r="Z306">
-        <v>59.917185</v>
+        <v>59.916464</v>
       </c>
       <c r="AA306">
-        <v>30.273003</v>
+        <v>30.269654</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y530046</t>
+          <t xml:space="preserve">Y064ef1</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -17844,13 +17814,13 @@
         <v>4.5</v>
       </c>
       <c r="G307">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H307">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I307">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="W307" t="inlineStr">
         <is>
@@ -17868,16 +17838,16 @@
         </is>
       </c>
       <c r="Z307">
-        <v>59.916594</v>
+        <v>59.917185</v>
       </c>
       <c r="AA307">
-        <v>30.265234</v>
+        <v>30.273003</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yead4a4</t>
+          <t xml:space="preserve">Y530046</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -17908,7 +17878,7 @@
         <v>10</v>
       </c>
       <c r="I308">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="W308" t="inlineStr">
         <is>
@@ -17926,16 +17896,16 @@
         </is>
       </c>
       <c r="Z308">
-        <v>59.918206</v>
+        <v>59.916594</v>
       </c>
       <c r="AA308">
-        <v>30.268907</v>
+        <v>30.265234</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ya7ddb4</t>
+          <t xml:space="preserve">Yead4a4</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -17966,7 +17936,7 @@
         <v>10</v>
       </c>
       <c r="I309">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="W309" t="inlineStr">
         <is>
@@ -17984,55 +17954,79 @@
         </is>
       </c>
       <c r="Z309">
-        <v>59.920157</v>
+        <v>59.918206</v>
       </c>
       <c r="AA309">
-        <v>30.273581</v>
+        <v>30.268907</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">Ya7ddb4</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Плавучий док «Луга»</t>
+          <t xml:space="preserve">Вспомогательное здание</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Плавучий док</t>
-        </is>
+          <t xml:space="preserve">Вспомогательное здание</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Основная площадка</t>
+        </is>
+      </c>
+      <c r="E310">
+        <v>1</v>
       </c>
       <c r="F310">
-        <v>14</v>
-      </c>
-      <c r="G310" s="3">
-        <v>2484</v>
+        <v>4.5</v>
+      </c>
+      <c r="G310">
+        <v>10</v>
+      </c>
+      <c r="H310">
+        <v>10</v>
+      </c>
+      <c r="I310">
+        <v>47</v>
       </c>
       <c r="W310" t="inlineStr">
         <is>
           <t xml:space="preserve">Нет данных</t>
         </is>
       </c>
+      <c r="X310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+      <c r="Y310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Microsoft ML Buildings</t>
+        </is>
+      </c>
       <c r="Z310">
-        <v>59.930184</v>
+        <v>59.920157</v>
       </c>
       <c r="AA310">
-        <v>30.27568</v>
+        <v>30.273581</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Плавучий док СПД-2М</t>
+          <t xml:space="preserve">Плавучий док «Луга»</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -18044,7 +18038,7 @@
         <v>14</v>
       </c>
       <c r="G311" s="3">
-        <v>2024</v>
+        <v>2484</v>
       </c>
       <c r="W311" t="inlineStr">
         <is>
@@ -18052,33 +18046,33 @@
         </is>
       </c>
       <c r="Z311">
-        <v>59.920492</v>
+        <v>59.930184</v>
       </c>
       <c r="AA311">
-        <v>30.269747</v>
+        <v>30.27568</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t xml:space="preserve">MB4</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Причальный мост над устьем Пряжки</t>
+          <t xml:space="preserve">Плавучий док СПД-2М</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Заводской мост (сооружение)</t>
+          <t xml:space="preserve">Плавучий док</t>
         </is>
       </c>
       <c r="F312">
-        <v>3</v>
-      </c>
-      <c r="G312">
-        <v>722</v>
+        <v>14</v>
+      </c>
+      <c r="G312" s="3">
+        <v>2024</v>
       </c>
       <c r="W312" t="inlineStr">
         <is>
@@ -18086,21 +18080,21 @@
         </is>
       </c>
       <c r="Z312">
-        <v>59.921307</v>
+        <v>59.920492</v>
       </c>
       <c r="AA312">
-        <v>30.270857</v>
+        <v>30.269747</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">MB4</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Галерный мост</t>
+          <t xml:space="preserve">Причальный мост над устьем Пряжки</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -18112,7 +18106,7 @@
         <v>3</v>
       </c>
       <c r="G313">
-        <v>561</v>
+        <v>722</v>
       </c>
       <c r="W313" t="inlineStr">
         <is>
@@ -18120,21 +18114,21 @@
         </is>
       </c>
       <c r="Z313">
-        <v>59.915481</v>
+        <v>59.921307</v>
       </c>
       <c r="AA313">
-        <v>30.269281</v>
+        <v>30.270857</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Подзорный мост</t>
+          <t xml:space="preserve">Галерный мост</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -18146,7 +18140,7 @@
         <v>3</v>
       </c>
       <c r="G314">
-        <v>450</v>
+        <v>561</v>
       </c>
       <c r="W314" t="inlineStr">
         <is>
@@ -18154,21 +18148,21 @@
         </is>
       </c>
       <c r="Z314">
-        <v>59.920884</v>
+        <v>59.915481</v>
       </c>
       <c r="AA314">
-        <v>30.273826</v>
+        <v>30.269281</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мост</t>
+          <t xml:space="preserve">Подзорный мост</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -18180,7 +18174,7 @@
         <v>3</v>
       </c>
       <c r="G315">
-        <v>317</v>
+        <v>450</v>
       </c>
       <c r="W315" t="inlineStr">
         <is>
@@ -18188,33 +18182,33 @@
         </is>
       </c>
       <c r="Z315">
-        <v>59.92661</v>
+        <v>59.920884</v>
       </c>
       <c r="AA315">
-        <v>30.275432</v>
+        <v>30.273826</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t xml:space="preserve">CH1</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Дымовая труба котельной</t>
+          <t xml:space="preserve">Мост</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Дымовая труба (сооружение)</t>
+          <t xml:space="preserve">Заводской мост (сооружение)</t>
         </is>
       </c>
       <c r="F316">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="G316">
-        <v>28</v>
+        <v>317</v>
       </c>
       <c r="W316" t="inlineStr">
         <is>
@@ -18222,38 +18216,33 @@
         </is>
       </c>
       <c r="Z316">
-        <v>59.916044</v>
+        <v>59.92661</v>
       </c>
       <c r="AA316">
-        <v>30.274169</v>
+        <v>30.275432</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t xml:space="preserve">B26</t>
+          <t xml:space="preserve">CH1</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мост</t>
+          <t xml:space="preserve">Дымовая труба котельной</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Заводской мост (сооружение)</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Матисов остров</t>
+          <t xml:space="preserve">Дымовая труба (сооружение)</t>
         </is>
       </c>
       <c r="F317">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="G317">
-        <v>183</v>
+        <v>28</v>
       </c>
       <c r="W317" t="inlineStr">
         <is>
@@ -18261,38 +18250,38 @@
         </is>
       </c>
       <c r="Z317">
-        <v>59.920798</v>
+        <v>59.916044</v>
       </c>
       <c r="AA317">
-        <v>30.276034</v>
+        <v>30.274169</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t xml:space="preserve">S1</t>
+          <t xml:space="preserve">B26</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Открытый наклонный стапель № 1</t>
+          <t xml:space="preserve">Мост</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Стапель (сооружение)</t>
+          <t xml:space="preserve">Заводской мост (сооружение)</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Основная площадка</t>
+          <t xml:space="preserve">Матисов остров</t>
         </is>
       </c>
       <c r="F318">
-        <v>6</v>
-      </c>
-      <c r="G318" s="3">
-        <v>9681</v>
+        <v>3</v>
+      </c>
+      <c r="G318">
+        <v>183</v>
       </c>
       <c r="W318" t="inlineStr">
         <is>
@@ -18300,21 +18289,21 @@
         </is>
       </c>
       <c r="Z318">
-        <v>59.917317</v>
+        <v>59.920798</v>
       </c>
       <c r="AA318">
-        <v>30.268153</v>
+        <v>30.276034</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t xml:space="preserve">S2</t>
+          <t xml:space="preserve">S1</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Открытый наклонный стапель № 2</t>
+          <t xml:space="preserve">Открытый наклонный стапель № 1</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -18331,7 +18320,7 @@
         <v>6</v>
       </c>
       <c r="G319" s="3">
-        <v>9630</v>
+        <v>9681</v>
       </c>
       <c r="W319" t="inlineStr">
         <is>
@@ -18339,35 +18328,38 @@
         </is>
       </c>
       <c r="Z319">
-        <v>59.917763</v>
+        <v>59.917317</v>
       </c>
       <c r="AA319">
-        <v>30.268565</v>
+        <v>30.268153</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t xml:space="preserve">C11</t>
+          <t xml:space="preserve">S2</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Козловой кран открытого склада</t>
+          <t xml:space="preserve">Открытый наклонный стапель № 2</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Грузоподъёмный кран</t>
+          <t xml:space="preserve">Стапель (сооружение)</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Галерный остров</t>
+          <t xml:space="preserve">Основная площадка</t>
         </is>
       </c>
       <c r="F320">
-        <v>24</v>
+        <v>6</v>
+      </c>
+      <c r="G320" s="3">
+        <v>9630</v>
       </c>
       <c r="W320" t="inlineStr">
         <is>
@@ -18375,21 +18367,21 @@
         </is>
       </c>
       <c r="Z320">
-        <v>59.913208</v>
+        <v>59.917763</v>
       </c>
       <c r="AA320">
-        <v>30.264121</v>
+        <v>30.268565</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">C11</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Портальный кран (Матисов остров)</t>
+          <t xml:space="preserve">Козловой кран открытого склада</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -18399,11 +18391,11 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Матисов остров</t>
+          <t xml:space="preserve">Галерный остров</t>
         </is>
       </c>
       <c r="F321">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="W321" t="inlineStr">
         <is>
@@ -18411,16 +18403,16 @@
         </is>
       </c>
       <c r="Z321">
-        <v>59.922241</v>
+        <v>59.913208</v>
       </c>
       <c r="AA321">
-        <v>30.271466</v>
+        <v>30.264121</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -18447,21 +18439,21 @@
         </is>
       </c>
       <c r="Z322">
-        <v>59.923143</v>
+        <v>59.922241</v>
       </c>
       <c r="AA322">
-        <v>30.272097</v>
+        <v>30.271466</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Портальный кран причала у устья Мойки</t>
+          <t xml:space="preserve">Портальный кран (Матисов остров)</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -18483,16 +18475,16 @@
         </is>
       </c>
       <c r="Z323">
-        <v>59.924415</v>
+        <v>59.923143</v>
       </c>
       <c r="AA323">
-        <v>30.272258</v>
+        <v>30.272097</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -18519,21 +18511,21 @@
         </is>
       </c>
       <c r="Z324">
-        <v>59.9252</v>
+        <v>59.924415</v>
       </c>
       <c r="AA324">
-        <v>30.272657</v>
+        <v>30.272258</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t xml:space="preserve">C10</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Портальный кран (Новое Адмиралтейство)</t>
+          <t xml:space="preserve">Портальный кран причала у устья Мойки</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -18543,11 +18535,11 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ново-Адмиралтейский остров</t>
+          <t xml:space="preserve">Матисов остров</t>
         </is>
       </c>
       <c r="F325">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="W325" t="inlineStr">
         <is>
@@ -18555,21 +18547,21 @@
         </is>
       </c>
       <c r="Z325">
-        <v>59.928636</v>
+        <v>59.9252</v>
       </c>
       <c r="AA325">
-        <v>30.275116</v>
+        <v>30.272657</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">C10</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Стапельный кран (путь между стапелями)</t>
+          <t xml:space="preserve">Портальный кран (Новое Адмиралтейство)</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -18579,11 +18571,11 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Основная площадка</t>
+          <t xml:space="preserve">Ново-Адмиралтейский остров</t>
         </is>
       </c>
       <c r="F326">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="W326" t="inlineStr">
         <is>
@@ -18591,16 +18583,16 @@
         </is>
       </c>
       <c r="Z326">
-        <v>59.917374</v>
+        <v>59.928636</v>
       </c>
       <c r="AA326">
-        <v>30.269392</v>
+        <v>30.275116</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -18627,21 +18619,21 @@
         </is>
       </c>
       <c r="Z327">
-        <v>59.917628</v>
+        <v>59.917374</v>
       </c>
       <c r="AA327">
-        <v>30.267768</v>
+        <v>30.269392</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t xml:space="preserve">Стапельный кран стапеля № 1</t>
+          <t xml:space="preserve">Стапельный кран (путь между стапелями)</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -18655,7 +18647,7 @@
         </is>
       </c>
       <c r="F328">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="W328" t="inlineStr">
         <is>
@@ -18663,21 +18655,21 @@
         </is>
       </c>
       <c r="Z328">
-        <v>59.917055</v>
+        <v>59.917628</v>
       </c>
       <c r="AA328">
-        <v>30.26823</v>
+        <v>30.267768</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t xml:space="preserve">Портальный кран достроечной набережной</t>
+          <t xml:space="preserve">Стапельный кран стапеля № 1</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -18691,7 +18683,7 @@
         </is>
       </c>
       <c r="F329">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="W329" t="inlineStr">
         <is>
@@ -18699,16 +18691,16 @@
         </is>
       </c>
       <c r="Z329">
-        <v>59.920147</v>
+        <v>59.917055</v>
       </c>
       <c r="AA329">
-        <v>30.27</v>
+        <v>30.26823</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -18735,14 +18727,50 @@
         </is>
       </c>
       <c r="Z330">
+        <v>59.920147</v>
+      </c>
+      <c r="AA330">
+        <v>30.27</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C5</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Портальный кран достроечной набережной</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Грузоподъёмный кран</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Основная площадка</t>
+        </is>
+      </c>
+      <c r="F331">
+        <v>42</v>
+      </c>
+      <c r="W331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Нет данных</t>
+        </is>
+      </c>
+      <c r="Z331">
         <v>59.92075</v>
       </c>
-      <c r="AA330">
+      <c r="AA331">
         <v>30.270422</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA330"/>
+  <autoFilter ref="A1:AA331"/>
 </worksheet>
 </file>
 
@@ -18785,7 +18813,7 @@
       </c>
       <c r="B3" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">329</t>
+          <t xml:space="preserve">330</t>
         </is>
       </c>
     </row>

--- a/admiralty-shipyards-territory/dist/admiralty-shipyards-registry.xlsx
+++ b/admiralty-shipyards-territory/dist/admiralty-shipyards-registry.xlsx
@@ -799,10 +799,10 @@
         <v>1338</v>
       </c>
       <c r="H11" s="3">
-        <v>6691</v>
+        <v>5200</v>
       </c>
       <c r="I11" s="3">
-        <v>23551</v>
+        <v>18485</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -3762,17 +3762,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z121</t>
+          <t xml:space="preserve">Ybea863</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Административно-бытовой корпус</t>
+          <t xml:space="preserve">Склад</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Административно-бытовой корпус</t>
+          <t xml:space="preserve">Склад</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3781,19 +3781,19 @@
         </is>
       </c>
       <c r="E63">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F63">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G63">
-        <v>814</v>
-      </c>
-      <c r="H63" s="3">
-        <v>2443</v>
+        <v>856</v>
+      </c>
+      <c r="H63">
+        <v>856</v>
       </c>
       <c r="I63" s="3">
-        <v>9773</v>
+        <v>7701</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
@@ -3807,30 +3807,30 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenStreetMap</t>
+          <t xml:space="preserve">Microsoft ML Buildings</t>
         </is>
       </c>
       <c r="Z63">
-        <v>59.922568</v>
+        <v>59.926101</v>
       </c>
       <c r="AA63">
-        <v>30.274415</v>
+        <v>30.275729</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ybea863</t>
+          <t xml:space="preserve">Z121</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Склад</t>
+          <t xml:space="preserve">Административно-бытовой корпус</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Склад</t>
+          <t xml:space="preserve">Административно-бытовой корпус</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3839,19 +3839,19 @@
         </is>
       </c>
       <c r="E64">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F64">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G64">
-        <v>809</v>
-      </c>
-      <c r="H64">
-        <v>809</v>
+        <v>814</v>
+      </c>
+      <c r="H64" s="3">
+        <v>2443</v>
       </c>
       <c r="I64" s="3">
-        <v>7284</v>
+        <v>9773</v>
       </c>
       <c r="W64" t="inlineStr">
         <is>
@@ -3865,14 +3865,14 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Microsoft ML Buildings</t>
+          <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z64">
-        <v>59.92612</v>
+        <v>59.922568</v>
       </c>
       <c r="AA64">
-        <v>30.275704</v>
+        <v>30.274415</v>
       </c>
     </row>
     <row r="65">
@@ -3958,16 +3958,16 @@
         <v>1</v>
       </c>
       <c r="F66">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="G66">
-        <v>661</v>
+        <v>689</v>
       </c>
       <c r="H66">
-        <v>661</v>
+        <v>689</v>
       </c>
       <c r="I66" s="3">
-        <v>5947</v>
+        <v>7060</v>
       </c>
       <c r="W66" t="inlineStr">
         <is>
@@ -3985,10 +3985,10 @@
         </is>
       </c>
       <c r="Z66">
-        <v>59.921845</v>
+        <v>59.921843</v>
       </c>
       <c r="AA66">
-        <v>30.275737</v>
+        <v>30.27575</v>
       </c>
     </row>
     <row r="67">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вспомогательное здание</t>
+          <t xml:space="preserve">Административно-бытовой корпус</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4129,28 +4129,23 @@
         </is>
       </c>
       <c r="E69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F69">
-        <v>6.5</v>
+        <v>10.5</v>
       </c>
       <c r="G69">
         <v>536</v>
       </c>
       <c r="H69" s="3">
-        <v>1071</v>
+        <v>1607</v>
       </c>
       <c r="I69" s="3">
-        <v>3482</v>
+        <v>5626</v>
       </c>
       <c r="W69" t="inlineStr">
         <is>
           <t xml:space="preserve">Нет данных</t>
-        </is>
-      </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">да</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
@@ -8111,28 +8106,23 @@
         </is>
       </c>
       <c r="E138">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F138">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G138" s="3">
         <v>8440</v>
       </c>
       <c r="H138" s="3">
-        <v>8440</v>
+        <v>25319</v>
       </c>
       <c r="I138" s="3">
-        <v>168794</v>
+        <v>109716</v>
       </c>
       <c r="W138" t="inlineStr">
         <is>
           <t xml:space="preserve">Нет данных</t>
-        </is>
-      </c>
-      <c r="X138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">да</t>
         </is>
       </c>
       <c r="Y138" t="inlineStr">
@@ -9560,17 +9550,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z143</t>
+          <t xml:space="preserve">Y40444c</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Нарядный дом</t>
+          <t xml:space="preserve">Вспомогательное здание</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Историческое здание</t>
+          <t xml:space="preserve">Вспомогательное здание</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -9582,48 +9572,53 @@
         <v>2</v>
       </c>
       <c r="F164">
-        <v>11.5</v>
+        <v>6.5</v>
       </c>
       <c r="G164">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="H164">
-        <v>639</v>
+        <v>668</v>
       </c>
       <c r="I164" s="3">
-        <v>3037</v>
+        <v>2171</v>
       </c>
       <c r="W164" t="inlineStr">
         <is>
           <t xml:space="preserve">Нет данных</t>
         </is>
       </c>
+      <c r="X164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenStreetMap</t>
+          <t xml:space="preserve">Microsoft ML Buildings</t>
         </is>
       </c>
       <c r="Z164">
-        <v>59.92917</v>
+        <v>59.931376</v>
       </c>
       <c r="AA164">
-        <v>30.27945</v>
+        <v>30.28093</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y40444c</t>
+          <t xml:space="preserve">Z143</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вспомогательное здание</t>
+          <t xml:space="preserve">Нарядный дом</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вспомогательное здание</t>
+          <t xml:space="preserve">Историческое здание</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -9635,37 +9630,32 @@
         <v>2</v>
       </c>
       <c r="F165">
-        <v>6.5</v>
+        <v>11.5</v>
       </c>
       <c r="G165">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="H165">
-        <v>612</v>
+        <v>639</v>
       </c>
       <c r="I165" s="3">
-        <v>1988</v>
+        <v>3037</v>
       </c>
       <c r="W165" t="inlineStr">
         <is>
           <t xml:space="preserve">Нет данных</t>
         </is>
       </c>
-      <c r="X165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">да</t>
-        </is>
-      </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Microsoft ML Buildings</t>
+          <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z165">
-        <v>59.931374</v>
+        <v>59.92917</v>
       </c>
       <c r="AA165">
-        <v>30.28092</v>
+        <v>30.27945</v>
       </c>
     </row>
     <row r="166">

--- a/admiralty-shipyards-territory/dist/admiralty-shipyards-registry.xlsx
+++ b/admiralty-shipyards-territory/dist/admiralty-shipyards-registry.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Справка" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Реестр'!$A$1:$AA$303</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Реестр'!$A$1:$AA$305</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -11086,17 +11086,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z181</t>
+          <t xml:space="preserve">Z182</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Главная электрическая станция</t>
+          <t xml:space="preserve">Заводоуправление (Лоцманская ул., 3)</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Производственный корпус</t>
+          <t xml:space="preserve">Административно-бытовой корпус</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -11105,19 +11105,19 @@
         </is>
       </c>
       <c r="E191">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F191">
-        <v>16</v>
+        <v>28.5</v>
       </c>
       <c r="G191" s="3">
-        <v>2204</v>
+        <v>3375</v>
       </c>
       <c r="H191" s="3">
-        <v>4408</v>
+        <v>17502</v>
       </c>
       <c r="I191" s="3">
-        <v>30858</v>
+        <v>79667</v>
       </c>
       <c r="W191" t="inlineStr">
         <is>
@@ -11130,26 +11130,26 @@
         </is>
       </c>
       <c r="Z191">
-        <v>59.916923</v>
+        <v>59.918162</v>
       </c>
       <c r="AA191">
-        <v>30.274636</v>
+        <v>30.276503</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z155</t>
+          <t xml:space="preserve">Z181</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Инженерный корпус</t>
+          <t xml:space="preserve">Главная электрическая станция</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Административно-бытовой корпус</t>
+          <t xml:space="preserve">Производственный корпус</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -11158,56 +11158,51 @@
         </is>
       </c>
       <c r="E192">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F192">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G192" s="3">
-        <v>2122</v>
+        <v>2204</v>
       </c>
       <c r="H192" s="3">
-        <v>8487</v>
+        <v>4408</v>
       </c>
       <c r="I192" s="3">
-        <v>31824</v>
+        <v>30858</v>
       </c>
       <c r="W192" t="inlineStr">
         <is>
           <t xml:space="preserve">Нет данных</t>
         </is>
       </c>
-      <c r="X192" t="inlineStr">
-        <is>
-          <t xml:space="preserve">да</t>
-        </is>
-      </c>
       <c r="Y192" t="inlineStr">
         <is>
           <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z192">
-        <v>59.91856</v>
+        <v>59.916923</v>
       </c>
       <c r="AA192">
-        <v>30.27438</v>
+        <v>30.274636</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z108</t>
+          <t xml:space="preserve">Z155</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Цех</t>
+          <t xml:space="preserve">Инженерный корпус</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Производственный корпус</t>
+          <t xml:space="preserve">Административно-бытовой корпус</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -11216,19 +11211,19 @@
         </is>
       </c>
       <c r="E193">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F193">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G193" s="3">
-        <v>1864</v>
+        <v>2122</v>
       </c>
       <c r="H193" s="3">
-        <v>1864</v>
+        <v>8487</v>
       </c>
       <c r="I193" s="3">
-        <v>26099</v>
+        <v>31824</v>
       </c>
       <c r="W193" t="inlineStr">
         <is>
@@ -11242,20 +11237,20 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z193">
-        <v>59.916421</v>
+        <v>59.91856</v>
       </c>
       <c r="AA193">
-        <v>30.270523</v>
+        <v>30.27438</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z11</t>
+          <t xml:space="preserve">Z108</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -11277,16 +11272,16 @@
         <v>1</v>
       </c>
       <c r="F194">
-        <v>29.8</v>
+        <v>14</v>
       </c>
       <c r="G194" s="3">
-        <v>1703</v>
+        <v>1864</v>
       </c>
       <c r="H194" s="3">
-        <v>1703</v>
+        <v>1864</v>
       </c>
       <c r="I194" s="3">
-        <v>45394</v>
+        <v>26099</v>
       </c>
       <c r="W194" t="inlineStr">
         <is>
@@ -11300,25 +11295,25 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenStreetMap</t>
+          <t xml:space="preserve">карта предприятия</t>
         </is>
       </c>
       <c r="Z194">
-        <v>59.91687</v>
+        <v>59.916421</v>
       </c>
       <c r="AA194">
-        <v>30.266039</v>
+        <v>30.270523</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y47f4ff</t>
+          <t xml:space="preserve">Z11</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Адмиралтейская</t>
+          <t xml:space="preserve">Цех</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -11335,16 +11330,16 @@
         <v>1</v>
       </c>
       <c r="F195">
-        <v>21.2</v>
+        <v>29.8</v>
       </c>
       <c r="G195" s="3">
-        <v>1451</v>
+        <v>1703</v>
       </c>
       <c r="H195" s="3">
-        <v>1451</v>
+        <v>1703</v>
       </c>
       <c r="I195" s="3">
-        <v>30771</v>
+        <v>45394</v>
       </c>
       <c r="W195" t="inlineStr">
         <is>
@@ -11362,26 +11357,26 @@
         </is>
       </c>
       <c r="Z195">
-        <v>59.920131</v>
+        <v>59.91687</v>
       </c>
       <c r="AA195">
-        <v>30.275259</v>
+        <v>30.266039</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z162</t>
+          <t xml:space="preserve">Y47f4ff</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Склад (Лоцманская ул., 1)</t>
+          <t xml:space="preserve">Адмиралтейская</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Склад</t>
+          <t xml:space="preserve">Производственный корпус</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -11390,51 +11385,56 @@
         </is>
       </c>
       <c r="E196">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F196">
-        <v>12</v>
+        <v>21.2</v>
       </c>
       <c r="G196" s="3">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="H196" s="3">
-        <v>2899</v>
+        <v>1451</v>
       </c>
       <c r="I196" s="3">
-        <v>15585</v>
+        <v>30771</v>
       </c>
       <c r="W196" t="inlineStr">
         <is>
           <t xml:space="preserve">Нет данных</t>
         </is>
       </c>
+      <c r="X196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
       <c r="Y196" t="inlineStr">
         <is>
           <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z196">
-        <v>59.919139</v>
+        <v>59.920131</v>
       </c>
       <c r="AA196">
-        <v>30.274836</v>
+        <v>30.275259</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z197</t>
+          <t xml:space="preserve">Z162</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Административный корпус у Фонтанки</t>
+          <t xml:space="preserve">Склад (Лоцманская ул., 1)</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Административно-бытовой корпус</t>
+          <t xml:space="preserve">Склад</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -11443,56 +11443,51 @@
         </is>
       </c>
       <c r="E197">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F197">
-        <v>18.5</v>
+        <v>12</v>
       </c>
       <c r="G197" s="3">
-        <v>1335</v>
+        <v>1450</v>
       </c>
       <c r="H197" s="3">
-        <v>3864</v>
+        <v>2899</v>
       </c>
       <c r="I197" s="3">
-        <v>17069</v>
+        <v>15585</v>
       </c>
       <c r="W197" t="inlineStr">
         <is>
           <t xml:space="preserve">Нет данных</t>
         </is>
       </c>
-      <c r="X197" t="inlineStr">
-        <is>
-          <t xml:space="preserve">да</t>
-        </is>
-      </c>
       <c r="Y197" t="inlineStr">
         <is>
           <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z197">
-        <v>59.916375</v>
+        <v>59.919139</v>
       </c>
       <c r="AA197">
-        <v>30.276311</v>
+        <v>30.274836</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z115</t>
+          <t xml:space="preserve">Z197</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Цех</t>
+          <t xml:space="preserve">Административный корпус у Фонтанки</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Производственный корпус</t>
+          <t xml:space="preserve">Административно-бытовой корпус</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -11501,19 +11496,19 @@
         </is>
       </c>
       <c r="E198">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F198">
-        <v>20.3</v>
+        <v>18.5</v>
       </c>
       <c r="G198" s="3">
-        <v>1203</v>
+        <v>1335</v>
       </c>
       <c r="H198" s="3">
-        <v>1203</v>
+        <v>3864</v>
       </c>
       <c r="I198" s="3">
-        <v>24427</v>
+        <v>17069</v>
       </c>
       <c r="W198" t="inlineStr">
         <is>
@@ -11531,26 +11526,26 @@
         </is>
       </c>
       <c r="Z198">
-        <v>59.916881</v>
+        <v>59.916375</v>
       </c>
       <c r="AA198">
-        <v>30.270821</v>
+        <v>30.276311</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z165</t>
+          <t xml:space="preserve">Z115</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Производственный корпус (лит. Ж)</t>
+          <t xml:space="preserve">Цех</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Историческое здание</t>
+          <t xml:space="preserve">Производственный корпус</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -11559,51 +11554,56 @@
         </is>
       </c>
       <c r="E199">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F199">
-        <v>12.5</v>
+        <v>20.3</v>
       </c>
       <c r="G199" s="3">
-        <v>1199</v>
+        <v>1203</v>
       </c>
       <c r="H199" s="3">
-        <v>2398</v>
+        <v>1203</v>
       </c>
       <c r="I199" s="3">
-        <v>12888</v>
+        <v>24427</v>
       </c>
       <c r="W199" t="inlineStr">
         <is>
           <t xml:space="preserve">Нет данных</t>
         </is>
       </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
       <c r="Y199" t="inlineStr">
         <is>
           <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z199">
-        <v>59.917093</v>
+        <v>59.916881</v>
       </c>
       <c r="AA199">
-        <v>30.273341</v>
+        <v>30.270821</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z110</t>
+          <t xml:space="preserve">Z165</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Административно-бытовой корпус</t>
+          <t xml:space="preserve">Производственный корпус (лит. Ж)</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Административно-бытовой корпус</t>
+          <t xml:space="preserve">Историческое здание</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -11612,56 +11612,51 @@
         </is>
       </c>
       <c r="E200">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F200">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="G200" s="3">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="H200" s="3">
-        <v>3595</v>
+        <v>2398</v>
       </c>
       <c r="I200" s="3">
-        <v>14380</v>
+        <v>12888</v>
       </c>
       <c r="W200" t="inlineStr">
         <is>
           <t xml:space="preserve">Нет данных</t>
         </is>
       </c>
-      <c r="X200" t="inlineStr">
-        <is>
-          <t xml:space="preserve">да</t>
-        </is>
-      </c>
       <c r="Y200" t="inlineStr">
         <is>
           <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z200">
-        <v>59.920653</v>
+        <v>59.917093</v>
       </c>
       <c r="AA200">
-        <v>30.273124</v>
+        <v>30.273341</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z7</t>
+          <t xml:space="preserve">Z110</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Склад</t>
+          <t xml:space="preserve">Административно-бытовой корпус</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Склад</t>
+          <t xml:space="preserve">Административно-бытовой корпус</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -11670,19 +11665,19 @@
         </is>
       </c>
       <c r="E201">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F201">
-        <v>12.6</v>
-      </c>
-      <c r="G201">
-        <v>948</v>
-      </c>
-      <c r="H201">
-        <v>948</v>
+        <v>12</v>
+      </c>
+      <c r="G201" s="3">
+        <v>1198</v>
+      </c>
+      <c r="H201" s="3">
+        <v>3595</v>
       </c>
       <c r="I201" s="3">
-        <v>10222</v>
+        <v>14380</v>
       </c>
       <c r="W201" t="inlineStr">
         <is>
@@ -11700,26 +11695,26 @@
         </is>
       </c>
       <c r="Z201">
-        <v>59.916973</v>
+        <v>59.920653</v>
       </c>
       <c r="AA201">
-        <v>30.265413</v>
+        <v>30.273124</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z67</t>
+          <t xml:space="preserve">Z7</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Административно-бытовой корпус</t>
+          <t xml:space="preserve">Склад</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Административно-бытовой корпус</t>
+          <t xml:space="preserve">Склад</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -11728,19 +11723,19 @@
         </is>
       </c>
       <c r="E202">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F202">
-        <v>12</v>
+        <v>12.6</v>
       </c>
       <c r="G202">
-        <v>882</v>
-      </c>
-      <c r="H202" s="3">
-        <v>2646</v>
+        <v>948</v>
+      </c>
+      <c r="H202">
+        <v>948</v>
       </c>
       <c r="I202" s="3">
-        <v>10585</v>
+        <v>10222</v>
       </c>
       <c r="W202" t="inlineStr">
         <is>
@@ -11754,30 +11749,30 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z202">
-        <v>59.920346</v>
+        <v>59.916973</v>
       </c>
       <c r="AA202">
-        <v>30.271233</v>
+        <v>30.265413</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z199</t>
+          <t xml:space="preserve">Z67</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Центральная проходная АО «Адмиралтейские верфи»</t>
+          <t xml:space="preserve">Административно-бытовой корпус</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Проходная, КПП</t>
+          <t xml:space="preserve">Административно-бытовой корпус</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -11786,19 +11781,19 @@
         </is>
       </c>
       <c r="E203">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F203">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G203">
-        <v>864</v>
+        <v>882</v>
       </c>
       <c r="H203" s="3">
-        <v>1729</v>
+        <v>2646</v>
       </c>
       <c r="I203" s="3">
-        <v>6915</v>
+        <v>10585</v>
       </c>
       <c r="W203" t="inlineStr">
         <is>
@@ -11812,30 +11807,30 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenStreetMap</t>
+          <t xml:space="preserve">карта предприятия</t>
         </is>
       </c>
       <c r="Z203">
-        <v>59.917265</v>
+        <v>59.920346</v>
       </c>
       <c r="AA203">
-        <v>30.277625</v>
+        <v>30.271233</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z141</t>
+          <t xml:space="preserve">Z199</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Административно-бытовой корпус</t>
+          <t xml:space="preserve">Центральная проходная АО «Адмиралтейские верфи»</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Административно-бытовой корпус</t>
+          <t xml:space="preserve">Проходная, КПП</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -11844,19 +11839,19 @@
         </is>
       </c>
       <c r="E204">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F204">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G204">
-        <v>810</v>
+        <v>864</v>
       </c>
       <c r="H204" s="3">
-        <v>2429</v>
+        <v>1729</v>
       </c>
       <c r="I204" s="3">
-        <v>9718</v>
+        <v>6915</v>
       </c>
       <c r="W204" t="inlineStr">
         <is>
@@ -11874,26 +11869,26 @@
         </is>
       </c>
       <c r="Z204">
-        <v>59.920024</v>
+        <v>59.917265</v>
       </c>
       <c r="AA204">
-        <v>30.273876</v>
+        <v>30.277625</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z43</t>
+          <t xml:space="preserve">Z141</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Склад</t>
+          <t xml:space="preserve">Административно-бытовой корпус</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Склад</t>
+          <t xml:space="preserve">Административно-бытовой корпус</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -11902,19 +11897,19 @@
         </is>
       </c>
       <c r="E205">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F205">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="G205">
-        <v>752</v>
-      </c>
-      <c r="H205">
-        <v>752</v>
+        <v>810</v>
+      </c>
+      <c r="H205" s="3">
+        <v>2429</v>
       </c>
       <c r="I205" s="3">
-        <v>7954</v>
+        <v>9718</v>
       </c>
       <c r="W205" t="inlineStr">
         <is>
@@ -11928,30 +11923,30 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z205">
-        <v>59.919915</v>
+        <v>59.920024</v>
       </c>
       <c r="AA205">
-        <v>30.270178</v>
+        <v>30.273876</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z117</t>
+          <t xml:space="preserve">Z43</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Канцелярия, чертёжная и бухгалтерия</t>
+          <t xml:space="preserve">Склад</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Административно-бытовой корпус</t>
+          <t xml:space="preserve">Склад</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -11960,19 +11955,19 @@
         </is>
       </c>
       <c r="E206">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F206">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="G206">
-        <v>533</v>
-      </c>
-      <c r="H206" s="3">
-        <v>1599</v>
+        <v>752</v>
+      </c>
+      <c r="H206">
+        <v>752</v>
       </c>
       <c r="I206" s="3">
-        <v>6398</v>
+        <v>7954</v>
       </c>
       <c r="W206" t="inlineStr">
         <is>
@@ -11986,30 +11981,30 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenStreetMap</t>
+          <t xml:space="preserve">карта предприятия</t>
         </is>
       </c>
       <c r="Z206">
-        <v>59.917356</v>
+        <v>59.919915</v>
       </c>
       <c r="AA206">
-        <v>30.271116</v>
+        <v>30.270178</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z174</t>
+          <t xml:space="preserve">Z117</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Склад</t>
+          <t xml:space="preserve">Канцелярия, чертёжная и бухгалтерия</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Склад</t>
+          <t xml:space="preserve">Административно-бытовой корпус</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -12018,19 +12013,19 @@
         </is>
       </c>
       <c r="E207">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F207">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="G207">
-        <v>526</v>
-      </c>
-      <c r="H207">
-        <v>526</v>
+        <v>533</v>
+      </c>
+      <c r="H207" s="3">
+        <v>1599</v>
       </c>
       <c r="I207" s="3">
-        <v>5395</v>
+        <v>6398</v>
       </c>
       <c r="W207" t="inlineStr">
         <is>
@@ -12048,26 +12043,26 @@
         </is>
       </c>
       <c r="Z207">
-        <v>59.917052</v>
+        <v>59.917356</v>
       </c>
       <c r="AA207">
-        <v>30.273775</v>
+        <v>30.271116</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z198</t>
+          <t xml:space="preserve">Z174</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Административно-бытовой корпус</t>
+          <t xml:space="preserve">Склад</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Административно-бытовой корпус</t>
+          <t xml:space="preserve">Склад</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -12076,19 +12071,19 @@
         </is>
       </c>
       <c r="E208">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F208">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="G208">
-        <v>506</v>
-      </c>
-      <c r="H208" s="3">
-        <v>1518</v>
+        <v>526</v>
+      </c>
+      <c r="H208">
+        <v>526</v>
       </c>
       <c r="I208" s="3">
-        <v>6071</v>
+        <v>5395</v>
       </c>
       <c r="W208" t="inlineStr">
         <is>
@@ -12106,26 +12101,26 @@
         </is>
       </c>
       <c r="Z208">
-        <v>59.916608</v>
+        <v>59.917052</v>
       </c>
       <c r="AA208">
-        <v>30.276732</v>
+        <v>30.273775</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z42</t>
+          <t xml:space="preserve">Z198</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вспомогательное здание</t>
+          <t xml:space="preserve">Административно-бытовой корпус</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вспомогательное здание</t>
+          <t xml:space="preserve">Административно-бытовой корпус</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -12134,19 +12129,19 @@
         </is>
       </c>
       <c r="E209">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F209">
-        <v>6.5</v>
+        <v>12</v>
       </c>
       <c r="G209">
-        <v>491</v>
-      </c>
-      <c r="H209">
-        <v>981</v>
+        <v>506</v>
+      </c>
+      <c r="H209" s="3">
+        <v>1518</v>
       </c>
       <c r="I209" s="3">
-        <v>3189</v>
+        <v>6071</v>
       </c>
       <c r="W209" t="inlineStr">
         <is>
@@ -12160,20 +12155,20 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z209">
-        <v>59.918025</v>
+        <v>59.916608</v>
       </c>
       <c r="AA209">
-        <v>30.269341</v>
+        <v>30.276732</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z142</t>
+          <t xml:space="preserve">Z42</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -12198,13 +12193,13 @@
         <v>6.5</v>
       </c>
       <c r="G210">
-        <v>441</v>
+        <v>491</v>
       </c>
       <c r="H210">
-        <v>882</v>
+        <v>981</v>
       </c>
       <c r="I210" s="3">
-        <v>2866</v>
+        <v>3189</v>
       </c>
       <c r="W210" t="inlineStr">
         <is>
@@ -12218,20 +12213,20 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenStreetMap</t>
+          <t xml:space="preserve">карта предприятия</t>
         </is>
       </c>
       <c r="Z210">
-        <v>59.920594</v>
+        <v>59.918025</v>
       </c>
       <c r="AA210">
-        <v>30.274176</v>
+        <v>30.269341</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z66</t>
+          <t xml:space="preserve">Z142</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -12256,13 +12251,13 @@
         <v>6.5</v>
       </c>
       <c r="G211">
-        <v>378</v>
+        <v>441</v>
       </c>
       <c r="H211">
-        <v>757</v>
+        <v>882</v>
       </c>
       <c r="I211" s="3">
-        <v>2460</v>
+        <v>2866</v>
       </c>
       <c r="W211" t="inlineStr">
         <is>
@@ -12280,21 +12275,21 @@
         </is>
       </c>
       <c r="Z211">
-        <v>59.919154</v>
+        <v>59.920594</v>
       </c>
       <c r="AA211">
-        <v>30.270439</v>
+        <v>30.274176</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t xml:space="preserve">N2</t>
+          <t xml:space="preserve">Z66</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Одноэтажное здание у Z162</t>
+          <t xml:space="preserve">Вспомогательное здание</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -12308,41 +12303,51 @@
         </is>
       </c>
       <c r="E212">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F212">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="G212">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="H212">
-        <v>376</v>
+        <v>757</v>
       </c>
       <c r="I212" s="3">
-        <v>1691</v>
+        <v>2460</v>
       </c>
       <c r="W212" t="inlineStr">
         <is>
           <t xml:space="preserve">Нет данных</t>
         </is>
       </c>
+      <c r="X212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OpenStreetMap</t>
+        </is>
+      </c>
       <c r="Z212">
-        <v>59.919602</v>
+        <v>59.919154</v>
       </c>
       <c r="AA212">
-        <v>30.274487</v>
+        <v>30.270439</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z10</t>
+          <t xml:space="preserve">N2</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вспомогательное здание</t>
+          <t xml:space="preserve">Одноэтажное здание у Z162</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -12356,46 +12361,36 @@
         </is>
       </c>
       <c r="E213">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F213">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="G213">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="H213">
-        <v>726</v>
+        <v>376</v>
       </c>
       <c r="I213" s="3">
-        <v>2360</v>
+        <v>1691</v>
       </c>
       <c r="W213" t="inlineStr">
         <is>
           <t xml:space="preserve">Нет данных</t>
         </is>
       </c>
-      <c r="X213" t="inlineStr">
-        <is>
-          <t xml:space="preserve">да</t>
-        </is>
-      </c>
-      <c r="Y213" t="inlineStr">
-        <is>
-          <t xml:space="preserve">карта предприятия</t>
-        </is>
-      </c>
       <c r="Z213">
-        <v>59.91841</v>
+        <v>59.919602</v>
       </c>
       <c r="AA213">
-        <v>30.266818</v>
+        <v>30.274487</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z29</t>
+          <t xml:space="preserve">Z10</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -12420,13 +12415,13 @@
         <v>6.5</v>
       </c>
       <c r="G214">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="H214">
-        <v>717</v>
+        <v>726</v>
       </c>
       <c r="I214" s="3">
-        <v>2331</v>
+        <v>2360</v>
       </c>
       <c r="W214" t="inlineStr">
         <is>
@@ -12440,20 +12435,20 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenStreetMap</t>
+          <t xml:space="preserve">карта предприятия</t>
         </is>
       </c>
       <c r="Z214">
-        <v>59.91623</v>
+        <v>59.91841</v>
       </c>
       <c r="AA214">
-        <v>30.267671</v>
+        <v>30.266818</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z134</t>
+          <t xml:space="preserve">Z29</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -12478,13 +12473,13 @@
         <v>6.5</v>
       </c>
       <c r="G215">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="H215">
-        <v>704</v>
+        <v>717</v>
       </c>
       <c r="I215" s="3">
-        <v>2289</v>
+        <v>2331</v>
       </c>
       <c r="W215" t="inlineStr">
         <is>
@@ -12502,16 +12497,16 @@
         </is>
       </c>
       <c r="Z215">
-        <v>59.919242</v>
+        <v>59.91623</v>
       </c>
       <c r="AA215">
-        <v>30.273115</v>
+        <v>30.267671</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z83</t>
+          <t xml:space="preserve">Z134</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -12536,13 +12531,13 @@
         <v>6.5</v>
       </c>
       <c r="G216">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="H216">
-        <v>693</v>
+        <v>704</v>
       </c>
       <c r="I216" s="3">
-        <v>2252</v>
+        <v>2289</v>
       </c>
       <c r="W216" t="inlineStr">
         <is>
@@ -12560,16 +12555,16 @@
         </is>
       </c>
       <c r="Z216">
-        <v>59.919041</v>
+        <v>59.919242</v>
       </c>
       <c r="AA216">
-        <v>30.271084</v>
+        <v>30.273115</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z79</t>
+          <t xml:space="preserve">Z83</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -12594,13 +12589,13 @@
         <v>6.5</v>
       </c>
       <c r="G217">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="H217">
-        <v>674</v>
+        <v>693</v>
       </c>
       <c r="I217" s="3">
-        <v>2191</v>
+        <v>2252</v>
       </c>
       <c r="W217" t="inlineStr">
         <is>
@@ -12614,20 +12609,20 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z217">
-        <v>59.916646</v>
+        <v>59.919041</v>
       </c>
       <c r="AA217">
-        <v>30.269619</v>
+        <v>30.271084</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z18</t>
+          <t xml:space="preserve">Z79</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -12652,13 +12647,13 @@
         <v>6.5</v>
       </c>
       <c r="G218">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="H218">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="I218" s="3">
-        <v>2174</v>
+        <v>2191</v>
       </c>
       <c r="W218" t="inlineStr">
         <is>
@@ -12672,20 +12667,20 @@
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Microsoft ML Buildings</t>
+          <t xml:space="preserve">карта предприятия</t>
         </is>
       </c>
       <c r="Z218">
-        <v>59.918178</v>
+        <v>59.916646</v>
       </c>
       <c r="AA218">
-        <v>30.268236</v>
+        <v>30.269619</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z122</t>
+          <t xml:space="preserve">Z18</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -12710,13 +12705,13 @@
         <v>6.5</v>
       </c>
       <c r="G219">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="H219">
-        <v>646</v>
+        <v>669</v>
       </c>
       <c r="I219" s="3">
-        <v>2099</v>
+        <v>2174</v>
       </c>
       <c r="W219" t="inlineStr">
         <is>
@@ -12730,20 +12725,20 @@
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenStreetMap</t>
+          <t xml:space="preserve">Microsoft ML Buildings</t>
         </is>
       </c>
       <c r="Z219">
-        <v>59.917663</v>
+        <v>59.918178</v>
       </c>
       <c r="AA219">
-        <v>30.271202</v>
+        <v>30.268236</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z25</t>
+          <t xml:space="preserve">Z122</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -12768,13 +12763,13 @@
         <v>6.5</v>
       </c>
       <c r="G220">
-        <v>270</v>
+        <v>323</v>
       </c>
       <c r="H220">
-        <v>540</v>
+        <v>646</v>
       </c>
       <c r="I220" s="3">
-        <v>1755</v>
+        <v>2099</v>
       </c>
       <c r="W220" t="inlineStr">
         <is>
@@ -12788,20 +12783,20 @@
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Microsoft ML Buildings</t>
+          <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z220">
-        <v>59.918074</v>
+        <v>59.917663</v>
       </c>
       <c r="AA220">
-        <v>30.268785</v>
+        <v>30.271202</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z98</t>
+          <t xml:space="preserve">Z25</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -12826,13 +12821,13 @@
         <v>6.5</v>
       </c>
       <c r="G221">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="H221">
-        <v>525</v>
+        <v>540</v>
       </c>
       <c r="I221" s="3">
-        <v>1706</v>
+        <v>1755</v>
       </c>
       <c r="W221" t="inlineStr">
         <is>
@@ -12850,16 +12845,16 @@
         </is>
       </c>
       <c r="Z221">
-        <v>59.917964</v>
+        <v>59.918074</v>
       </c>
       <c r="AA221">
-        <v>30.270548</v>
+        <v>30.268785</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z20</t>
+          <t xml:space="preserve">Z98</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -12887,10 +12882,10 @@
         <v>262</v>
       </c>
       <c r="H222">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="I222" s="3">
-        <v>1701</v>
+        <v>1706</v>
       </c>
       <c r="W222" t="inlineStr">
         <is>
@@ -12904,20 +12899,20 @@
       </c>
       <c r="Y222" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">Microsoft ML Buildings</t>
         </is>
       </c>
       <c r="Z222">
-        <v>59.919109</v>
+        <v>59.917964</v>
       </c>
       <c r="AA222">
-        <v>30.268844</v>
+        <v>30.270548</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y7ecd57</t>
+          <t xml:space="preserve">Z20</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -12942,13 +12937,13 @@
         <v>6.5</v>
       </c>
       <c r="G223">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="H223">
-        <v>490</v>
+        <v>523</v>
       </c>
       <c r="I223" s="3">
-        <v>1593</v>
+        <v>1701</v>
       </c>
       <c r="W223" t="inlineStr">
         <is>
@@ -12962,20 +12957,20 @@
       </c>
       <c r="Y223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Microsoft ML Buildings</t>
+          <t xml:space="preserve">карта предприятия</t>
         </is>
       </c>
       <c r="Z223">
-        <v>59.918443</v>
+        <v>59.919109</v>
       </c>
       <c r="AA223">
-        <v>30.267458</v>
+        <v>30.268844</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z157</t>
+          <t xml:space="preserve">Y7ecd57</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -13000,13 +12995,13 @@
         <v>6.5</v>
       </c>
       <c r="G224">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="H224">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="I224" s="3">
-        <v>1570</v>
+        <v>1593</v>
       </c>
       <c r="W224" t="inlineStr">
         <is>
@@ -13020,25 +13015,25 @@
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenStreetMap</t>
+          <t xml:space="preserve">Microsoft ML Buildings</t>
         </is>
       </c>
       <c r="Z224">
-        <v>59.920499</v>
+        <v>59.918443</v>
       </c>
       <c r="AA224">
-        <v>30.274833</v>
+        <v>30.267458</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z195</t>
+          <t xml:space="preserve">Z157</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Трансформаторная подстанция</t>
+          <t xml:space="preserve">Вспомогательное здание</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -13058,13 +13053,13 @@
         <v>6.5</v>
       </c>
       <c r="G225">
-        <v>204</v>
+        <v>242</v>
       </c>
       <c r="H225">
-        <v>408</v>
+        <v>483</v>
       </c>
       <c r="I225" s="3">
-        <v>1327</v>
+        <v>1570</v>
       </c>
       <c r="W225" t="inlineStr">
         <is>
@@ -13082,21 +13077,21 @@
         </is>
       </c>
       <c r="Z225">
-        <v>59.916787</v>
+        <v>59.920499</v>
       </c>
       <c r="AA225">
-        <v>30.276143</v>
+        <v>30.274833</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z19</t>
+          <t xml:space="preserve">Z195</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вспомогательное здание</t>
+          <t xml:space="preserve">Трансформаторная подстанция</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -13116,13 +13111,13 @@
         <v>6.5</v>
       </c>
       <c r="G226">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H226">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="I226" s="3">
-        <v>1320</v>
+        <v>1327</v>
       </c>
       <c r="W226" t="inlineStr">
         <is>
@@ -13136,20 +13131,20 @@
       </c>
       <c r="Y226" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z226">
-        <v>59.917016</v>
+        <v>59.916787</v>
       </c>
       <c r="AA226">
-        <v>30.267698</v>
+        <v>30.276143</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z49</t>
+          <t xml:space="preserve">Z19</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -13168,19 +13163,19 @@
         </is>
       </c>
       <c r="E227">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F227">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="G227">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="H227">
-        <v>190</v>
-      </c>
-      <c r="I227">
-        <v>857</v>
+        <v>406</v>
+      </c>
+      <c r="I227" s="3">
+        <v>1320</v>
       </c>
       <c r="W227" t="inlineStr">
         <is>
@@ -13198,21 +13193,21 @@
         </is>
       </c>
       <c r="Z227">
-        <v>59.920428</v>
+        <v>59.917016</v>
       </c>
       <c r="AA227">
-        <v>30.27058</v>
+        <v>30.267698</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z16</t>
+          <t xml:space="preserve">Yb16555</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вспомогательное здание</t>
+          <t xml:space="preserve">Пристройка у северного торца заводоуправления</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -13226,46 +13221,41 @@
         </is>
       </c>
       <c r="E228">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F228">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="G228">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="H228">
-        <v>361</v>
-      </c>
-      <c r="I228" s="3">
-        <v>1173</v>
+        <v>194</v>
+      </c>
+      <c r="I228">
+        <v>776</v>
       </c>
       <c r="W228" t="inlineStr">
         <is>
           <t xml:space="preserve">Нет данных</t>
         </is>
       </c>
-      <c r="X228" t="inlineStr">
-        <is>
-          <t xml:space="preserve">да</t>
-        </is>
-      </c>
       <c r="Y228" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z228">
-        <v>59.917091</v>
+        <v>59.918785</v>
       </c>
       <c r="AA228">
-        <v>30.267237</v>
+        <v>30.27544</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y4f6129</t>
+          <t xml:space="preserve">Z49</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -13284,19 +13274,19 @@
         </is>
       </c>
       <c r="E229">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F229">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="G229">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="H229">
-        <v>347</v>
-      </c>
-      <c r="I229" s="3">
-        <v>1129</v>
+        <v>190</v>
+      </c>
+      <c r="I229">
+        <v>857</v>
       </c>
       <c r="W229" t="inlineStr">
         <is>
@@ -13310,30 +13300,30 @@
       </c>
       <c r="Y229" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenStreetMap</t>
+          <t xml:space="preserve">карта предприятия</t>
         </is>
       </c>
       <c r="Z229">
-        <v>59.921035</v>
+        <v>59.920428</v>
       </c>
       <c r="AA229">
-        <v>30.271017</v>
+        <v>30.27058</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z161</t>
+          <t xml:space="preserve">Z16</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Служебное здание у часовни</t>
+          <t xml:space="preserve">Вспомогательное здание</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Историческое здание</t>
+          <t xml:space="preserve">Вспомогательное здание</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -13342,41 +13332,46 @@
         </is>
       </c>
       <c r="E230">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F230">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="G230">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="H230">
-        <v>157</v>
-      </c>
-      <c r="I230">
-        <v>785</v>
+        <v>361</v>
+      </c>
+      <c r="I230" s="3">
+        <v>1173</v>
       </c>
       <c r="W230" t="inlineStr">
         <is>
           <t xml:space="preserve">Нет данных</t>
         </is>
       </c>
+      <c r="X230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
       <c r="Y230" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenStreetMap</t>
+          <t xml:space="preserve">карта предприятия</t>
         </is>
       </c>
       <c r="Z230">
-        <v>59.931366</v>
+        <v>59.917091</v>
       </c>
       <c r="AA230">
-        <v>30.282141</v>
+        <v>30.267237</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y43a4c5</t>
+          <t xml:space="preserve">Y4f6129</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -13395,19 +13390,19 @@
         </is>
       </c>
       <c r="E231">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F231">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="G231">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="H231">
-        <v>141</v>
-      </c>
-      <c r="I231">
-        <v>636</v>
+        <v>347</v>
+      </c>
+      <c r="I231" s="3">
+        <v>1129</v>
       </c>
       <c r="W231" t="inlineStr">
         <is>
@@ -13421,30 +13416,30 @@
       </c>
       <c r="Y231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Microsoft ML Buildings</t>
+          <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z231">
-        <v>59.91832</v>
+        <v>59.921035</v>
       </c>
       <c r="AA231">
-        <v>30.268162</v>
+        <v>30.271017</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ya0f72e</t>
+          <t xml:space="preserve">Z161</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вспомогательное здание</t>
+          <t xml:space="preserve">Служебное здание у часовни</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вспомогательное здание</t>
+          <t xml:space="preserve">Историческое здание</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -13456,43 +13451,38 @@
         <v>1</v>
       </c>
       <c r="F232">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="G232">
-        <v>113</v>
+        <v>157</v>
       </c>
       <c r="H232">
-        <v>113</v>
+        <v>157</v>
       </c>
       <c r="I232">
-        <v>507</v>
+        <v>785</v>
       </c>
       <c r="W232" t="inlineStr">
         <is>
           <t xml:space="preserve">Нет данных</t>
         </is>
       </c>
-      <c r="X232" t="inlineStr">
-        <is>
-          <t xml:space="preserve">да</t>
-        </is>
-      </c>
       <c r="Y232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Microsoft ML Buildings</t>
+          <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z232">
-        <v>59.918837</v>
+        <v>59.931366</v>
       </c>
       <c r="AA232">
-        <v>30.269144</v>
+        <v>30.282141</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yf9aefe</t>
+          <t xml:space="preserve">Y43a4c5</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -13517,13 +13507,13 @@
         <v>4.5</v>
       </c>
       <c r="G233">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="H233">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="I233">
-        <v>507</v>
+        <v>636</v>
       </c>
       <c r="W233" t="inlineStr">
         <is>
@@ -13541,16 +13531,16 @@
         </is>
       </c>
       <c r="Z233">
-        <v>59.919075</v>
+        <v>59.91832</v>
       </c>
       <c r="AA233">
-        <v>30.272368</v>
+        <v>30.268162</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y3f0129</t>
+          <t xml:space="preserve">Ya0f72e</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -13575,13 +13565,13 @@
         <v>4.5</v>
       </c>
       <c r="G234">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="H234">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="I234">
-        <v>467</v>
+        <v>507</v>
       </c>
       <c r="W234" t="inlineStr">
         <is>
@@ -13599,16 +13589,16 @@
         </is>
       </c>
       <c r="Z234">
-        <v>59.917315</v>
+        <v>59.918837</v>
       </c>
       <c r="AA234">
-        <v>30.265637</v>
+        <v>30.269144</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z6</t>
+          <t xml:space="preserve">Yf9aefe</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -13633,13 +13623,13 @@
         <v>4.5</v>
       </c>
       <c r="G235">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="H235">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="I235">
-        <v>469</v>
+        <v>507</v>
       </c>
       <c r="W235" t="inlineStr">
         <is>
@@ -13653,20 +13643,20 @@
       </c>
       <c r="Y235" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenStreetMap</t>
+          <t xml:space="preserve">Microsoft ML Buildings</t>
         </is>
       </c>
       <c r="Z235">
-        <v>59.916734</v>
+        <v>59.919075</v>
       </c>
       <c r="AA235">
-        <v>30.265018</v>
+        <v>30.272368</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z15</t>
+          <t xml:space="preserve">Y3f0129</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -13691,13 +13681,13 @@
         <v>4.5</v>
       </c>
       <c r="G236">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H236">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I236">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="W236" t="inlineStr">
         <is>
@@ -13711,20 +13701,20 @@
       </c>
       <c r="Y236" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">Microsoft ML Buildings</t>
         </is>
       </c>
       <c r="Z236">
-        <v>59.918251</v>
+        <v>59.917315</v>
       </c>
       <c r="AA236">
-        <v>30.267724</v>
+        <v>30.265637</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z12</t>
+          <t xml:space="preserve">Z6</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -13749,13 +13739,13 @@
         <v>4.5</v>
       </c>
       <c r="G237">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H237">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="I237">
-        <v>446</v>
+        <v>469</v>
       </c>
       <c r="W237" t="inlineStr">
         <is>
@@ -13769,20 +13759,20 @@
       </c>
       <c r="Y237" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z237">
-        <v>59.918314</v>
+        <v>59.916734</v>
       </c>
       <c r="AA237">
-        <v>30.267323</v>
+        <v>30.265018</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y24c47e</t>
+          <t xml:space="preserve">Z15</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -13807,13 +13797,13 @@
         <v>4.5</v>
       </c>
       <c r="G238">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="H238">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="I238">
-        <v>438</v>
+        <v>462</v>
       </c>
       <c r="W238" t="inlineStr">
         <is>
@@ -13827,20 +13817,20 @@
       </c>
       <c r="Y238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Microsoft ML Buildings</t>
+          <t xml:space="preserve">карта предприятия</t>
         </is>
       </c>
       <c r="Z238">
-        <v>59.918802</v>
+        <v>59.918251</v>
       </c>
       <c r="AA238">
-        <v>30.272684</v>
+        <v>30.267724</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z78</t>
+          <t xml:space="preserve">Z12</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -13865,13 +13855,13 @@
         <v>4.5</v>
       </c>
       <c r="G239">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="H239">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="I239">
-        <v>360</v>
+        <v>446</v>
       </c>
       <c r="W239" t="inlineStr">
         <is>
@@ -13889,21 +13879,21 @@
         </is>
       </c>
       <c r="Z239">
-        <v>59.916289</v>
+        <v>59.918314</v>
       </c>
       <c r="AA239">
-        <v>30.269171</v>
+        <v>30.267323</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y39fdef</t>
+          <t xml:space="preserve">Y24c47e</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Техническое здание</t>
+          <t xml:space="preserve">Вспомогательное здание</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -13923,13 +13913,13 @@
         <v>4.5</v>
       </c>
       <c r="G240">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="H240">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="I240">
-        <v>335</v>
+        <v>438</v>
       </c>
       <c r="W240" t="inlineStr">
         <is>
@@ -13943,20 +13933,20 @@
       </c>
       <c r="Y240" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenStreetMap</t>
+          <t xml:space="preserve">Microsoft ML Buildings</t>
         </is>
       </c>
       <c r="Z240">
-        <v>59.916869</v>
+        <v>59.918802</v>
       </c>
       <c r="AA240">
-        <v>30.276026</v>
+        <v>30.272684</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y97543d</t>
+          <t xml:space="preserve">Z78</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -13981,13 +13971,13 @@
         <v>4.5</v>
       </c>
       <c r="G241">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="H241">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="I241">
-        <v>301</v>
+        <v>360</v>
       </c>
       <c r="W241" t="inlineStr">
         <is>
@@ -14001,25 +13991,25 @@
       </c>
       <c r="Y241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Microsoft ML Buildings</t>
+          <t xml:space="preserve">карта предприятия</t>
         </is>
       </c>
       <c r="Z241">
-        <v>59.91616</v>
+        <v>59.916289</v>
       </c>
       <c r="AA241">
-        <v>30.266067</v>
+        <v>30.269171</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yb90624</t>
+          <t xml:space="preserve">Y39fdef</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вспомогательное здание</t>
+          <t xml:space="preserve">Техническое здание</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -14039,13 +14029,13 @@
         <v>4.5</v>
       </c>
       <c r="G242">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="H242">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="I242">
-        <v>285</v>
+        <v>335</v>
       </c>
       <c r="W242" t="inlineStr">
         <is>
@@ -14059,20 +14049,20 @@
       </c>
       <c r="Y242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Microsoft ML Buildings</t>
+          <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z242">
-        <v>59.918887</v>
+        <v>59.916869</v>
       </c>
       <c r="AA242">
-        <v>30.272798</v>
+        <v>30.276026</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y6ae3a7</t>
+          <t xml:space="preserve">Y97543d</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -14097,13 +14087,13 @@
         <v>4.5</v>
       </c>
       <c r="G243">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="H243">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="I243">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="W243" t="inlineStr">
         <is>
@@ -14121,16 +14111,16 @@
         </is>
       </c>
       <c r="Z243">
-        <v>59.917264</v>
+        <v>59.91616</v>
       </c>
       <c r="AA243">
-        <v>30.273049</v>
+        <v>30.266067</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y64b17f</t>
+          <t xml:space="preserve">Yb90624</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -14155,13 +14145,13 @@
         <v>4.5</v>
       </c>
       <c r="G244">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="H244">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="I244">
-        <v>250</v>
+        <v>285</v>
       </c>
       <c r="W244" t="inlineStr">
         <is>
@@ -14179,16 +14169,16 @@
         </is>
       </c>
       <c r="Z244">
-        <v>59.920224</v>
+        <v>59.918887</v>
       </c>
       <c r="AA244">
-        <v>30.270423</v>
+        <v>30.272798</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y8ec98b</t>
+          <t xml:space="preserve">Y6ae3a7</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -14213,13 +14203,13 @@
         <v>4.5</v>
       </c>
       <c r="G245">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H245">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="I245">
-        <v>237</v>
+        <v>262</v>
       </c>
       <c r="W245" t="inlineStr">
         <is>
@@ -14237,16 +14227,16 @@
         </is>
       </c>
       <c r="Z245">
-        <v>59.916248</v>
+        <v>59.917264</v>
       </c>
       <c r="AA245">
-        <v>30.266045</v>
+        <v>30.273049</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z86</t>
+          <t xml:space="preserve">Y64b17f</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -14271,13 +14261,13 @@
         <v>4.5</v>
       </c>
       <c r="G246">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H246">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I246">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="W246" t="inlineStr">
         <is>
@@ -14295,21 +14285,21 @@
         </is>
       </c>
       <c r="Z246">
-        <v>59.917903</v>
+        <v>59.920224</v>
       </c>
       <c r="AA246">
-        <v>30.270279</v>
+        <v>30.270423</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y536a17</t>
+          <t xml:space="preserve">Y8ec98b</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Часовня храма «Спас-на-Водах»</t>
+          <t xml:space="preserve">Вспомогательное здание</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -14326,38 +14316,43 @@
         <v>1</v>
       </c>
       <c r="F247">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="G247">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H247">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I247">
-        <v>199</v>
+        <v>237</v>
       </c>
       <c r="W247" t="inlineStr">
         <is>
           <t xml:space="preserve">Нет данных</t>
         </is>
       </c>
+      <c r="X247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
       <c r="Y247" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenStreetMap</t>
+          <t xml:space="preserve">Microsoft ML Buildings</t>
         </is>
       </c>
       <c r="Z247">
-        <v>59.931521</v>
+        <v>59.916248</v>
       </c>
       <c r="AA247">
-        <v>30.281789</v>
+        <v>30.266045</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y91523f</t>
+          <t xml:space="preserve">Z86</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -14382,13 +14377,13 @@
         <v>4.5</v>
       </c>
       <c r="G248">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="H248">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="I248">
-        <v>212</v>
+        <v>240</v>
       </c>
       <c r="W248" t="inlineStr">
         <is>
@@ -14406,21 +14401,21 @@
         </is>
       </c>
       <c r="Z248">
-        <v>59.916955</v>
+        <v>59.917903</v>
       </c>
       <c r="AA248">
-        <v>30.268761</v>
+        <v>30.270279</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y459669</t>
+          <t xml:space="preserve">Y536a17</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вспомогательное здание</t>
+          <t xml:space="preserve">Часовня храма «Спас-на-Водах»</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -14437,43 +14432,38 @@
         <v>1</v>
       </c>
       <c r="F249">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="G249">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H249">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="I249">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="W249" t="inlineStr">
         <is>
           <t xml:space="preserve">Нет данных</t>
         </is>
       </c>
-      <c r="X249" t="inlineStr">
-        <is>
-          <t xml:space="preserve">да</t>
-        </is>
-      </c>
       <c r="Y249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Microsoft ML Buildings</t>
+          <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z249">
-        <v>59.918267</v>
+        <v>59.931521</v>
       </c>
       <c r="AA249">
-        <v>30.268037</v>
+        <v>30.281789</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y7fa697</t>
+          <t xml:space="preserve">Y91523f</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -14498,13 +14488,13 @@
         <v>4.5</v>
       </c>
       <c r="G250">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="H250">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="I250">
-        <v>177</v>
+        <v>212</v>
       </c>
       <c r="W250" t="inlineStr">
         <is>
@@ -14518,20 +14508,20 @@
       </c>
       <c r="Y250" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenStreetMap</t>
+          <t xml:space="preserve">Microsoft ML Buildings</t>
         </is>
       </c>
       <c r="Z250">
-        <v>59.916091</v>
+        <v>59.916955</v>
       </c>
       <c r="AA250">
-        <v>30.270079</v>
+        <v>30.268761</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y604d03</t>
+          <t xml:space="preserve">Y459669</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -14556,13 +14546,13 @@
         <v>4.5</v>
       </c>
       <c r="G251">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H251">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="I251">
-        <v>161</v>
+        <v>203</v>
       </c>
       <c r="W251" t="inlineStr">
         <is>
@@ -14580,21 +14570,21 @@
         </is>
       </c>
       <c r="Z251">
-        <v>59.919335</v>
+        <v>59.918267</v>
       </c>
       <c r="AA251">
-        <v>30.268958</v>
+        <v>30.268037</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ye48a35</t>
+          <t xml:space="preserve">Y7fa697</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Техническое здание</t>
+          <t xml:space="preserve">Вспомогательное здание</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -14614,13 +14604,13 @@
         <v>4.5</v>
       </c>
       <c r="G252">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H252">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I252">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="W252" t="inlineStr">
         <is>
@@ -14634,20 +14624,20 @@
       </c>
       <c r="Y252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Microsoft ML Buildings</t>
+          <t xml:space="preserve">OpenStreetMap</t>
         </is>
       </c>
       <c r="Z252">
-        <v>59.916893</v>
+        <v>59.916091</v>
       </c>
       <c r="AA252">
-        <v>30.276229</v>
+        <v>30.270079</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y1a50d5</t>
+          <t xml:space="preserve">Y604d03</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -14672,13 +14662,13 @@
         <v>4.5</v>
       </c>
       <c r="G253">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H253">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I253">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="W253" t="inlineStr">
         <is>
@@ -14696,21 +14686,21 @@
         </is>
       </c>
       <c r="Z253">
-        <v>59.917883</v>
+        <v>59.919335</v>
       </c>
       <c r="AA253">
-        <v>30.266264</v>
+        <v>30.268958</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y33cd36</t>
+          <t xml:space="preserve">Ye48a35</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вспомогательное здание</t>
+          <t xml:space="preserve">Техническое здание</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -14730,13 +14720,13 @@
         <v>4.5</v>
       </c>
       <c r="G254">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H254">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I254">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="W254" t="inlineStr">
         <is>
@@ -14754,16 +14744,16 @@
         </is>
       </c>
       <c r="Z254">
-        <v>59.916815</v>
+        <v>59.916893</v>
       </c>
       <c r="AA254">
-        <v>30.265001</v>
+        <v>30.276229</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yac22bc</t>
+          <t xml:space="preserve">Y1a50d5</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -14788,13 +14778,13 @@
         <v>4.5</v>
       </c>
       <c r="G255">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H255">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I255">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="W255" t="inlineStr">
         <is>
@@ -14812,16 +14802,16 @@
         </is>
       </c>
       <c r="Z255">
-        <v>59.916682</v>
+        <v>59.917883</v>
       </c>
       <c r="AA255">
-        <v>30.269965</v>
+        <v>30.266264</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yba1032</t>
+          <t xml:space="preserve">Y33cd36</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -14846,13 +14836,13 @@
         <v>4.5</v>
       </c>
       <c r="G256">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H256">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I256">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="W256" t="inlineStr">
         <is>
@@ -14870,16 +14860,16 @@
         </is>
       </c>
       <c r="Z256">
-        <v>59.917812</v>
+        <v>59.916815</v>
       </c>
       <c r="AA256">
-        <v>30.266622</v>
+        <v>30.265001</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y8ef773</t>
+          <t xml:space="preserve">Yac22bc</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -14904,13 +14894,13 @@
         <v>4.5</v>
       </c>
       <c r="G257">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H257">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I257">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="W257" t="inlineStr">
         <is>
@@ -14928,16 +14918,16 @@
         </is>
       </c>
       <c r="Z257">
-        <v>59.917792</v>
+        <v>59.916682</v>
       </c>
       <c r="AA257">
-        <v>30.271182</v>
+        <v>30.269965</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y5f32ee</t>
+          <t xml:space="preserve">Yba1032</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -14962,13 +14952,13 @@
         <v>4.5</v>
       </c>
       <c r="G258">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H258">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I258">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="W258" t="inlineStr">
         <is>
@@ -14986,16 +14976,16 @@
         </is>
       </c>
       <c r="Z258">
-        <v>59.918398</v>
+        <v>59.917812</v>
       </c>
       <c r="AA258">
-        <v>30.267786</v>
+        <v>30.266622</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y0af2fb</t>
+          <t xml:space="preserve">Y8ef773</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -15020,13 +15010,13 @@
         <v>4.5</v>
       </c>
       <c r="G259">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H259">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I259">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="W259" t="inlineStr">
         <is>
@@ -15044,16 +15034,16 @@
         </is>
       </c>
       <c r="Z259">
-        <v>59.918313</v>
+        <v>59.917792</v>
       </c>
       <c r="AA259">
-        <v>30.266511</v>
+        <v>30.271182</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y289bd5</t>
+          <t xml:space="preserve">Y5f32ee</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -15078,13 +15068,13 @@
         <v>4.5</v>
       </c>
       <c r="G260">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H260">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I260">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="W260" t="inlineStr">
         <is>
@@ -15102,16 +15092,16 @@
         </is>
       </c>
       <c r="Z260">
-        <v>59.918011</v>
+        <v>59.918398</v>
       </c>
       <c r="AA260">
-        <v>30.275561</v>
+        <v>30.267786</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y2cf1c4</t>
+          <t xml:space="preserve">Y0af2fb</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -15136,13 +15126,13 @@
         <v>4.5</v>
       </c>
       <c r="G261">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H261">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I261">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="W261" t="inlineStr">
         <is>
@@ -15160,16 +15150,16 @@
         </is>
       </c>
       <c r="Z261">
-        <v>59.920802</v>
+        <v>59.918313</v>
       </c>
       <c r="AA261">
-        <v>30.270869</v>
+        <v>30.266511</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ye86f38</t>
+          <t xml:space="preserve">Y289bd5</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -15194,13 +15184,13 @@
         <v>4.5</v>
       </c>
       <c r="G262">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H262">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I262">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="W262" t="inlineStr">
         <is>
@@ -15218,16 +15208,16 @@
         </is>
       </c>
       <c r="Z262">
-        <v>59.917665</v>
+        <v>59.918011</v>
       </c>
       <c r="AA262">
-        <v>30.267606</v>
+        <v>30.275561</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y842542</t>
+          <t xml:space="preserve">Y2cf1c4</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -15252,13 +15242,13 @@
         <v>4.5</v>
       </c>
       <c r="G263">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H263">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I263">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="W263" t="inlineStr">
         <is>
@@ -15276,16 +15266,16 @@
         </is>
       </c>
       <c r="Z263">
-        <v>59.916201</v>
+        <v>59.920802</v>
       </c>
       <c r="AA263">
-        <v>30.268012</v>
+        <v>30.270869</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ya14596</t>
+          <t xml:space="preserve">Ye86f38</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -15316,7 +15306,7 @@
         <v>19</v>
       </c>
       <c r="I264">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="W264" t="inlineStr">
         <is>
@@ -15334,16 +15324,16 @@
         </is>
       </c>
       <c r="Z264">
-        <v>59.917193</v>
+        <v>59.917665</v>
       </c>
       <c r="AA264">
-        <v>30.272902</v>
+        <v>30.267606</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yd8176d</t>
+          <t xml:space="preserve">Y842542</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -15368,13 +15358,13 @@
         <v>4.5</v>
       </c>
       <c r="G265">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H265">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I265">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="W265" t="inlineStr">
         <is>
@@ -15392,16 +15382,16 @@
         </is>
       </c>
       <c r="Z265">
-        <v>59.920319</v>
+        <v>59.916201</v>
       </c>
       <c r="AA265">
-        <v>30.270815</v>
+        <v>30.268012</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y8819d9</t>
+          <t xml:space="preserve">Ya14596</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -15426,13 +15416,13 @@
         <v>4.5</v>
       </c>
       <c r="G266">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H266">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I266">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="W266" t="inlineStr">
         <is>
@@ -15450,16 +15440,16 @@
         </is>
       </c>
       <c r="Z266">
-        <v>59.918745</v>
+        <v>59.917193</v>
       </c>
       <c r="AA266">
-        <v>30.273317</v>
+        <v>30.272902</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yc9cd64</t>
+          <t xml:space="preserve">Yd8176d</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -15490,7 +15480,7 @@
         <v>16</v>
       </c>
       <c r="I267">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="W267" t="inlineStr">
         <is>
@@ -15508,16 +15498,16 @@
         </is>
       </c>
       <c r="Z267">
-        <v>59.919104</v>
+        <v>59.920319</v>
       </c>
       <c r="AA267">
-        <v>30.272734</v>
+        <v>30.270815</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y9f3807</t>
+          <t xml:space="preserve">Y8819d9</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -15542,13 +15532,13 @@
         <v>4.5</v>
       </c>
       <c r="G268">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H268">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I268">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="W268" t="inlineStr">
         <is>
@@ -15566,16 +15556,16 @@
         </is>
       </c>
       <c r="Z268">
-        <v>59.91927</v>
+        <v>59.918745</v>
       </c>
       <c r="AA268">
-        <v>30.268932</v>
+        <v>30.273317</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z139</t>
+          <t xml:space="preserve">Yc9cd64</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -15600,13 +15590,13 @@
         <v>4.5</v>
       </c>
       <c r="G269">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H269">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I269">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="W269" t="inlineStr">
         <is>
@@ -15624,16 +15614,16 @@
         </is>
       </c>
       <c r="Z269">
-        <v>59.918826</v>
+        <v>59.919104</v>
       </c>
       <c r="AA269">
-        <v>30.273003</v>
+        <v>30.272734</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yc94432</t>
+          <t xml:space="preserve">Y9f3807</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -15664,7 +15654,7 @@
         <v>15</v>
       </c>
       <c r="I270">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="W270" t="inlineStr">
         <is>
@@ -15682,16 +15672,16 @@
         </is>
       </c>
       <c r="Z270">
-        <v>59.917389</v>
+        <v>59.91927</v>
       </c>
       <c r="AA270">
-        <v>30.27673</v>
+        <v>30.268932</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y11bd95</t>
+          <t xml:space="preserve">Z139</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -15716,13 +15706,13 @@
         <v>4.5</v>
       </c>
       <c r="G271">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H271">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I271">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="W271" t="inlineStr">
         <is>
@@ -15740,16 +15730,16 @@
         </is>
       </c>
       <c r="Z271">
-        <v>59.920819</v>
+        <v>59.918826</v>
       </c>
       <c r="AA271">
-        <v>30.270751</v>
+        <v>30.273003</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y8d968a</t>
+          <t xml:space="preserve">Yc94432</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -15774,13 +15764,13 @@
         <v>4.5</v>
       </c>
       <c r="G272">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H272">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I272">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="W272" t="inlineStr">
         <is>
@@ -15798,16 +15788,16 @@
         </is>
       </c>
       <c r="Z272">
-        <v>59.919203</v>
+        <v>59.917389</v>
       </c>
       <c r="AA272">
-        <v>30.272331</v>
+        <v>30.27673</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y8cb1f5</t>
+          <t xml:space="preserve">Y11bd95</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -15856,16 +15846,16 @@
         </is>
       </c>
       <c r="Z273">
-        <v>59.917333</v>
+        <v>59.920819</v>
       </c>
       <c r="AA273">
-        <v>30.276728</v>
+        <v>30.270751</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ya7ebb7</t>
+          <t xml:space="preserve">Y8d968a</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -15890,13 +15880,13 @@
         <v>4.5</v>
       </c>
       <c r="G274">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H274">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I274">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="W274" t="inlineStr">
         <is>
@@ -15914,16 +15904,16 @@
         </is>
       </c>
       <c r="Z274">
-        <v>59.917716</v>
+        <v>59.919203</v>
       </c>
       <c r="AA274">
-        <v>30.267397</v>
+        <v>30.272331</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ydee944</t>
+          <t xml:space="preserve">Y8cb1f5</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -15948,13 +15938,13 @@
         <v>4.5</v>
       </c>
       <c r="G275">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H275">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I275">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="W275" t="inlineStr">
         <is>
@@ -15972,16 +15962,16 @@
         </is>
       </c>
       <c r="Z275">
-        <v>59.916563</v>
+        <v>59.917333</v>
       </c>
       <c r="AA275">
-        <v>30.265103</v>
+        <v>30.276728</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y56dd04</t>
+          <t xml:space="preserve">Ya7ebb7</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -16006,13 +15996,13 @@
         <v>4.5</v>
       </c>
       <c r="G276">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H276">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I276">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="W276" t="inlineStr">
         <is>
@@ -16030,16 +16020,16 @@
         </is>
       </c>
       <c r="Z276">
-        <v>59.916593</v>
+        <v>59.917716</v>
       </c>
       <c r="AA276">
-        <v>30.26494</v>
+        <v>30.267397</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y350b1e</t>
+          <t xml:space="preserve">Ydee944</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -16070,7 +16060,7 @@
         <v>11</v>
       </c>
       <c r="I277">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="W277" t="inlineStr">
         <is>
@@ -16088,16 +16078,16 @@
         </is>
       </c>
       <c r="Z277">
-        <v>59.916464</v>
+        <v>59.916563</v>
       </c>
       <c r="AA277">
-        <v>30.269654</v>
+        <v>30.265103</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y064ef1</t>
+          <t xml:space="preserve">Y56dd04</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -16128,7 +16118,7 @@
         <v>11</v>
       </c>
       <c r="I278">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="W278" t="inlineStr">
         <is>
@@ -16146,16 +16136,16 @@
         </is>
       </c>
       <c r="Z278">
-        <v>59.917185</v>
+        <v>59.916593</v>
       </c>
       <c r="AA278">
-        <v>30.273003</v>
+        <v>30.26494</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y530046</t>
+          <t xml:space="preserve">Y350b1e</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -16180,13 +16170,13 @@
         <v>4.5</v>
       </c>
       <c r="G279">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H279">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I279">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="W279" t="inlineStr">
         <is>
@@ -16204,16 +16194,16 @@
         </is>
       </c>
       <c r="Z279">
-        <v>59.916594</v>
+        <v>59.916464</v>
       </c>
       <c r="AA279">
-        <v>30.265234</v>
+        <v>30.269654</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yead4a4</t>
+          <t xml:space="preserve">Y064ef1</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -16238,13 +16228,13 @@
         <v>4.5</v>
       </c>
       <c r="G280">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H280">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I280">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="W280" t="inlineStr">
         <is>
@@ -16262,16 +16252,16 @@
         </is>
       </c>
       <c r="Z280">
-        <v>59.918206</v>
+        <v>59.917185</v>
       </c>
       <c r="AA280">
-        <v>30.268907</v>
+        <v>30.273003</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ya7ddb4</t>
+          <t xml:space="preserve">Y530046</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -16302,7 +16292,7 @@
         <v>10</v>
       </c>
       <c r="I281">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="W281" t="inlineStr">
         <is>
@@ -16320,101 +16310,149 @@
         </is>
       </c>
       <c r="Z281">
-        <v>59.920157</v>
+        <v>59.916594</v>
       </c>
       <c r="AA281">
-        <v>30.273581</v>
+        <v>30.265234</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">Yead4a4</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Плавучий док «Луга»</t>
+          <t xml:space="preserve">Вспомогательное здание</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Плавучий док</t>
-        </is>
+          <t xml:space="preserve">Вспомогательное здание</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Основная площадка</t>
+        </is>
+      </c>
+      <c r="E282">
+        <v>1</v>
       </c>
       <c r="F282">
-        <v>14</v>
-      </c>
-      <c r="G282" s="3">
-        <v>2484</v>
+        <v>4.5</v>
+      </c>
+      <c r="G282">
+        <v>10</v>
+      </c>
+      <c r="H282">
+        <v>10</v>
+      </c>
+      <c r="I282">
+        <v>46</v>
       </c>
       <c r="W282" t="inlineStr">
         <is>
           <t xml:space="preserve">Нет данных</t>
         </is>
       </c>
+      <c r="X282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+      <c r="Y282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Microsoft ML Buildings</t>
+        </is>
+      </c>
       <c r="Z282">
-        <v>59.930184</v>
+        <v>59.918206</v>
       </c>
       <c r="AA282">
-        <v>30.27568</v>
+        <v>30.268907</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">Ya7ddb4</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Плавучий док СПД-2М</t>
+          <t xml:space="preserve">Вспомогательное здание</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Плавучий док</t>
-        </is>
+          <t xml:space="preserve">Вспомогательное здание</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Основная площадка</t>
+        </is>
+      </c>
+      <c r="E283">
+        <v>1</v>
       </c>
       <c r="F283">
-        <v>14</v>
-      </c>
-      <c r="G283" s="3">
-        <v>2024</v>
+        <v>4.5</v>
+      </c>
+      <c r="G283">
+        <v>10</v>
+      </c>
+      <c r="H283">
+        <v>10</v>
+      </c>
+      <c r="I283">
+        <v>47</v>
       </c>
       <c r="W283" t="inlineStr">
         <is>
           <t xml:space="preserve">Нет данных</t>
         </is>
       </c>
+      <c r="X283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">да</t>
+        </is>
+      </c>
+      <c r="Y283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Microsoft ML Buildings</t>
+        </is>
+      </c>
       <c r="Z283">
-        <v>59.920492</v>
+        <v>59.920157</v>
       </c>
       <c r="AA283">
-        <v>30.269747</v>
+        <v>30.273581</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t xml:space="preserve">MB4</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Причальный мост над устьем Пряжки</t>
+          <t xml:space="preserve">Плавучий док «Луга»</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Заводской мост (сооружение)</t>
+          <t xml:space="preserve">Плавучий док</t>
         </is>
       </c>
       <c r="F284">
-        <v>3</v>
-      </c>
-      <c r="G284">
-        <v>722</v>
+        <v>14</v>
+      </c>
+      <c r="G284" s="3">
+        <v>2484</v>
       </c>
       <c r="W284" t="inlineStr">
         <is>
@@ -16422,33 +16460,33 @@
         </is>
       </c>
       <c r="Z284">
-        <v>59.921307</v>
+        <v>59.930184</v>
       </c>
       <c r="AA284">
-        <v>30.270857</v>
+        <v>30.27568</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Галерный мост</t>
+          <t xml:space="preserve">Плавучий док СПД-2М</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Заводской мост (сооружение)</t>
+          <t xml:space="preserve">Плавучий док</t>
         </is>
       </c>
       <c r="F285">
-        <v>3</v>
-      </c>
-      <c r="G285">
-        <v>561</v>
+        <v>14</v>
+      </c>
+      <c r="G285" s="3">
+        <v>2024</v>
       </c>
       <c r="W285" t="inlineStr">
         <is>
@@ -16456,21 +16494,21 @@
         </is>
       </c>
       <c r="Z285">
-        <v>59.915481</v>
+        <v>59.920492</v>
       </c>
       <c r="AA285">
-        <v>30.269281</v>
+        <v>30.269747</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">MB4</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Подзорный мост</t>
+          <t xml:space="preserve">Причальный мост над устьем Пряжки</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -16482,7 +16520,7 @@
         <v>3</v>
       </c>
       <c r="G286">
-        <v>450</v>
+        <v>722</v>
       </c>
       <c r="W286" t="inlineStr">
         <is>
@@ -16490,21 +16528,21 @@
         </is>
       </c>
       <c r="Z286">
-        <v>59.920884</v>
+        <v>59.921307</v>
       </c>
       <c r="AA286">
-        <v>30.273826</v>
+        <v>30.270857</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мост</t>
+          <t xml:space="preserve">Галерный мост</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -16516,7 +16554,7 @@
         <v>3</v>
       </c>
       <c r="G287">
-        <v>317</v>
+        <v>561</v>
       </c>
       <c r="W287" t="inlineStr">
         <is>
@@ -16524,38 +16562,33 @@
         </is>
       </c>
       <c r="Z287">
-        <v>59.92661</v>
+        <v>59.915481</v>
       </c>
       <c r="AA287">
-        <v>30.275432</v>
+        <v>30.269281</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t xml:space="preserve">B26</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мост</t>
+          <t xml:space="preserve">Подзорный мост</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
           <t xml:space="preserve">Заводской мост (сооружение)</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Матисов остров</t>
         </is>
       </c>
       <c r="F288">
         <v>3</v>
       </c>
       <c r="G288">
-        <v>183</v>
+        <v>450</v>
       </c>
       <c r="W288" t="inlineStr">
         <is>
@@ -16563,38 +16596,33 @@
         </is>
       </c>
       <c r="Z288">
-        <v>59.920798</v>
+        <v>59.920884</v>
       </c>
       <c r="AA288">
-        <v>30.276034</v>
+        <v>30.273826</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t xml:space="preserve">CH1</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Дымовая труба котельной «Судомеха»</t>
+          <t xml:space="preserve">Мост</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Дымовая труба (сооружение)</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ново-Адмиралтейский остров</t>
+          <t xml:space="preserve">Заводской мост (сооружение)</t>
         </is>
       </c>
       <c r="F289">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="G289">
-        <v>9</v>
+        <v>317</v>
       </c>
       <c r="W289" t="inlineStr">
         <is>
@@ -16602,38 +16630,38 @@
         </is>
       </c>
       <c r="Z289">
-        <v>59.92859</v>
+        <v>59.92661</v>
       </c>
       <c r="AA289">
-        <v>30.281231</v>
+        <v>30.275432</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t xml:space="preserve">CH2</t>
+          <t xml:space="preserve">B26</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Дымовая труба котельной «Судомеха»</t>
+          <t xml:space="preserve">Мост</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Дымовая труба (сооружение)</t>
+          <t xml:space="preserve">Заводской мост (сооружение)</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ново-Адмиралтейский остров</t>
+          <t xml:space="preserve">Матисов остров</t>
         </is>
       </c>
       <c r="F290">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="G290">
-        <v>9</v>
+        <v>183</v>
       </c>
       <c r="W290" t="inlineStr">
         <is>
@@ -16641,16 +16669,16 @@
         </is>
       </c>
       <c r="Z290">
-        <v>59.928658</v>
+        <v>59.920798</v>
       </c>
       <c r="AA290">
-        <v>30.281263</v>
+        <v>30.276034</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t xml:space="preserve">CH3</t>
+          <t xml:space="preserve">CH1</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -16669,7 +16697,7 @@
         </is>
       </c>
       <c r="F291">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G291">
         <v>9</v>
@@ -16680,38 +16708,38 @@
         </is>
       </c>
       <c r="Z291">
-        <v>59.928707</v>
+        <v>59.92859</v>
       </c>
       <c r="AA291">
-        <v>30.281407</v>
+        <v>30.281231</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t xml:space="preserve">S1</t>
+          <t xml:space="preserve">CH2</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Открытый наклонный стапель № 1</t>
+          <t xml:space="preserve">Дымовая труба котельной «Судомеха»</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Стапель (сооружение)</t>
+          <t xml:space="preserve">Дымовая труба (сооружение)</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Основная площадка</t>
+          <t xml:space="preserve">Ново-Адмиралтейский остров</t>
         </is>
       </c>
       <c r="F292">
-        <v>6</v>
-      </c>
-      <c r="G292" s="3">
-        <v>9681</v>
+        <v>32</v>
+      </c>
+      <c r="G292">
+        <v>9</v>
       </c>
       <c r="W292" t="inlineStr">
         <is>
@@ -16719,38 +16747,38 @@
         </is>
       </c>
       <c r="Z292">
-        <v>59.917317</v>
+        <v>59.928658</v>
       </c>
       <c r="AA292">
-        <v>30.268153</v>
+        <v>30.281263</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t xml:space="preserve">S2</t>
+          <t xml:space="preserve">CH3</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Открытый наклонный стапель № 2</t>
+          <t xml:space="preserve">Дымовая труба котельной «Судомеха»</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Стапель (сооружение)</t>
+          <t xml:space="preserve">Дымовая труба (сооружение)</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Основная площадка</t>
+          <t xml:space="preserve">Ново-Адмиралтейский остров</t>
         </is>
       </c>
       <c r="F293">
-        <v>6</v>
-      </c>
-      <c r="G293" s="3">
-        <v>9630</v>
+        <v>31</v>
+      </c>
+      <c r="G293">
+        <v>9</v>
       </c>
       <c r="W293" t="inlineStr">
         <is>
@@ -16758,35 +16786,38 @@
         </is>
       </c>
       <c r="Z293">
-        <v>59.917763</v>
+        <v>59.928707</v>
       </c>
       <c r="AA293">
-        <v>30.268565</v>
+        <v>30.281407</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">S1</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Портальный кран (Матисов остров)</t>
+          <t xml:space="preserve">Открытый наклонный стапель № 1</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Грузоподъёмный кран</t>
+          <t xml:space="preserve">Стапель (сооружение)</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Матисов остров</t>
+          <t xml:space="preserve">Основная площадка</t>
         </is>
       </c>
       <c r="F294">
-        <v>44</v>
+        <v>6</v>
+      </c>
+      <c r="G294" s="3">
+        <v>9681</v>
       </c>
       <c r="W294" t="inlineStr">
         <is>
@@ -16794,35 +16825,38 @@
         </is>
       </c>
       <c r="Z294">
-        <v>59.922241</v>
+        <v>59.917317</v>
       </c>
       <c r="AA294">
-        <v>30.271466</v>
+        <v>30.268153</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">S2</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Портальный кран (Матисов остров)</t>
+          <t xml:space="preserve">Открытый наклонный стапель № 2</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Грузоподъёмный кран</t>
+          <t xml:space="preserve">Стапель (сооружение)</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Матисов остров</t>
+          <t xml:space="preserve">Основная площадка</t>
         </is>
       </c>
       <c r="F295">
-        <v>44</v>
+        <v>6</v>
+      </c>
+      <c r="G295" s="3">
+        <v>9630</v>
       </c>
       <c r="W295" t="inlineStr">
         <is>
@@ -16830,21 +16864,21 @@
         </is>
       </c>
       <c r="Z295">
-        <v>59.923143</v>
+        <v>59.917763</v>
       </c>
       <c r="AA295">
-        <v>30.272097</v>
+        <v>30.268565</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Портальный кран причала у устья Мойки</t>
+          <t xml:space="preserve">Портальный кран (Матисов остров)</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -16866,21 +16900,21 @@
         </is>
       </c>
       <c r="Z296">
-        <v>59.924415</v>
+        <v>59.922241</v>
       </c>
       <c r="AA296">
-        <v>30.272258</v>
+        <v>30.271466</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Портальный кран причала у устья Мойки</t>
+          <t xml:space="preserve">Портальный кран (Матисов остров)</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -16902,21 +16936,21 @@
         </is>
       </c>
       <c r="Z297">
-        <v>59.9252</v>
+        <v>59.923143</v>
       </c>
       <c r="AA297">
-        <v>30.272657</v>
+        <v>30.272097</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t xml:space="preserve">C10</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Портальный кран (Новое Адмиралтейство)</t>
+          <t xml:space="preserve">Портальный кран причала у устья Мойки</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -16926,11 +16960,11 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ново-Адмиралтейский остров</t>
+          <t xml:space="preserve">Матисов остров</t>
         </is>
       </c>
       <c r="F298">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="W298" t="inlineStr">
         <is>
@@ -16938,21 +16972,21 @@
         </is>
       </c>
       <c r="Z298">
-        <v>59.928636</v>
+        <v>59.924415</v>
       </c>
       <c r="AA298">
-        <v>30.275116</v>
+        <v>30.272258</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t xml:space="preserve">Стапельный кран (путь между стапелями)</t>
+          <t xml:space="preserve">Портальный кран причала у устья Мойки</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -16962,11 +16996,11 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t xml:space="preserve">Основная площадка</t>
+          <t xml:space="preserve">Матисов остров</t>
         </is>
       </c>
       <c r="F299">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="W299" t="inlineStr">
         <is>
@@ -16974,21 +17008,21 @@
         </is>
       </c>
       <c r="Z299">
-        <v>59.917374</v>
+        <v>59.9252</v>
       </c>
       <c r="AA299">
-        <v>30.269392</v>
+        <v>30.272657</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">C10</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Стапельный кран (путь между стапелями)</t>
+          <t xml:space="preserve">Портальный кран (Новое Адмиралтейство)</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -16998,11 +17032,11 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Основная площадка</t>
+          <t xml:space="preserve">Ново-Адмиралтейский остров</t>
         </is>
       </c>
       <c r="F300">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="W300" t="inlineStr">
         <is>
@@ -17010,21 +17044,21 @@
         </is>
       </c>
       <c r="Z300">
-        <v>59.917628</v>
+        <v>59.928636</v>
       </c>
       <c r="AA300">
-        <v>30.267768</v>
+        <v>30.275116</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Стапельный кран стапеля № 1</t>
+          <t xml:space="preserve">Стапельный кран (путь между стапелями)</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -17038,7 +17072,7 @@
         </is>
       </c>
       <c r="F301">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="W301" t="inlineStr">
         <is>
@@ -17046,21 +17080,21 @@
         </is>
       </c>
       <c r="Z301">
-        <v>59.917055</v>
+        <v>59.917374</v>
       </c>
       <c r="AA301">
-        <v>30.26823</v>
+        <v>30.269392</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t xml:space="preserve">Портальный кран достроечной набережной</t>
+          <t xml:space="preserve">Стапельный кран (путь между стапелями)</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -17074,7 +17108,7 @@
         </is>
       </c>
       <c r="F302">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="W302" t="inlineStr">
         <is>
@@ -17082,50 +17116,122 @@
         </is>
       </c>
       <c r="Z302">
-        <v>59.920147</v>
+        <v>59.917628</v>
       </c>
       <c r="AA302">
-        <v>30.27</v>
+        <v>30.267768</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
+          <t xml:space="preserve">C3</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Стапельный кран стапеля № 1</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Грузоподъёмный кран</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Основная площадка</t>
+        </is>
+      </c>
+      <c r="F303">
+        <v>54</v>
+      </c>
+      <c r="W303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Нет данных</t>
+        </is>
+      </c>
+      <c r="Z303">
+        <v>59.917055</v>
+      </c>
+      <c r="AA303">
+        <v>30.26823</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C4</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Портальный кран достроечной набережной</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Грузоподъёмный кран</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Основная площадка</t>
+        </is>
+      </c>
+      <c r="F304">
+        <v>42</v>
+      </c>
+      <c r="W304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Нет данных</t>
+        </is>
+      </c>
+      <c r="Z304">
+        <v>59.920147</v>
+      </c>
+      <c r="AA304">
+        <v>30.27</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
           <t xml:space="preserve">C5</t>
         </is>
       </c>
-      <c r="B303" t="inlineStr">
+      <c r="B305" t="inlineStr">
         <is>
           <t xml:space="preserve">Портальный кран достроечной набережной</t>
         </is>
       </c>
-      <c r="C303" t="inlineStr">
+      <c r="C305" t="inlineStr">
         <is>
           <t xml:space="preserve">Грузоподъёмный кран</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr">
+      <c r="D305" t="inlineStr">
         <is>
           <t xml:space="preserve">Основная площадка</t>
         </is>
       </c>
-      <c r="F303">
+      <c r="F305">
         <v>42</v>
       </c>
-      <c r="W303" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Нет данных</t>
-        </is>
-      </c>
-      <c r="Z303">
+      <c r="W305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Нет данных</t>
+        </is>
+      </c>
+      <c r="Z305">
         <v>59.92075</v>
       </c>
-      <c r="AA303">
+      <c r="AA305">
         <v>30.270422</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA303"/>
+  <autoFilter ref="A1:AA305"/>
 </worksheet>
 </file>
 
@@ -17168,7 +17274,7 @@
       </c>
       <c r="B3" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">302</t>
+          <t xml:space="preserve">304</t>
         </is>
       </c>
     </row>

--- a/admiralty-shipyards-territory/dist/admiralty-shipyards-registry.xlsx
+++ b/admiralty-shipyards-territory/dist/admiralty-shipyards-registry.xlsx
@@ -17256,7 +17256,7 @@
       </c>
       <c r="B2" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">02.10.2026</t>
+          <t xml:space="preserve">03.10.2026</t>
         </is>
       </c>
     </row>

--- a/admiralty-shipyards-territory/dist/admiralty-shipyards-registry.xlsx
+++ b/admiralty-shipyards-territory/dist/admiralty-shipyards-registry.xlsx
@@ -293,7 +293,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y2">
@@ -409,7 +409,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y4">
@@ -525,7 +525,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y6">
@@ -578,7 +578,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y7">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y15">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y19">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y22">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y23">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y51">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y52">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y53">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y55">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y56">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y60">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y65">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y66">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y69">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y72">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y73">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y74">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y85">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y111">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y113">
@@ -6850,7 +6850,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y116">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y117">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y118">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y119">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y120">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y121">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y124">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y130">
@@ -7975,7 +7975,7 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y136">
@@ -8033,7 +8033,7 @@
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y137">
@@ -8550,7 +8550,7 @@
       </c>
       <c r="X146" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y146">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="X149" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y149">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="X153" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y153">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="X158" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y158">
@@ -9304,7 +9304,7 @@
       </c>
       <c r="X159" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y159">
@@ -9362,7 +9362,7 @@
       </c>
       <c r="X160" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y160">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="X164" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y164">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="X165" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y165">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="X167" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y167">
@@ -10744,7 +10744,7 @@
       </c>
       <c r="X184" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y184">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="X185" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y185">
@@ -10850,7 +10850,7 @@
       </c>
       <c r="X186" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y186">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="X187" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y187">
@@ -10956,7 +10956,7 @@
       </c>
       <c r="X188" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y188">
@@ -11009,7 +11009,7 @@
       </c>
       <c r="X189" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y189">
@@ -11289,7 +11289,7 @@
       </c>
       <c r="X194" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y194">
@@ -11801,7 +11801,7 @@
       </c>
       <c r="X203" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y203">
@@ -11975,7 +11975,7 @@
       </c>
       <c r="X206" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y206">
@@ -12207,7 +12207,7 @@
       </c>
       <c r="X210" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y210">
@@ -12429,7 +12429,7 @@
       </c>
       <c r="X214" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y214">
@@ -12661,7 +12661,7 @@
       </c>
       <c r="X218" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y218">
@@ -12951,7 +12951,7 @@
       </c>
       <c r="X223" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y223">
@@ -13183,7 +13183,7 @@
       </c>
       <c r="X227" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y227">
@@ -13294,7 +13294,7 @@
       </c>
       <c r="X229" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y229">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="X230" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y230">
@@ -13811,7 +13811,7 @@
       </c>
       <c r="X238" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y238">
@@ -13869,7 +13869,7 @@
       </c>
       <c r="X239" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y239">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="X241" t="inlineStr">
         <is>
-          <t xml:space="preserve">карта предприятия</t>
+          <t xml:space="preserve">уточнённый контур</t>
         </is>
       </c>
       <c r="Y241">
@@ -17316,7 +17316,7 @@
       </c>
       <c r="B7" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">OpenStreetMap и Microsoft ML Buildings (через Overture Maps, лицензия ODbL), карта предприятия.</t>
+          <t xml:space="preserve">OpenStreetMap и Microsoft ML Buildings (через Overture Maps, лицензия ODbL); часть контуров уточнена.</t>
         </is>
       </c>
     </row>

--- a/admiralty-shipyards-territory/dist/admiralty-shipyards-registry.xlsx
+++ b/admiralty-shipyards-territory/dist/admiralty-shipyards-registry.xlsx
@@ -258,7 +258,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Главный корпус Галерного острова</t>
+          <t xml:space="preserve">Главный корпус Галерного острова 1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3108,6 +3108,11 @@
       <c r="I51" s="3">
         <v>147901</v>
       </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7 Цех</t>
+        </is>
+      </c>
       <c r="V51" t="inlineStr">
         <is>
           <t xml:space="preserve">Нет данных</t>
@@ -10737,6 +10742,11 @@
       <c r="I184" s="3">
         <v>301688</v>
       </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7 Цех; ОТЗ</t>
+        </is>
+      </c>
       <c r="V184" t="inlineStr">
         <is>
           <t xml:space="preserve">Нет данных</t>
@@ -16966,10 +16976,10 @@
         </is>
       </c>
       <c r="Y298">
-        <v>59.924415</v>
+        <v>59.924676</v>
       </c>
       <c r="Z298">
-        <v>30.272258</v>
+        <v>30.272396</v>
       </c>
     </row>
     <row r="299">
@@ -17256,7 +17266,7 @@
       </c>
       <c r="B2" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">03.10.2026</t>
+          <t xml:space="preserve">06.10.2026</t>
         </is>
       </c>
     </row>

--- a/admiralty-shipyards-territory/dist/admiralty-shipyards-registry.xlsx
+++ b/admiralty-shipyards-territory/dist/admiralty-shipyards-registry.xlsx
@@ -31529,7 +31529,7 @@
       </c>
       <c r="B5" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">Впишите данные в столбцы: Инвентарный №, Год постройки, Класс ОПО, Рег. № ОПО, № заключения ЭПБ, Дата заключения ЭПБ, Срок безопасной эксплуатации до, Техническое состояние, Дата обследования, Примечание. Столбец «Код в модели» не меняйте — по нему строки сопоставляются с объектами. Даты — в формате ДД.ММ.ГГГГ. Столбец «Инвентарный №» уже заполнен по данным предприятия, при необходимости поправьте. Затем загрузите файл в реестр кнопкой «Загрузить таблицу».</t>
+          <t xml:space="preserve">Впишите данные в столбцы: Инвентарный №, Год постройки, Класс ОПО, Рег. № ОПО, № заключения ЭПБ, Дата заключения ЭПБ, Срок безопасной эксплуатации до, Техническое состояние, Дата обследования, Примечание. Столбец «Код в модели» не меняйте — по нему строки сопоставляются с объектами. Даты — в формате ДД.ММ.ГГГГ. Столбец «Инвентарный №» уже заполнен, при необходимости поправьте. Затем загрузите файл в реестр кнопкой «Загрузить таблицу».</t>
         </is>
       </c>
     </row>
@@ -31542,18 +31542,6 @@
       <c r="B6" t="inlineStr" s="7">
         <is>
           <t xml:space="preserve">Площадь застройки — по контуру здания (за вычетом дворов). Этажность — по OpenStreetMap, для цехов и складов без данных — 1, для остальных — по высоте. Общая площадь — площадь застройки × этажность. Строительный объём — площадь застройки × высоту до средней отметки кровли. Высоты цехов верфи в открытых данных отсутствуют и оценены — такие строки отмечены в столбце «Высота оценена».</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Данные предприятия</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">Контуры зданий и сооружений верфи, номера объектов, инвентарные номера, литеры и назначение — по данным предприятия. У зданий без обмеров высоты оценены по назначению и размерам (отмечены в столбце «Высота оценена»).</t>
         </is>
       </c>
     </row>

--- a/admiralty-shipyards-territory/dist/admiralty-shipyards-registry.xlsx
+++ b/admiralty-shipyards-territory/dist/admiralty-shipyards-registry.xlsx
@@ -31463,6 +31463,30 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AB516"/>
+  <dataValidations count="6">
+    <dataValidation type="whole" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="Число" error="Введите целое число от 1700 до 2100" sqref="P2:P516">
+      <formula1>1700</formula1>
+      <formula2>2100</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Значение не из списка" error="Выберите одно из значений: I, II, III, IV, не ОПО" promptTitle="Класс ОПО" prompt="Выберите значение из списка" sqref="Q2:Q516">
+      <formula1>"I,II,III,IV,не ОПО"</formula1>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="Дата" error="Введите дату в формате ДД.ММ.ГГГГ" sqref="T2:T516">
+      <formula1>1</formula1>
+      <formula2>73050</formula2>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="Дата" error="Введите дату в формате ДД.ММ.ГГГГ" sqref="U2:U516">
+      <formula1>1</formula1>
+      <formula2>73050</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Значение не из списка" error="Выберите одно из значений: нормативное, работоспособное, ограниченно работоспособное, аварийное" promptTitle="Техническое состояние" prompt="Выберите значение из списка" sqref="V2:V516">
+      <formula1>"нормативное,работоспособное,ограниченно работоспособное,аварийное"</formula1>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="Дата" error="Введите дату в формате ДД.ММ.ГГГГ" sqref="W2:W516">
+      <formula1>1</formula1>
+      <formula2>73050</formula2>
+    </dataValidation>
+  </dataValidations>
 </worksheet>
 </file>
 

--- a/admiralty-shipyards-territory/dist/admiralty-shipyards-registry.xlsx
+++ b/admiralty-shipyards-territory/dist/admiralty-shipyards-registry.xlsx
@@ -27,7 +27,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -54,6 +54,11 @@
         <fgColor rgb="FFCDEBD6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -67,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1" vertical="center"/>
@@ -79,6 +84,9 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -109,10 +117,10 @@
     <col min="17" max="17" width="18" customWidth="1"/>
     <col min="18" max="18" width="18" customWidth="1"/>
     <col min="19" max="19" width="18" customWidth="1"/>
-    <col min="20" max="20" width="14" customWidth="1"/>
-    <col min="21" max="21" width="14" customWidth="1"/>
+    <col min="20" max="20" width="18" customWidth="1"/>
+    <col min="21" max="21" width="18" customWidth="1"/>
     <col min="22" max="22" width="18" customWidth="1"/>
-    <col min="23" max="23" width="14" customWidth="1"/>
+    <col min="23" max="23" width="18" customWidth="1"/>
     <col min="24" max="24" width="30" customWidth="1"/>
     <col min="25" max="25" width="14" customWidth="1"/>
     <col min="26" max="26" width="12" customWidth="1"/>
@@ -120,7 +128,7 @@
     <col min="28" max="28" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="45" customHeight="1">
       <c r="A1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Код в модели</t>
@@ -136,7 +144,7 @@
           <t xml:space="preserve">№ объекта</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr" s="1">
+      <c r="D1" t="inlineStr" s="8">
         <is>
           <t xml:space="preserve">Инвентарный №</t>
         </is>
@@ -196,47 +204,47 @@
           <t xml:space="preserve">Отвечает за здание</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr" s="1">
+      <c r="P1" t="inlineStr" s="8">
         <is>
           <t xml:space="preserve">Год постройки</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr" s="1">
+      <c r="Q1" t="inlineStr" s="8">
         <is>
           <t xml:space="preserve">Класс ОПО</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr" s="1">
+      <c r="R1" t="inlineStr" s="8">
         <is>
           <t xml:space="preserve">Рег. № ОПО</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr" s="1">
+      <c r="S1" t="inlineStr" s="8">
         <is>
           <t xml:space="preserve">№ заключения ЭПБ</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr" s="1">
+      <c r="T1" t="inlineStr" s="8">
         <is>
           <t xml:space="preserve">Дата заключения ЭПБ</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr" s="1">
+      <c r="U1" t="inlineStr" s="8">
         <is>
           <t xml:space="preserve">Срок безопасной эксплуатации до</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr" s="1">
+      <c r="V1" t="inlineStr" s="8">
         <is>
           <t xml:space="preserve">Техническое состояние</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr" s="1">
+      <c r="W1" t="inlineStr" s="8">
         <is>
           <t xml:space="preserve">Дата обследования</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr" s="1">
+      <c r="X1" t="inlineStr" s="8">
         <is>
           <t xml:space="preserve">Примечание</t>
         </is>
@@ -31497,7 +31505,7 @@
     <col min="2" max="2" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="45" customHeight="1">
       <c r="A1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Параметр</t>
@@ -31553,17 +31561,29 @@
       </c>
       <c r="B5" t="inlineStr" s="7">
         <is>
-          <t xml:space="preserve">Впишите данные в столбцы: Инвентарный №, Год постройки, Класс ОПО, Рег. № ОПО, № заключения ЭПБ, Дата заключения ЭПБ, Срок безопасной эксплуатации до, Техническое состояние, Дата обследования, Примечание. Столбец «Код в модели» не меняйте — по нему строки сопоставляются с объектами. Даты — в формате ДД.ММ.ГГГГ. Столбец «Инвентарный №» уже заполнен, при необходимости поправьте. Затем загрузите файл в реестр кнопкой «Загрузить таблицу».</t>
+          <t xml:space="preserve">Впишите данные в столбцы с жёлтой шапкой: Инвентарный №, Год постройки, Класс ОПО, Рег. № ОПО, № заключения ЭПБ, Дата заключения ЭПБ, Срок безопасной эксплуатации до, Техническое состояние, Дата обследования, Примечание. Столбец «Код в модели» не меняйте — по нему строки сопоставляются с объектами. Даты — в формате ДД.ММ.ГГГГ. Столбец «Инвентарный №» уже заполнен, при необходимости поправьте. Затем загрузите файл в реестр кнопкой «Загрузить таблицу».</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Выпадающие списки</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">В столбцах «Класс ОПО» и «Техническое состояние» значение выбирается из списка: выделите ячейку и нажмите стрелку справа от неё. Если Excel открыл файл в режиме защищённого просмотра, сначала нажмите «Разрешить редактирование». Значения не из списка, неверные даты и год постройки вне 1700–2100 при загрузке в реестр пропускаются.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Расчётные показатели</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr" s="7">
+      <c r="B7" t="inlineStr" s="7">
         <is>
           <t xml:space="preserve">Площадь застройки — по контуру здания (за вычетом дворов). Этажность — по OpenStreetMap, для цехов и складов без данных — 1, для остальных — по высоте. Общая площадь — площадь застройки × этажность. Строительный объём — площадь застройки × высоту до средней отметки кровли. Высоты цехов верфи в открытых данных отсутствуют и оценены — такие строки отмечены в столбце «Высота оценена».</t>
         </is>

--- a/admiralty-shipyards-territory/dist/admiralty-shipyards-registry.xlsx
+++ b/admiralty-shipyards-territory/dist/admiralty-shipyards-registry.xlsx
@@ -1058,19 +1058,19 @@
         <v>20.1</v>
       </c>
       <c r="V13">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="W13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X13" s="3">
         <v>1191</v>
       </c>
       <c r="Y13" s="3">
-        <v>4762</v>
+        <v>5953</v>
       </c>
       <c r="Z13" s="3">
-        <v>17858</v>
+        <v>20835</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>38</v>
       </c>
       <c r="V59">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="W59">
         <v>3</v>
@@ -4129,7 +4129,7 @@
         <v>3364</v>
       </c>
       <c r="Z59" s="3">
-        <v>13454</v>
+        <v>14762</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
@@ -11414,19 +11414,19 @@
         <v>17.3</v>
       </c>
       <c r="V172">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="W172">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X172" s="3">
         <v>1094</v>
       </c>
       <c r="Y172" s="3">
-        <v>1126</v>
+        <v>3314</v>
       </c>
       <c r="Z172" s="3">
-        <v>7801</v>
+        <v>12178</v>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
@@ -12025,19 +12025,19 @@
         <v>24.7</v>
       </c>
       <c r="V181">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W181">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X181">
         <v>619</v>
       </c>
       <c r="Y181" s="3">
-        <v>1995</v>
+        <v>2615</v>
       </c>
       <c r="Z181" s="3">
-        <v>8049</v>
+        <v>9288</v>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
@@ -12350,7 +12350,7 @@
         <v>23.5</v>
       </c>
       <c r="V186">
-        <v>7.6</v>
+        <v>8.2</v>
       </c>
       <c r="W186">
         <v>2</v>
@@ -12362,7 +12362,7 @@
         <v>1043</v>
       </c>
       <c r="Z186" s="3">
-        <v>3983</v>
+        <v>4283</v>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
@@ -12885,13 +12885,13 @@
         <v>7</v>
       </c>
       <c r="W194">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X194">
         <v>357</v>
       </c>
       <c r="Y194">
-        <v>357</v>
+        <v>713</v>
       </c>
       <c r="Z194" s="3">
         <v>2497</v>
@@ -13018,13 +13018,13 @@
         <v>9</v>
       </c>
       <c r="W196">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X196">
         <v>334</v>
       </c>
       <c r="Y196">
-        <v>400</v>
+        <v>734</v>
       </c>
       <c r="Z196" s="3">
         <v>3304</v>
@@ -13240,13 +13240,13 @@
         <v>9</v>
       </c>
       <c r="W199">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X199">
         <v>304</v>
       </c>
       <c r="Y199">
-        <v>306</v>
+        <v>610</v>
       </c>
       <c r="Z199" s="3">
         <v>2744</v>
@@ -13296,7 +13296,7 @@
         <v>17.8</v>
       </c>
       <c r="V200">
-        <v>7.6</v>
+        <v>8.2</v>
       </c>
       <c r="W200">
         <v>2</v>
@@ -13308,7 +13308,7 @@
         <v>606</v>
       </c>
       <c r="Z200" s="3">
-        <v>2301</v>
+        <v>2483</v>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
@@ -19169,19 +19169,19 @@
         <v>28.1</v>
       </c>
       <c r="V292">
-        <v>7</v>
+        <v>15.5</v>
       </c>
       <c r="W292">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X292">
         <v>637</v>
       </c>
-      <c r="Y292">
-        <v>842</v>
+      <c r="Y292" s="3">
+        <v>2117</v>
       </c>
       <c r="Z292" s="3">
-        <v>5383</v>
+        <v>9685</v>
       </c>
       <c r="AA292" t="inlineStr">
         <is>
